--- a/Pengujian UNI-NEXUS.xlsx
+++ b/Pengujian UNI-NEXUS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College\Telkom University\Associate Degree of Information Systems\Projects\UNI-NEXUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3284A4DC-995E-4C2A-858A-8A59831C9386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E92382A-4A66-4F4E-A6CC-B69FFE6282D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="1430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="1434">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -9690,6 +9690,18 @@
 • Global Search tidak pernah menjadi bypass permission/workspace.
 • Debounce+Abort mencegah stale result race dan keyboard interaction dapat digunakan penuh.
 • Dengan kasus ini, seluruh fitur global production yang ditemukan final route audit memiliki coverage eksplisit.</t>
+  </si>
+  <si>
+    <t>[2026-09-14 16:17 WIB] Dry run oleh ACCOUNT #4 (Chief Technology Officer). Currency IDR -&gt; USD: dialog 'Ubah mata uang default?' tampil dengan penjelasan dampak; Batal tidak mengubah nilai setelah reload, konfirmasi menyimpan USD, lalu nilai berhasil dipulihkan ke IDR. Timezone Asia/Jakarta -&gt; UTC: dialog 'Ubah zona waktu organisasi?' tampil dengan penjelasan bahwa timestamp historis tidak ditulis ulang; setelah 'Simpan Zona Waktu', alert 'Data pengaturan tidak valid.' tampil, nilai UTC tidak persisten, dan browser mencatat respons HTTP 400 pada /api/v1/settings/organization. Langkah lanjutan timezone dan uji gabungan tidak dilanjutkan karena kegagalan ini. Nilai asli Currency IDR dan Timezone Asia/Jakarta dipulihkan serta diverifikasi setelah reload. Tidak ada transaksi/dokumen historis tersedia di UI untuk verifikasi konversi/timestamp. Bukti: test-evidence/dry-run-1/UNX-S03-003/timezone-save-failure.png.</t>
+  </si>
+  <si>
+    <t>Dry Run 2 2026-09-14: Diuji via frontend. CTO melihat 7 dataset dan kontrol kelola; Insinyur 3D melihat 6 dataset sesuai scope tanpa Tambah Data/Kelola. Blocked pada langkah Penggunaan karena semua dataset berisi 0 record sehingga aksi Penggunaan pada record tidak tersedia. Status dibiarkan kosong karena dropdown hanya Pass/Bug/Failed. Bukti: test-evidence/dry-run-2/UNX-S03-008/01-cto-initial-state.png dan 02-engineer-read-only.png.</t>
+  </si>
+  <si>
+    <t>Dry Run 2 2026-09-14: Diuji via frontend. Navigasi 7 dataset, pencarian, filter, refresh, dan viewport mobile tanpa overflow terverifikasi. Blocked untuk filter yang menghasilkan data, pagination &gt;25, dan ekspor CSV/XLSX nonkosong karena seluruh dataset berisi 0 record. Status dibiarkan kosong karena dropdown hanya Pass/Bug/Failed. Bukti: test-evidence/dry-run-2/UNX-S03-009/01-initial-overview.png dan 03-mobile-empty-state.png.</t>
+  </si>
+  <si>
+    <t>Dry Run 2 2026-09-14: Pass. QA_U_163552 dibuat aktif dan diedit menjadi Satuan QA Edit 163552 (qe, weight, 3 desimal). Validasi input, uppercase, duplicate, code lock, penggunaan 0, batal nonaktif, nonaktif/aktif kembali terverifikasi. Satuan QA dibiarkan aktif untuk prasyarat test lanjutan. Bukti: test-evidence/dry-run-2/UNX-S03-010/01-validation-error.png dan 02-final-active-unit.png.</t>
   </si>
 </sst>
 </file>
@@ -11210,9 +11222,13 @@
       <c r="E34" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="F34" s="5"/>
+      <c r="F34" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>1430</v>
+      </c>
       <c r="I34" s="4"/>
       <c r="O34" s="10"/>
     </row>
@@ -11328,9 +11344,13 @@
       <c r="E39" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="F39" s="5"/>
+      <c r="F39" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
+      <c r="H39" s="4" t="s">
+        <v>1431</v>
+      </c>
       <c r="I39" s="4"/>
       <c r="O39" s="10"/>
     </row>
@@ -11350,9 +11370,13 @@
       <c r="E40" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="F40" s="5"/>
+      <c r="F40" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
+      <c r="H40" s="4" t="s">
+        <v>1432</v>
+      </c>
       <c r="I40" s="4"/>
       <c r="O40" s="10"/>
     </row>
@@ -11372,9 +11396,13 @@
       <c r="E41" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F41" s="5"/>
+      <c r="F41" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
+      <c r="H41" s="4" t="s">
+        <v>1433</v>
+      </c>
       <c r="I41" s="4"/>
       <c r="O41" s="10"/>
     </row>

--- a/Pengujian UNI-NEXUS.xlsx
+++ b/Pengujian UNI-NEXUS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\College\Telkom University\Associate Degree of Information Systems\Projects\UNI-NEXUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E92382A-4A66-4F4E-A6CC-B69FFE6282D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE6D48E3-1FDE-4368-A483-105E342D2D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="1434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2181" uniqueCount="1654">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -9702,6 +9702,686 @@
   </si>
   <si>
     <t>Dry Run 2 2026-09-14: Pass. QA_U_163552 dibuat aktif dan diedit menjadi Satuan QA Edit 163552 (qe, weight, 3 desimal). Validasi input, uppercase, duplicate, code lock, penggunaan 0, batal nonaktif, nonaktif/aktif kembali terverifikasi. Satuan QA dibiarkan aktif untuk prasyarat test lanjutan. Bukti: test-evidence/dry-run-2/UNX-S03-010/01-validation-error.png dan 02-final-active-unit.png.</t>
+  </si>
+  <si>
+    <t>Promosi periode valid menambahkan badge Mitra, tombol Kelola Kemitraan, tab Harga Mitra, dan tetap mempertahankan pelanggan aktif serta kode CUS-000015. Rentang terbalik ditolak dan Batal pada pengakhiran tidak mengubah status; pengakhiran menonaktifkan kemitraan tanpa menonaktifkan pelanggan. Namun setelah periode valid diubah dan halaman di-reload, field Mulai berlaku dan Berakhir kembali kosong, sehingga persistensi periode tidak terpenuhi. Promosi ulang tanpa periode juga ditolak; promosi ulang dengan periode valid berhasil dan fixture aktif tampil pada halaman Mitra. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Craft.</t>
+  </si>
+  <si>
+    <t>Pelacakan dan pencarian berdasarkan kode, nama, email, telepon, WhatsApp, serta NPWP; filter jenis, hubungan, status, kombinasi, pesanan aktif, sort, halaman Mitra, kartu detail, keadaan kosong/reset, dan ekspor CSV telah dijalankan melalui UI Craft dan hasilnya terlihat sesuai. Pada langkah menonaktifkan Customer Duplicate QA (CUS-000016), data sudah berstatus Tidak Aktif sebelum tindakan dimulai sehingga tombol yang tersedia adalah Aktifkan, bukan Nonaktifkan; tindakan penonaktifan yang diwajibkan tidak dapat dilakukan tanpa mengubah prasyarat. Setelah reload, CUS-000016 tetap tampil pada filter Tidak Aktif dan file CSV terfilter berisi data CUS-000015. Karena satu langkah wajib tidak dapat dilaksanakan, hasil keseluruhan Bug/Failed. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Craft.</t>
+  </si>
+  <si>
+    <t>Melalui Kelola Kategori Produk, dibuat kategori induk dan anak baru; kode otomatis berubah menjadi huruf besar dengan garis bawah, kode manual pada kategori anak tersimpan, duplikasi kode dibuat unik dengan sufiks _2, dan hierarki induk-anak terlihat. Nama, kode, dan induk kategori anak diedit lalu tersimpan; pilihan induk tidak memuat kategori dirinya sendiri sehingga relasi siklik dicegah. Nama kosong tidak menambah baris, nama lebih dari 120 karakter ditolak dengan pesan Data kategori tidak valid. Kategori anak dinonaktifkan, tidak muncul pada pilihan kategori di form Tambah Produk, lalu diaktifkan kembali dan muncul sebagai opsi bertingkat. Data Master menampilkan record yang sama dan status Aktif. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Craft.</t>
+  </si>
+  <si>
+    <t>Form Tambah Produk melalui UI diuji dengan field wajib, tipe produk, kategori, deskripsi, harga, biaya, margin, berat, waktu cetak, dan gambar. Batas invalid tidak membuat row dan validasi menampilkan Data produk tidak valid. Produk utama tersimpan aktif dengan SKU otomatis PRD-000001, lalu persisten setelah reload; SKU duplikat ditolak. Produk pembanding tipe Layanan Custom berhasil dibuat lalu dinonaktifkan; produk utama tetap aktif dan ditemukan melalui pencarian katalog. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Craft.</t>
+  </si>
+  <si>
+    <t>Katalog Craft diuji dengan keadaan awal Aktif, pencarian SKU/nama/deskripsi/varian, filter kategori/tipe/status dan kombinasi AND, refresh, keadaan kosong, reset filter, kartu readiness, serta akses detail. Hasil terlihat sesuai; pencarian Varian QA 20260914_2256 menampilkan produk utama yang memuat varian tersebut. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Craft.</t>
+  </si>
+  <si>
+    <t>Detail produk, seluruh tab, nilai costing, readiness, riwayat kosong, edit, dan lifecycle aktif/nonaktif/aktif kembali diuji melalui UI. Produk nonaktif tidak muncul sebagai pilihan katalog atau produk pesanan baru. Unggah gambar unsupported, lebih dari 10 MB, dan file 6â€“10 MB yang tidak sesuai format ditolak dengan pesan UI yang sesuai; gambar valid tetap tersimpan. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Craft.</t>
+  </si>
+  <si>
+    <t>Form varian, validasi nilai kosong/negatif/di luar batas dan JSON invalid diuji tanpa membuat row invalid. Varian QA tersimpan dengan SKU otomatis, atribut, override harga/biaya/berat/waktu, dan persisten setelah reload; varian fallback juga tersimpan dengan harga dasar. SKU duplikat ditolak. Varian QA dinonaktifkan sehingga tidak ditawarkan pada pesanan baru, kemudian diaktifkan kembali. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Craft.</t>
+  </si>
+  <si>
+    <t>Pustaka Desain 3D diuji dari detail produk: upload valid pertama/kedua, aturan satu FINAL terbaru, filter Semua/Produk, reload, download, hapus desain non-final, serta penolakan AGENTS.md dan file STL lebih dari batas ukuran. Pada langkah submit tanpa file dan tanpa nama, row memang tidak dibuat, tetapi UI tidak menampilkan pesan wajib yang diharapkan Pilih file desain dan isi nama file; validasi yang terlihat tidak memenuhi Expected Result. Karena satu validasi wajib tidak terpenuhi, hasil keseluruhan Bug/Failed. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Craft.</t>
+  </si>
+  <si>
+    <t>Tab Profil Cetak dan form Tambah Profil dibuka melalui detail produk; field Nama, Produk, Printer, Slicer, Nozzle, Layer height, Infill, Est. cetak, Est. material, Satuan material, Support, dan Default terlihat. Submit kosong tidak menampilkan pesan UI Nama profil wajib diisi, dan nilai invalid tidak membuat row. Pada langkah pembuatan Profil A, nilai yang diwajibkan Nozzle 0,4 dan Layer height 0,2 ditolak validasi browser dengan pesan bahwa nilai valid terdekat adalah 0 dan 1, sehingga profil yang diminta tidak dapat disimpan dan langkah default/filter/delete/readiness tidak dapat diselesaikan. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Craft.</t>
+  </si>
+  <si>
+    <t>Pada CUS-000015 aktif, form Harga Mitra kosong menonaktifkan Simpan Harga. Batas minimum, diskon, harga negatif, dan periode terbalik ditolak tanpa row baru; Rule A produk dasar minimum 1 diskon 10% tersimpan, duplikat aktif ditolak dengan pesan yang diwajibkan, dan Rule B varian minimum 5 harga khusus tersimpan. Rule B diedit menjadi minimum 6 dan Rp125.000 lalu persisten setelah reload. Resolver pesanan Mitra memilih harga varian Rp125.000 pada kuantitas 6, sedangkan saat Rule B di luar periode harga kembali ke Rp144.000 dari Rule A. Dialog Nonaktifkan diuji dengan Batal lalu konfirmasi; Rule B tetap tersimpan sebagai Tidak Aktif dan Rule A tetap Aktif. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Craft.</t>
+  </si>
+  <si>
+    <t>Kategori QA Filament berhasil dibuat dengan kode MATCAT-000003, tipe filament, diganti nama menjadi QA Filament Utama, dinonaktifkan/diaktifkan kembali, tidak ditawarkan pada form material saat nonaktif, dan terlihat sama di Data Master setelah reload. Namun pada Data Master untuk akun yang diwajibkan tidak tersedia kontrol rename/mutasi, sehingga arah sinkronisasi balik dari Data Master tidak dapat dijalankan secara lengkap. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-62-71/UNX-S05-001/01-global-category-sync.png.</t>
+  </si>
+  <si>
+    <t>Form Tambah Material dapat dibuka dan penekanan Simpan tanpa Nama menampilkan validasi nama/kategori/satuan. Namun prasyarat tidak terpenuhi: pilihan satuan aktif hanya Satuan QA Edit 163552 (qe), bukan Gram/G, dan pemilih Pemasok Pilihan hanya berisi Belum dipilih tanpa pemasok aktif. Material utama/sekunder tidak dibuat karena data uji wajib tidak tersedia; langkah validasi numerik, warna, SKU, dan duplikasi tidak dapat dilanjutkan secara sah. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-62-71/UNX-S05-002/01-material-prerequisite-failure.png.</t>
+  </si>
+  <si>
+    <t>Tab Filament, Resin, Hardware, Kemasan, Consumable, dan Lainnya dapat dibuka dan menampilkan empty state; pencarian acak juga tidak menemukan data. Prasyarat material utama dan sekunder aktif tanpa stok tidak tersedia karena UNX-S05-002 gagal menemukan satuan Gram/G dan pemasok aktif. Kartu stok, pencarian SKU/nama/brand/jenis/warna, edit master, dan uji nonaktif material tidak dapat diverifikasi lengkap. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-62-71/UNX-S05-003/01-material-inventory-prerequisite-empty.png.</t>
+  </si>
+  <si>
+    <t>Inventaris Filament menampilkan Belum Ada Filament, sehingga detail material utama dan material sekunder tidak tersedia. Akibatnya ringkasan stok/batch/spool/movement, edit nilai, uji SKU duplikat, arsip-batal/konfirmasi, serta jalur aktivasi ulang tidak dapat dijalankan lengkap. Prasyarat dua material yang ditentukan tidak terpenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-62-71/UNX-S05-004/01-no-material-detail-or-archive.png.</t>
+  </si>
+  <si>
+    <t>Dialog Terima Stok dapat dibuka, tetapi pemilih material hanya menampilkan Pilih material... yang disabled dan tidak ada material aktif untuk dipilih. Karena material utama Filament bersatuan G dan pemasok/prasyarat material tidak tersedia, penerimaan 1.000 G tidak dapat dilakukan; batch, spool, nilai, dan movement tidak terbentuk sehingga Expected Result tidak terpenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-62-71/UNX-S05-005/01-receipt-no-material-picker.png.</t>
+  </si>
+  <si>
+    <t>Halaman Pergerakan Stok terbuka dan menampilkan Belum Ada Pergerakan Stok. Tidak ada detail material, batch 1.000 G, atau spool sebagai prasyarat, sehingga menu Sesuaikan Stok dan uji adjustment keluar/masuk, validasi saldo, reason default, serta perlindungan saldo tidak dapat dijalankan. Saldo akhir 975 G tidak dapat diverifikasi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-62-71/UNX-S05-006/01-no-material-movement.png.</t>
+  </si>
+  <si>
+    <t>Halaman Spool Filament terbuka dan menampilkan Belum Ada Spool Filament dengan keterangan spool dibuat saat penerimaan stok. Spool QA berbobot 975 G dan batch terkait tidak tersedia karena penerimaan pada UNX-S05-005 tidak dapat dilakukan; timbang ulang, lokasi, opened, dried, dan movement -75 tidak dapat diuji. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-62-71/UNX-S05-007/01-no-spool-prerequisite.png.</t>
+  </si>
+  <si>
+    <t>Form Catat Limbah Manual menampilkan field Material, Batch, Jumlah, Alasan, dan Catatan, serta pilihan alasan yang diminta. Namun Material hanya memiliki Pilih materialâ€¦, Batch disabled, dan submit kosong menampilkan Material, batch, dan jumlah limbah wajib valid. Material/batch QA 900 G tidak tersedia, sehingga waste 100 G, rollback saldo 800 G, movement waste, dan penolakan over-balance tidak dapat diselesaikan. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-62-71/UNX-S05-008/01-waste-no-material-validation.png.</t>
+  </si>
+  <si>
+    <t>Halaman Stok Menipis menampilkan Semua Stok Dalam Kondisi Aman dan tidak menampilkan material utama. Prasyarat Available 800 G, threshold 850 G, reorder 200 G, serta bukti material stok nol tidak tersedia karena material utama/sekunder belum berhasil dibuat. Badge low stock, tautan pengadaan dengan query material, perubahan threshold/reorder, dan pengecualian material nonaktif tidak dapat diverifikasi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-62-71/UNX-S05-009/01-low-stock-no-material.png.</t>
+  </si>
+  <si>
+    <t>Produk QA aktif dan desain 3D tersedia, tetapi Ringkasan terlihat menyatakan Profil cetak tersedia â€“ dan Profil cetak belum tersedia. Pada tab BOM / Material, form Tambah BOM tersedia tetapi pemilih Material hanya berisi Pilih material, tanpa material aktif Craft untuk dipilih. Karena prasyarat print profile dan material utama G dengan saldo 800/0/800 tidak terpenuhi, BOM valid v1, validasi material, pemeriksaan multi-item, dan verifikasi stok tidak dapat diselesaikan. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-62-71/UNX-S05-010/01-bom-material-picker-empty.png dan 02-product-prerequisite-missing-print-profile.png.</t>
+  </si>
+  <si>
+    <t>Produk uji dan halaman BOM dapat dibuka, tetapi ringkasan menunjukkan BOM dan profil cetak belum tersedia. Pada form Tambah BOM Material, pemilih material hanya menyediakan Pilih material tanpa material aktif Craft. Karena material utama/sekunder dan prasyarat profil cetak tidak tersedia, BOM v2, aktivasi, pemeriksaan stok, dan status kesiapan tidak dapat diselesaikan sesuai langkah. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-72-81/UNX-S05-011/01-bom-v2-prerequisites-missing.png.</t>
+  </si>
+  <si>
+    <t>Halaman costing produk dapat dibuka dan terlihat Belum ada BOM aktif; biaya efektif dan saran harga tampil, tetapi pembanding BOM aktif/fallback yang diwajibkan tidak tersedia. Karena BOM aktif dan data material prasyarat belum ada, formula costing, pembulatan, margin, serta verifikasi aktivasi tidak dapat diselesaikan lengkap. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-72-81/UNX-S05-012/01-no-active-bom-costing.png.</t>
+  </si>
+  <si>
+    <t>Printer utama dan printer sekunder berhasil dibuat melalui UI; kode dan nomor seri duplikat ditolak dengan pesan yang terlihat, pencarian kode/nama/brand/model, filter status, dan empty state pencarian juga bekerja. Namun pada uji nilai numerik tidak valid (nozzle/dimensi nol atau negatif dan biaya negatif), form tidak menampilkan validasi batas numerik yang jelas dan terlihat pesan lama Nama printer wajib diisi. Expected Result yang mewajibkan penolakan/validasi nilai numerik tidak terpenuhi secara dapat dibuktikan. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-72-81/UNX-S05-013/02-printer-list-search-filter.png.</t>
+  </si>
+  <si>
+    <t>Detail printer utama, metrik nol, edit metadata, perubahan Offline/Tersedia, halaman aktivitas, dan halaman riwayat berhasil diverifikasi. Printer sekunder dapat diarsipkan setelah pembatalan konfirmasi. Namun setelah arsip dikonfirmasi, tidak ada filter/daftar arsip yang dapat digunakan untuk mengaktifkan kembali printer; membuka URL detail lama lalu menekan aktivasi tidak mengembalikan printer ke daftar aktif. Expected Result untuk archive lalu reaktivasi tidak terpenuhi lengkap. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-72-81/UNX-S05-014/01-main-detail-metrics.png dan test-evidence/session-72-81/UNX-S05-014/02-archive-cancel-confirm-reactivate.png.</t>
+  </si>
+  <si>
+    <t>Validasi form kosong terlihat, jadwal berbasis tanggal dan jam cetak berhasil dibuat, diedit, dinonaktifkan/diaktifkan, sinkron dengan kalender, maintenance dimulai/diselesaikan, dan riwayat tampil. Jadwal alternatif dihapus setelah konfirmasi dan entri riwayat tetap ada. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-72-81/UNX-S05-015/01-maintenance-schedule-calendar-history.png dan test-evidence/session-72-81/UNX-S05-015/02-maintenance-completed-history-after-delete.png.</t>
+  </si>
+  <si>
+    <t>Submit kosong menampilkan validasi. Issue LOW tanpa assignee dan HIGH dengan assignee QA User-1 berhasil dibuat; issue HIGH membuat printer terlihat Bermasalah, dan filter severity/status menampilkan issue yang sesuai. Alur lengkap kasus berhasil diamati pada UI dengan ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-72-81/UNX-S06-001/01-high-low-issues-filters-open.png.</t>
+  </si>
+  <si>
+    <t>Issue HIGH dan LOW berhasil dipindahkan ke Investigasi, catatan penyelesaian diwajibkan sebelum simpan, lalu keduanya berhasil diselesaikan dan riwayat resolusi terlihat. Namun setelah semua issue open diselesaikan dan halaman dimuat ulang, kartu printer tetap berstatus Bermasalah, bukan Tersedia, tanpa job fisik aktif. Expected Result pemulihan status printer setelah seluruh issue selesai tidak terpenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-72-81/UNX-S06-002/02-printer-remains-problematic-after-resolve.png.</t>
+  </si>
+  <si>
+    <t>Ringkasan pengadaan dan halaman Stok Menipis dapat dibuka tanpa exception, tetapi seluruh metrik bernilai 0/Rp0, halaman low stock menyatakan semua stok aman, dan tidak ada material utama. Form permintaan/pesanan hanya menyediakan item non-material serta tidak menyediakan supplier/material uji. Expected Result stok 800, threshold 850, low-stock badge, serta cross navigation material tidak dapat dipenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-72-81/UNX-S06-003/01-procurement-empty-summary-and-low-stock.png dan test-evidence/session-72-81/UNX-S06-003/02-procurement-summary-empty-navigation.png.</t>
+  </si>
+  <si>
+    <t>Form kosong dan input invalid menahan penyimpanan tanpa membuat record. Supplier valid berhasil dibuat dan detailnya terlihat. Identitas yang sama dapat memakai Party yang sudah ada tanpa duplikasi; NPWP yang sama tanpa konfirmasi ditolak dengan pesan yang terlihat. Pencarian kode, nama, email, telepon, dan empty state pencarian acak berfungsi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-72-81/UNX-S06-004/01-supplier-created-duplicate-reuse-search.png.</t>
+  </si>
+  <si>
+    <t>Detail supplier, edit legal name/alamat, metrik PO nol, dan ringkasan kosong berhasil terlihat. Dua kontak berhasil ditambahkan; setelah kontak kedua ditandai utama, UI menampilkan hanya kontak kedua sebagai UTAMA. Namun kartu kontak tidak menyediakan kontrol WhatsApp, catatan, edit, atau hapus yang diwajibkan, dan bagian Material Terkait menampilkan Belum ada material terkait, sehingga pemilihan preferred supplier/material dan verifikasi PO tidak dapat dilakukan. Requirement kasus tidak terpenuhi lengkap karena fitur/kondisi prasyarat tersebut tidak tersedia pada UI. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-72-81/UNX-S06-005/01-supplier-detail-zero-metrics.png dan test-evidence/session-72-81/UNX-S06-005/02-contact-primary-and-no-material-related.png.</t>
+  </si>
+  <si>
+    <t>Daftar Pemasok hanya menampilkan QA Supplier Primary SUP-000020; pemasok sekunder/reuse aktif yang menjadi target tidak tersedia. Form PO baru hanya menyediakan QA Supplier Primary. Karena target sekunder dan data PO/tagihan pembanding tidak tersedia, alur batal/konfirmasi nonaktif, reaktivasi, pemeriksaan Party role lain, serta penolakan karena workflow terbuka tidak dapat dijalankan literal tanpa memakai pemasok yang salah. Expected Result tidak terpenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-82-91/UNX-S06-006/01-no-secondary-active-supplier-po-form.png.</t>
+  </si>
+  <si>
+    <t>Form Permintaan Pembelian dapat dibuka, tetapi tidak ada material QA atau jalur Low Stock dengan material. Dropdown hanya berisi Item non-material dan satuan yang tersedia bukan Gram/G; penyimpanan kosong hanya mempertahankan form tanpa membuat PR. Quantity 200 G, estimated price 150, multi-item, total 130.000, dan validasi material tidak dapat diuji karena prasyarat material 800 G/reorder 200 G tidak tersedia. Expected Result tidak terpenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-82-91/UNX-S06-007/01-no-material-low-stock-or-prerequisite.png.</t>
+  </si>
+  <si>
+    <t>Daftar Permintaan Pembelian menampilkan Belum Ada Permintaan Pembelian. PR utama Draft dan PR sekunder untuk skenario penolakan tidak tersedia, sehingga transisi Draft ke Submitted ke Approved/Rejected, dialog batal, alasan penolakan, audit, tombol Buat PO, dan kontrol lifecycle Draft tidak dapat diverifikasi lengkap. Expected Result tidak terpenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-82-91/UNX-S06-008/01-no-prerequisite-pr-list.png.</t>
+  </si>
+  <si>
+    <t>Halaman Pesanan Pembelian menampilkan Belum Ada Pesanan Pembelian. PR Approved dengan sisa item material/non-material dan fondasi supplier/material tidak tersedia, sehingga pembuatan PO parsial, batas remaining quantity, mapping item, subtotal 65.000, total 80.000, dan pembaruan PR tidak dapat dijalankan. Expected Result tidak terpenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-82-91/UNX-S06-009/01-no-approved-pr-or-po.png.</t>
+  </si>
+  <si>
+    <t>Tidak ada PR dengan sisa 100 G dan 1 PCS. Form PO langsung hanya menampilkan QA Supplier Primary dan pilihan item Non-material tanpa material aktif; karena itu PO kedua, status PR ORDERED, perlindungan over-order, serta PO langsung final tidak dapat diselesaikan sesuai langkah. Expected Result tidak terpenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-82-91/UNX-S06-010/01-no-pr-remaining-and-direct-po-form.png.</t>
+  </si>
+  <si>
+    <t>Tidak ada PO Draft yang dapat dibuka. Percobaan menyimpan form PO kosong mempertahankan form dan fokus pada pemasok wajib tanpa membuat PO. Karena tidak ada PO sumber, PDF, Send, Confirm, Cancel, audit transisi, kontrol receipt, dan verifikasi Document Center tidak dapat dilakukan. Expected Result tidak terpenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-82-91/UNX-S06-011/01-po-lifecycle-no-orders.png.</t>
+  </si>
+  <si>
+    <t>Form Terima Barang terbuka, tetapi dropdown PO hanya berisi Pilih PO dapat diterima dan tombol Simpan Penerimaan disabled. Tidak ada PO Sent/Confirmed, sehingga accepted/rejected quantity, alasan penolakan, batch, spool, stock-in, movement, dan status Partial tidak dapat diuji. Expected Result tidak terpenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-82-91/UNX-S06-012/01-no-receivable-po.png.</t>
+  </si>
+  <si>
+    <t>Daftar Penerimaan Barang menampilkan Belum Ada Penerimaan Barang. PO Partial/Confirmed, saldo stok 860 G, receipt pertama, dan remaining 40 G tidak tersedia. Karena itu penolakan over-receipt, penerimaan lanjutan, rollback, penyelesaian PO, pembatasan PO Received, dan rekonsiliasi 1.000 G tidak dapat dijalankan. Expected Result tidak terpenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-82-91/UNX-S06-013/01-no-partial-po-or-receipts.png.</t>
+  </si>
+  <si>
+    <t>Halaman Tagihan Pemasok menampilkan Belum Ada Tagihan Pemasok. Modal menyediakan pemasok QA Supplier Primary, nomor, tanggal, jatuh tempo, dan total; submit kosong mempertahankan form tanpa invoice. Invoice QA-INV-0601/open invoice, duplicate/void, AP, blokir deaktivasi supplier, dan verifikasi PO/notes/dokumen tidak dapat diselesaikan karena data sumber tidak tersedia. Expected Result tidak terpenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-82-91/UNX-S06-014/01-invoice-empty-and-fields.png.</t>
+  </si>
+  <si>
+    <t>Ringkasan Pengadaan menampilkan seluruh KPI 0/Rp0, material stok menipis 0, dan tidak ada exception. URL daftar requests rejected serta orders received menampilkan empty state. Riwayat hanya memuat event pembuatan/pembaruan supplier dan dua kontak; detail supplier menunjukkan Total PO 0, PO terbuka 0, PO diterima 0, nilai Rp0, tanpa material/PO terkait. Dataset PR/PO/receipt/invoice dan rekonsiliasi sesi tidak tersedia, sehingga Expected Result tidak terpenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-82-91/UNX-S06-015/01-procurement-summary-empty.png, 02-orders-query-received-empty.png, 03-procurement-history-limited-controls.png, dan 04-supplier-performance-zero-and-history.png.</t>
+  </si>
+  <si>
+    <t>Halaman daftar pesanan, subhalaman, pencarian, filter lanjutan, dan tombol ekspor CSV dapat diakses. Namun daftar pesanan tetap kosong, sehingga tiga order pembanding yang dipersyaratkan, hasil filter/sort/pagination berbasis data, isi CSV, dan pembandingan akun read-only tidak dapat diverifikasi secara lengkap. Expected Result tidak terpenuhi. Akun ACCOUNT #1 - Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-92-101/UNX-S07-001/01-orders-empty-filters-export.png.</t>
+  </si>
+  <si>
+    <t>Quick-create diuji dengan form kosong dan email tidak valid, lalu pelanggan valid QA Customer S07 dibuat, otomatis dipilih, ditemukan kembali setelah form dibuka ulang, dan pelanggan kedua dengan email kosong diterima. Log Audit menampilkan dua aktivitas Customer Create. Langkah dan Expected Result terpenuhi. Akun ACCOUNT #1 - Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-92-101/UNX-S07-002/02-customer-created-reused-optional.png dan test-evidence/session-92-101/UNX-S07-002/03-audit-log-customer-created.png.</t>
+  </si>
+  <si>
+    <t>Draft pertama berhasil disimpan, ditampilkan, dilanjutkan, perubahan dijaga dengan dialog unsaved changes dan tersimpan saat keluar. Draft kedua berhasil dibuang. Saat menyelesaikan draft pertama menjadi order final, UI menampilkan "Terjadi kesalahan pada server."; order final, converted lock, dan stale-reference warning tidak dapat diverifikasi. Expected Result tidak terpenuhi karena penyimpanan order final gagal. Akun ACCOUNT #1 - Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-92-101/UNX-S07-003/03-save-order-server-error.png.</t>
+  </si>
+  <si>
+    <t>Item katalog dengan varian aktif dan item custom berhasil diisi; subtotal, diskon, ongkos kirim, pajak, biaya marketplace, dan total terlihat terhitung. Validasi nilai diskon tidak mencegah nilai berlebihan pada input terformat, dan penyimpanan order menampilkan "Terjadi kesalahan pada server.", sehingga order gabungan serta price snapshot tidak terbentuk. Expected Result tidak terpenuhi karena validasi input dan penyimpanan order gagal memenuhi alur. Akun ACCOUNT #1 - Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-92-101/UNX-S07-004/01-catalog-custom-formula.png dan test-evidence/session-92-101/UNX-S07-004/02-submit-server-error.png.</t>
+  </si>
+  <si>
+    <t>Halaman Prioritas Produksi dan Kalkulasi Ulang dapat dibuka, tetapi menampilkan "Tidak Ada Pesanan Aktif"; dua order aktif dengan tenggat dan skor yang dipersyaratkan tidak tersedia sehingga pemetaan skor, recalculation, filter, sorting, dan validasi payload tidak dapat dilaksanakan lengkap. Expected Result tidak terpenuhi karena data prasyarat tidak tersedia pada frontend. Akun ACCOUNT #1 - Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-92-101/UNX-S07-005/01-priority-empty-after-recalculate.png.</t>
+  </si>
+  <si>
+    <t>Halaman Semua Pesanan menampilkan "Belum Ada Pesanan". Order A/B dan order utama yang diperlukan tidak tersedia, sehingga transisi state, pembatalan/pengembalian, histori status, edit lock, dan penolakan state invalid tidak dapat diverifikasi. Expected Result tidak terpenuhi karena fixture order yang dipersyaratkan tidak tersedia pada frontend. Akun ACCOUNT #1 - Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-92-101/UNX-S07-006/01-orders-empty-no-state-fixture.png.</t>
+  </si>
+  <si>
+    <t>Halaman Piutang Pelanggan menampilkan "Belum ada data." dan tidak ada order valid dengan total lebih dari nol; pembuatan invoice, pembayaran, posting finance, PDF, dan attachment/document center tidak dapat diuji lengkap dari frontend. Expected Result tidak terpenuhi karena order dan total valid yang dipersyaratkan tidak tersedia. Akun ACCOUNT #1 - Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-92-101/UNX-S07-007/01-receivables-empty-no-order.png.</t>
+  </si>
+  <si>
+    <t>Antrean Produksi menampilkan "Antrean Produksi Masih Kosong". Tidak tersedia order Ready dengan item produksi maupun item non-Ready untuk pembanding, sehingga enqueue, eligibility, duplicate guard, priority propagation, subset, dan edit lock tidak dapat diverifikasi. Expected Result tidak terpenuhi karena data order dan item produksi yang dipersyaratkan tidak tersedia. Akun ACCOUNT #1 - Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-92-101/UNX-S07-008/01-production-queue-empty.png.</t>
+  </si>
+  <si>
+    <t>Antrean Cetak dan Pekerjaan Cetak dapat dibuka tetapi masing-masing kosong; tidak ada queue item sebagai sumber print job, sehingga validasi remaining quantity, printer/operator/profile/design dan auto-ready tidak dapat dilaksanakan. Expected Result tidak terpenuhi karena queue item yang dipersyaratkan tidak tersedia. Akun ACCOUNT #1 - Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-92-101/UNX-S07-009/01-print-jobs-empty-no-queue.png.</t>
+  </si>
+  <si>
+    <t>Inventaris Material menampilkan "Belum Ada Filament" dan tidak ada stok/batch material; job Queued/Ready juga tidak tersedia, sehingga planning, unit conversion, reservation, replan, insufficient stock, auto batch, invalid batch, concurrency, dan kontrol konsumsi Finish tidak dapat diuji. Expected Result tidak terpenuhi karena material, batch, dan job yang dipersyaratkan tidak tersedia pada frontend. Akun ACCOUNT #1 - Insinyur 3D, workspace Uni-Inside Craft. Bukti: test-evidence/session-92-101/UNX-S07-010/01-material-inventory-empty.png.</t>
+  </si>
+  <si>
+    <t>Pass: Metode valid dibuat, duplicate, edit immutable, usage nol, deactivation/activation, filter, dan persistensi reload diverifikasi melalui UI. Fixture aktif. Akun ACCOUNT #4 â€” CTO, workspace Craft. Bukti: test-evidence/session-42-51/UNX-S03-011/04-invalid-rejected.png dan 05-final-active.png.
+[QA produksi session 42–51]
+Produksi QA (ACCOUNT #4 — CTO, workspace Craft): CRUD Metode Pembayaran, validasi kode/nama, duplicate, edit dengan kode terkunci, usage nol, filter Nonaktif, pembatalan/konfirmasi lifecycle, reaktivasi, dan persistensi setelah reload selesai melalui UI. Hasil yang terlihat memenuhi Expected Result. Bukti: test-evidence/session-42-51/UNX-S03-011/01-invalid-rejected.png dan 06-final-active.png.</t>
+  </si>
+  <si>
+    <t>Pass: Hierarki kategori, edit parent, pencegahan cycle/self-parent, proteksi active child, usage, lifecycle, dan persistensi reload diverifikasi melalui UI. Fixture aktif. Akun ACCOUNT #4 â€” CTO, workspace Craft. Bukti: test-evidence/session-42-51/UNX-S03-012/03-root-deactivate-protected.png dan 05-final-active-hierarchy.png.
+[QA produksi session 42–51]
+Produksi QA (ACCOUNT #4 — CTO, workspace Craft): root dan child Kategori Produk Craft dibuat, parent attach/detach, edit parent, pencegahan self-parent/cycle, perlindungan root saat child aktif, usage, filter Nonaktif, deactivation/activation, dan persistensi selesai melalui UI. Hasil yang terlihat memenuhi Expected Result. Bukti: test-evidence/session-42-51/UNX-S03-012/01-cycle-rejected.png dan 05-final-active-hierarchy.png.</t>
+  </si>
+  <si>
+    <t>Pass: Enum/default, validasi, duplicate, CRUD immutable, usage, lifecycle, filter, reload, dan ketersediaan kategori aktif pada form Material diverifikasi melalui UI. Fixture aktif. Akun ACCOUNT #4 â€” CTO, workspace Craft. Bukti: test-evidence/session-42-51/UNX-S03-013/05-active-category-available.png.
+[QA produksi session 42–51]
+Produksi QA (ACCOUNT #4 — CTO, workspace Craft): CRUD Kategori Material, enum/default, validasi kode/nama, duplicate, edit tipe menjadi resin, reload, usage nol, lifecycle aktif/nonaktif, filter, dan pengecualian kategori nonaktif dari formulir Material selesai melalui UI. Hasil yang terlihat memenuhi Expected Result. Bukti: test-evidence/session-42-51/UNX-S03-013/03-duplicate-rejected.png dan 07-nonactive-category-omitted.png.</t>
+  </si>
+  <si>
+    <t>Bug/Failed: Setelah channel dinonaktifkan, dropdown Kanal pada form Pemetaan Produk masih menawarkan channel nonaktif. Expected Result mewajibkan channel nonaktif tidak ditawarkan; validasi, CRUD, usage, filter, lifecycle, dan aktivasi lain berhasil. Akun ACCOUNT #4 â€” CTO, workspace Craft. Bukti: test-evidence/session-42-51/UNX-S03-014/03-nonactive-channel.png, 04-nonactive-offered-mapping.png, dan 05-final-active.png.
+[QA produksi session 42–51]
+Produksi QA (ACCOUNT #4 — CTO, workspace Craft): CRUD Sales Channel, validasi URL, duplicate, edit dengan URL kosong, reload, usage nol, lifecycle, dan filter selesai. Namun setelah channel dinonaktifkan, Channel Edit 091504 tetap muncul pada opsi Kanal di Pemetaan Produk; Expected Result mensyaratkan channel nonaktif tidak ditawarkan untuk mapping. Hasil: Bug/Failed. Bukti: test-evidence/session-42-51/UNX-S03-014/04-nonactive-channel.png dan 05-nonactive-offered-mapping.png.</t>
+  </si>
+  <si>
+    <t>Pass: CRUD, edit immutable, usage, lifecycle, filter, reload, dan ketersediaan kategori layanan aktif/nonaktif diverifikasi. Akun pembanding tidak melihat dataset Kategori Layanan; fixture CTO aktif. Akun ACCOUNT #4 â€” CTO dan ACCOUNT #1 â€” Insinyur 3D. Bukti: test-evidence/session-42-51/UNX-S03-015/03-nonactive-service.png, 04-engineer-no-service-category.png, dan 05-final-active.png.
+[QA produksi session 42–51]
+Produksi QA (ACCOUNT #4 — CTO, workspace Studio): CRUD Kategori Layanan Studio, validasi, duplicate, edit, reload, usage, lifecycle, dan pengecualian kategori nonaktif dari formulir Layanan selesai. ACCOUNT #1 — ENGINEER_3D tidak melihat kartu Kategori Layanan pada Data Master; ACCOUNT #4 — CTO mengembalikan fixture ke Aktif. Hasil memenuhi Expected Result. Bukti: test-evidence/session-42-51/UNX-S03-015/06-nonactive-category-disabled.png dan 08-engineer-no-service-category.png.</t>
+  </si>
+  <si>
+    <t>Bug/Failed: Filter status, tipe, scope, kombinasi, dan reset dapat digunakan, tetapi CRAFT_SALES, CRAFT_MATERIAL, STUDIO_PROJECT, dan STUDIO_PROJECT_COST tidak ditemukan pada frontend. Karena data inti tidak tersedia, detail dan proteksi data inti tidak dapat diverifikasi. ACCOUNT #1 â€” Insinyur 3D juga hanya melihat scope Craft/Studio tanpa Shared dan tanpa kontrol kelola. Akun ACCOUNT #4 â€” CTO dan ACCOUNT #1 â€” Insinyur 3D. Bukti: test-evidence/session-42-51/UNX-S04-001/01-filters-pendapatan-craft.png, 02-filters-pengeluaran-studio.png, 03-cto-finance-dataset-empty.png, dan 04-engineer-finance-scope.png.
+[QA produksi session 42–51]
+Produksi QA (ACCOUNT #4 — CTO serta ACCOUNT #1 — ENGINEER_3D, workspace Craft): filter tipe/scope dan reset selesai; tampilan ENGINEER_3D terbatas pada domainnya dan tidak menampilkan scope Shared. Namun pencarian UI CTO untuk CRAFT_SALES, CRAFT_MATERIAL, STUDIO_PROJECT, dan STUDIO_PROJECT_COST tidak menghasilkan data, sehingga data inti dan proteksi yang diwajibkan tidak dapat dibuktikan. Hasil: Bug/Failed. Bukti: test-evidence/session-42-51/UNX-S04-001/02-cto-finance-core-search-empty.png dan 04-engineer-finance-scope.png.</t>
+  </si>
+  <si>
+    <t>Pass: Form Kategori Transaksi memuat field dan scope/tipe/COA; validasi, create, duplicate, edit dengan code/scope/tipe terkunci, COA, usage nol, filter nonaktif, batal/konfirmasi lifecycle, omit dari form baru, aktivasi, dan reload berhasil. Akun ACCOUNT #4 â€” CTO, workspace Craft. Bukti: test-evidence/session-42-51/UNX-S04-002/01-created-edited-coa-nonactive-filter.png, 02-income-nonactive-omitted.png, 03-expense-nonactive-omitted.png, 04-budget-nonactive-omitted.png, dan 05-final-active-reload.png.
+[QA produksi session 42–51]
+Produksi QA (ACCOUNT #4 — CTO, workspace Craft): CRUD, duplicate, edit field yang diizinkan, COA yang tersedia, usage, lifecycle, filter riwayat, dan pengecualian kategori nonaktif dari Pendapatan/Pengeluaran/Anggaran selesai. Namun kode 61 karakter diterima, dipotong menjadi 60 karakter, lalu record dibuat; Expected Result mensyaratkan penolakan tanpa partial create. Opsi COA alternatif yang terlihat juga tidak memiliki label scope sehingga sublangkah COA lintas-scope tidak dapat dibuktikan dari UI. Hasil: Bug/Failed. Bukti: test-evidence/session-42-51/UNX-S04-002/02-code-over-60-created.png dan 07-income-nonactive-omitted.png.</t>
+  </si>
+  <si>
+    <t>Bug/Failed: Data valid dan deteksi duplikat NPWP berjalan; Kembali tidak membuat record dan Tetap Buat Baru membuat CUS-000016. Namun validasi Nama lebih dari 200 karakter membuat CUS-000017, Negara 3 karakter membuat CUS-000018, dan Catatan lebih dari 10.000 karakter membuat CUS-000019. Record invalid tersebut dinonaktifkan melalui UI setelah bukti diambil. Expected Result yang mewajibkan penolakan input invalid dan tidak adanya partial record tidak terpenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Craft. Bukti: test-evidence/session-42-51/UNX-S04-003/06-name-over-200-created.png, 10-invalid-country-created.png, 11-invalid-note-result.png, dan 12-invalid-note-deactivated.png.
+[QA produksi session 42–51]
+Produksi QA (ACCOUNT #1 — ENGINEER_3D, workspace Craft): validasi nama kosong, email, telepon, dan website tertolak; deteksi duplikat, Kembali, Tetap Buat Baru, detail, reload, dan daftar dua record selesai. Namun nama lebih dari 200 karakter dan catatan lebih dari 10.000 karakter tetap membuat record parsial, serta Country IDN diterima lalu dinormalisasi menjadi ID; ketiganya bertentangan dengan validasi yang diharapkan. Record invalid dinonaktifkan melalui UI. Hasil: Bug/Failed. Bukti: test-evidence/session-42-51/UNX-S04-003/02-name-over-200-created.png, 06-country-accepted.png, dan 07-note-over-10000-result.png.</t>
+  </si>
+  <si>
+    <t>Pass: Detail, metrik nol, tab Ringkasan/Kontak/Pesanan/Keuangan, prefill Pesanan Baru tanpa penyimpanan, edit lengkap Display Name/email/telepon/tipe/alamat/catatan, reload, dan kode CUS-000015 tetap berhasil. Email/website/negara invalid ditolak. Nonaktifkan batal/konfirmasi, pelanggan tidak muncul pada pilihan Pesanan Baru, lalu aktivasi kembali berhasil. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Craft. Bukti: test-evidence/session-42-51/UNX-S04-004/03-customer-full-edit-persisted.png, 04-invalid-edit-rejected.png, 05-customer-deactivated.png, 06-deactivated-absent-from-new-order.png, dan 07-customer-re-activated.png.
+[QA produksi session 42–51]
+Produksi QA (ACCOUNT #1 — ENGINEER_3D, workspace Craft): detail, metrik, tab Kontak/Pesanan/Keuangan kosong, Pesanan Baru dengan customer prefilled, edit, persistensi, code tetap, pembatalan/konfirmasi nonaktif, pengecualian customer nonaktif dari Pesanan Baru, dan reaktivasi selesai. Pada edit, Country IDN diterima dan disimpan sebagai ID, padahal country tiga karakter harus ditolak; validasi edit tidak memenuhi Expected Result. Hasil: Bug/Failed. Bukti: test-evidence/session-42-51/UNX-S04-004/06-edit-persisted.png, 07-invalid-edit-country-accepted.png, dan 10-deactivated-absent-from-new-order.png.</t>
+  </si>
+  <si>
+    <t>Bug/Failed: Empty state, validasi form kontak tanpa partial contact, create A/B, pengalihan kontak utama, edit/reload, batal hapus, konfirmasi hapus B, dan refleksi A pada Ringkasan berhasil. Hanya satu kontak menjadi utama, tetapi indikator kartu kontak utama tampil sebagai MITRA, bukan penanda utama yang sesuai. Expected Result tidak sepenuhnya terpenuhi. Akun ACCOUNT #1 â€” Insinyur 3D, workspace Craft; langkah read-only kondisional tidak berlaku karena tidak ada akun read-only tersedia. Bukti: test-evidence/session-42-51/UNX-S04-005/01-invalid-contact-validation.png, 02-primary-reassigned-a.png, 03-contact-a-edited-reloaded.png, 04-contact-b-deleted-a-primary.png, dan 05-ringkasan-primary-contact.png.
+[QA produksi session 42–51]
+Produksi QA (ACCOUNT #1 — ENGINEER_3D, workspace Craft): state kosong tersedia; nama wajib, nama lebih dari 150, email invalid, telepon/WhatsApp kurang dari 3, dan catatan lebih dari 500 ditolak tanpa record parsial. Kontak A dan B dibuat, hanya satu primary aktif, primary dipindah kembali ke A, edit A bertahan setelah reload, batal hapus mempertahankan B, konfirmasi hapus menghilangkan B, dan Ringkasan menampilkan A sebagai Kontak Utama. Namun kartu kontak A sebagai primary menampilkan indikator MITRA, bukan badge/indikator Utama yang diwajibkan; hanya ketiadaan tombol Jadikan Utama dan Ringkasan yang menunjukkan statusnya. Hasil: Bug/Failed. Actor read-only tidak tersedia pada akun uji. Bukti: test-evidence/session-42-51/UNX-S04-005/01-invalid-contact-validation.png, 02-primary-reassigned-a.png, 03-contact-a-edited-reloaded.png, 04-contact-b-deleted-a-primary.png, dan 05-ringkasan-primary-contact.png.</t>
+  </si>
+  <si>
+    <t>Prasyarat tidak tersedia: Papan Produksi menampilkan “Belum Ada Pekerjaan Produksi” (Menunggu/Siap = 0) dan Kalender Produksi menampilkan “Belum Ada Jadwal Produksi”. Tidak ada job A/B untuk menjalankan langkah scheduling, konflik printer, reschedule, clear, atau sinkronisasi calendar. ACCOUNT #1 — Insinyur 3D.</t>
+  </si>
+  <si>
+    <t>Prasyarat tidak tersedia: Produksi Aktif menunjukkan Sedang Dicetak/Dijeda/Menunggu QC = 0, printer QA FDM Primary berstatus error, dan Pekerjaan Cetak menampilkan “Belum Ada Pekerjaan Cetak”. Job Ready QA Print S07 Main dan job pembanding tidak tersedia, sehingga start/pause/resume/progress serta sinkronisasi printer/queue/order tidak dapat dijalankan. ACCOUNT #1 — Insinyur 3D.</t>
+  </si>
+  <si>
+    <t>Prasyarat tidak tersedia: halaman Pekerjaan Cetak menampilkan “Belum Ada Pekerjaan Cetak”, sehingga Main job S07-013 berstatus Printing, planned material/reservation, dan printer aktif tidak tersedia. Langkah Finish, validasi actual material, konsumsi/cost, pelepasan reservation/printer, serta pending QC tidak dapat dilakukan melalui frontend. ACCOUNT #1 — Insinyur 3D.</t>
+  </si>
+  <si>
+    <t>Prasyarat tidak tersedia: halaman Cetak Gagal menampilkan “Belum Ada Cetak Gagal”, dan halaman Pekerjaan Cetak sebelumnya tidak memiliki job Ready/Printing/Paused untuk diuji. Report Failure, waste, printer issue, queue recovery, dan one-time reprint tidak dapat dijalankan melalui frontend. ACCOUNT #1 — Insinyur 3D.</t>
+  </si>
+  <si>
+    <t>Prasyarat tidak tersedia: Kontrol Kualitas menampilkan “Belum Ada Pekerjaan Menunggu QC”, sehingga main job S07-013 berstatus QC dan pending inspection tidak tersedia. Validasi Pass/Conditional/Fail, fulfilment quantity, auto-complete order, lifecycle fulfilment, dan rekonsiliasi end-to-end tidak dapat dijalankan melalui frontend. ACCOUNT #1 — Insinyur 3D.</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #1 — Insinyur 3D, seluruh 12 route Finance dapat dibuka dan heading tampil setelah menunggu pemuatan; namun URL Finance tidak dikenal tetap berada di /app/craft/finance/route-tidak-dikenal dengan area main kosong, bukan redirect ke index Finance. Route protection setelah logout mengarahkan ke /login. Pada akun pembanding ACCOUNT #5, halaman baca dapat dibuka tetapi kontrol mutasi “Tambah Akun”, “Catat Pendapatan”, “Catat Pengeluaran”, “Simpan Profil”, dan “Buat Anggaran” terlihat; “Catat Pendapatan” membuka form “Catat Pendapatan Manual”, sehingga batas read-only tidak terpenuhi. Langkah mutation langsung tidak dilakukan karena aturan sesi mewajibkan interaksi frontend saja.</t>
+  </si>
+  <si>
+    <t>Prasyarat tidak tersedia pada ACCOUNT #1 — Insinyur 3D: Ringkasan Keuangan menunjukkan Total Kas, Pemasukan Periode, Pengeluaran Periode, Arus Kas Bersih, Piutang, dan Hutang semuanya Rp 0; Transaksi Terbaru kosong; Kas &amp; Bank menampilkan “Belum Ada Akun Kas”. Tidak tersedia treasury aktif, income/expense posted, invoice customer bersaldo, atau supplier invoice bersaldo untuk rekonsiliasi, deaktifasi/reaktivasi treasury, posting, dan verifikasi perubahan KPI. Karena workflow tidak dapat dipenuhi dari data frontend yang tersedia, expected result lengkap tidak dapat disahkan.</t>
+  </si>
+  <si>
+    <t>Langkah 1 berhasil: CTA “Tambah Akun” pada Ringkasan Keuangan diklik oleh ACCOUNT #1 — Insinyur 3D. Pada langkah 2, aplikasi mengarahkan ke Kas &amp; Bank, tetapi hanya menampilkan “Belum Ada Akun Kas” dan instruksi umum; tidak ada form atau tombol create nyata. Requirement workflow pembuatan treasury tidak terpenuhi, sehingga validasi field, opening balance, account code/audit, status, dan scope tidak dapat dilanjutkan melalui frontend.</t>
+  </si>
+  <si>
+    <t>ACCOUNT #1 — Insinyur 3D membuka Finance → Piutang Pelanggan; halaman menampilkan “Belum ada data.” Tidak tersedia invoice customer Craft aktif Rp500.000 dengan balance_due Rp500.000, payment method, atau treasury bersaldo sebagai prasyarat. Karena fixture invoice tidak muncul, verifikasi partial/full payment, treasury posting, overpayment, duplicate payment, dan rekonsiliasi journal tidak dapat dilakukan dari frontend.</t>
+  </si>
+  <si>
+    <t>ACCOUNT #1 — Insinyur 3D membuka Finance → Hutang Pemasok; halaman menampilkan “Belum ada data.” Tidak tersedia supplier invoice Procurement Rp600.000, payment method, atau treasury Craft bersaldo cukup sebagai prasyarat. Karena fixture tidak tersedia, partial/full supplier payment, treasury outflow, overpayment, duplicate payment, dan rekonsiliasi Procurement/Finance tidak dapat dilakukan dari frontend.</t>
+  </si>
+  <si>
+    <t>Langkah 1-2 pada Finance &gt; Pendapatan berhasil membuka list, KPI/filter, form, dan validasi native amount 0; percobaan amount negatif juga tidak dapat diposting. Expected Result mensyaratkan pendapatan positif dengan treasury valid, kategori income aktif, deskripsi wajib, lalu satu transaksi posted Rp250.000 beserta cash-in, jurnal, audit/event, filter, pagination, dan reload konsisten. Aktual: kategori income tersedia, tetapi dropdown Akun Kas Tujuan hanya berisi Pilih akun kas tanpa treasury aktif; percobaan valid Rp250.000 dengan kategori dan deskripsi ditolak validasi UI pada treasury. Requirement posting dan verifikasi turunannya tidak terpenuhi karena prasyarat treasury tidak tersedia. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-112-121/UNX-S08-006/02-income-empty-state.png; test-evidence/session-112-121/UNX-S08-006/03-income-invalid-empty.png; test-evidence/session-112-121/UNX-S08-006/04-income-valid-attempt-no-treasury.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1-3 pada Finance &gt; Pengeluaran berhasil membuka filter/KPI/list dan modal; submit awal ditahan validasi deskripsi wajib. Expected Result mensyaratkan kategori expense aktif, order Craft valid, treasury aktif, draft Rp100.000 + pajak Rp10.000, kode EXP, referensi order, summary amount+tax, serta tidak ada cash/ledger sebelum pembayaran. Aktual: list kosong, dropdown kategori hanya berisi Pilih kategori, akun kas tidak memiliki pilihan, dan order Craft valid tidak tersedia; draft tidak dapat dibuat sehingga filter, pagination, summary, dan no-cash-before-payment tidak dapat diverifikasi. Requirement gagal karena prasyarat data Finance Craft tidak tersedia. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-112-121/UNX-S08-007/01-expense-empty-state.png; test-evidence/session-112-121/UNX-S08-007/02-expense-invalid-amount.png; test-evidence/session-112-121/UNX-S08-007/03-expense-invalid-required.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1-4 pada modal Pengeluaran berhasil menampilkan status Dibayar langsung dan checkbox konfirmasi. Expected Result mensyaratkan kategori expense aktif, treasury bersaldo cukup, konfirmasi eksplisit, lalu expense paid atomik dengan cash-out, jurnal, audit/event, rollback, dan pembanding approved. Aktual: dropdown Kategori tidak memiliki kategori valid dan Akun Kas Pembayaran hanya berisi Pilih akun kas; submit percobaan Rp75.000 ditolak validasi kategori sebelum alur direct payment dapat dijalankan. Requirement direct-paid dan approved tidak terpenuhi karena fixture kategori/treasury tidak tersedia. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-112-121/UNX-S08-008/01-direct-paid-no-prereq.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1 pada Finance &gt; Pengeluaran dijalankan dengan filter status Draf. Expected Result mensyaratkan expense draft S08-007 tersedia untuk Pay harus ditolak sebelum Approve, lalu lifecycle Draft &gt; Approved &gt; Paid, state guard, idempotensi, cash-out amount+tax, journal, audit/event, dan reload konsisten. Aktual: hasil filter Draf berjumlah 0 dan empty state tampil; expense draft S08-007 tidak tersedia sehingga seluruh lifecycle dan guard tidak dapat dijalankan. Requirement gagal karena prasyarat kasus sebelumnya tidak tersedia. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-112-121/UNX-S08-009/01-no-expense-draft.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1 pada Finance &gt; Pengeluaran dijalankan dengan filter status Dibayar. Expected Result mensyaratkan expense paid S08-009 dapat direverse dengan reason valid, mengubah status menjadi void, memulihkan treasury, membuat reversal ledger/journal/audit, mempertahankan histori, dan menolak double reversal. Aktual: hasil filter Dibayar berjumlah 0 dan empty state tampil; expense paid tidak tersedia sehingga reversal dan rekonsiliasi cash-flow/budget tidak dapat dijalankan. Requirement gagal karena prasyarat S08-009 tidak tersedia. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-112-121/UNX-S08-010/01-no-paid-expense.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1 dan filter tanggal pada Finance &gt; HPP &amp; Profitabilitas berhasil dimuat. Expected Result mensyaratkan order Completed sebagai realized revenue, direct cost aktual/estimasi dengan flag, marketplace fee, gross profit, agregasi job, scope Craft, dan summary konsisten. Aktual: KPI seluruhnya Rp0 dan empty state Belum ada pesanan terealisasi pada periode ini, termasuk setelah filter tanggal hari ini; order Completed, job actual cost, fee, dan order pipeline yang diperlukan tidak tersedia. Requirement realized revenue, profitability, estimasi, dan rekonsiliasi tidak terpenuhi karena fixture tidak tersedia. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-112-121/UNX-S08-011/01-profitability-empty.png; test-evidence/session-112-121/UNX-S08-011/02-profitability-date-filter-empty.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1-7 pada Kalkulator Biaya Produk menghasilkan formula normal yang terlihat: material Rp20.000, listrik Rp10.000, tenaga kerja Rp50.000, HPP Rp85.000, rekomendasi sekitar Rp118.056, fee sekitar Rp11.806, dan laba Rp21.250. Boundary margin/fee 100% dan 101% tetap stabil tanpa Infinity, NaN, atau crash. Namun pada langkah 10 seluruh input negatif diterima tanpa validasi/peringatan dan menghasilkan output finansial menyesatkan; pada langkah 11 klik Reset tidak mengembalikan nilai ke default 0; pada langkah 12 klik Simpan Profil tidak memberi feedback/persistensi; setelah pindah route dan kembali nilai kembali default. Expected Result mewajibkan validasi input negatif, Reset nyata, serta persistensi atau feedback jelas. Karena tiga requirement tersebut tidak terpenuhi, hasil Bug/Failed. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-112-121/UNX-S08-012/01-calculator-formula.png; test-evidence/session-112-121/UNX-S08-012/02-calculator-boundary-101.png; test-evidence/session-112-121/UNX-S08-012/03-calculator-negative-inputs.png; test-evidence/session-112-121/UNX-S08-012/04-calculator-reset-save-noop.png; test-evidence/session-112-121/UNX-S08-012/05-calculator-after-route-defaults.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1-2 pada Finance &gt; Arus Kas berhasil membuka daily/by-treasury/by-kategori dan mengisi filter from/to hari ini. Expected Result mensyaratkan transaksi posted S08 income Rp250.000, expense, reversal, net cash-flow, breakdown treasury, inclusive date filter, posted-only, scope Craft, dan rekonsiliasi treasury. Aktual: seluruh KPI Rp0, Per Hari menampilkan empty state, serta Per Akun Kas dan Per Kategori menampilkan Tidak ada data; transaksi S08 tidak tersedia. Requirement cash-in/out, reversal, filter, scope, dan rekonsiliasi tidak dapat diverifikasi karena prasyarat transaksi tidak tersedia. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-112-121/UNX-S08-013/01-cash-flow-empty.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1-2 pada Finance &gt; Anggaran berhasil membuka list dan modal buat anggaran; submit kosong ditahan validasi dan allocated amount negatif ditolak validasi native. Expected Result mensyaratkan minimal dua kategori expense aktif, budget QA Budget S08 dengan dua item kategori valid, validasi periode/duplikat/scope, lifecycle Draft &gt; Approved &gt; Active &gt; Closed, actual paid termasuk tax, reversal mengurangi actual, serta audit transisi. Aktual: list kosong dan item hanya memiliki pilihan Tanpa kategori; kategori expense aktif dan expense paid yang dipersyaratkan tidak tersedia, sehingga budget valid, lifecycle, actual, invalid transition, dan audit tidak dapat diuji. Requirement gagal karena fixture kategori/expense tidak tersedia. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-112-121/UNX-S08-014/01-budget-empty.png; test-evidence/session-112-121/UNX-S08-014/02-budget-invalid-empty.png; test-evidence/session-112-121/UNX-S08-014/03-budget-invalid-negative.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1-7 dan detail journal pada Finance &gt; Jurnal &amp; Periode berhasil dimuat untuk satu row. Expected Result mensyaratkan seluruh jurnal Finance Craft, source traceability transaksi S08, debit-credit seimbang, scope Craft, period relevan, idempotensi, dan rekonsiliasi end-to-end. Aktual: satu-satunya row yang tampil bersumber dari studio_expense_reversal pada route Craft, bukan fixture Craft S08; detail JRN-000005 seimbang Rp100.000, tetapi Periode Keuangan menampilkan belum dikonfigurasi dan transaksi/jurnal S08 tidak tersedia. Pencarian ID tidak ada menghasilkan data kosong. Requirement scope Craft dan rekonsiliasi tidak terpenuhi; data lintas unit tampak pada halaman Craft. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-112-121/UNX-S08-015/01-accounting-studio-journal-in-craft.png; test-evidence/session-112-121/UNX-S08-015/02-accounting-search-empty.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1-4 pada Analytics Craft berhasil membuka dan me-refresh 11 route dengan heading yang benar, tetapi data seluruhnya kosong. Pada langkah 5, URL liar /app/craft/analytics/unknown-route-qa tetap menampilkan URL tersebut dengan main blank dan workspace berpindah ke Studio, bukan kembali ke Analytics index. Langkah 6 berhasil meminta login saat deep-link setelah logout. Pada langkah 7, akun pembanding #5 - Staf Spesialis tidak menampilkan Analytics pada sidebar awal, tetapi direct-link /app/craft/analytics tetap menampilkan Ringkasan Analitik dan menu Analytics, sehingga pembatasan akses yang diharapkan tidak terpenuhi. Verifikasi request backend dan manipulasi query tidak dilakukan karena sesi ini wajib frontend-only. Expected Result tentang routing unknown, pembatasan permission, dan scope tidak sepenuhnya terpenuhi. Akun utama #1 - Insinyur 3D dan akun pembanding #5 - Staf Spesialis. Bukti: test-evidence/session-122-131/UNX-S09-001/01-analytics-unknown-route-blank.png; test-evidence/session-122-131/UNX-S09-001/02-analytics-overview-empty.png; test-evidence/session-122-131/UNX-S09-001/03-analytics-sales-route-format.png; test-evidence/session-122-131/UNX-S09-001/04-deeplink-login-required.png; test-evidence/session-122-131/UNX-S09-001/05-analytics-printers-empty.png; test-evidence/session-122-131/UNX-S09-001/06-analytics-materials-empty.png; test-evidence/session-122-131/UNX-S09-001/07-analytics-procurement-empty.png; test-evidence/session-122-131/UNX-S09-001/08-comparison-account-analytics-visible.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1-5 membuka Overview; halaman menampilkan KPI 0 dan empty state tetapi tidak menyediakan kontrol rentang tanggal atau period filter. Network yang terlihat dari pemuatan UI menggunakan overview tanpa query filter. Expected Result mensyaratkan default 30 hari, filter inklusif, serta data tanggal yang dapat dikontrol pengguna. Langkah validasi request tanggal salah tidak dijalankan karena frontend-only dan UI tidak menyediakan input untuk mengirim filter tersebut. Requirement kontrol periode UI tidak tersedia, sehingga tanggal default dan rekonsiliasi range tidak dapat dibuktikan dari frontend. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-122-131/UNX-S09-002/01-overview-no-date-filter.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1 membuka Ringkasan Analitik. UI menampilkan Jumlah Pesanan 0, Nilai Pesanan Rp0, Kas Diterima Rp0, Material Terpakai 0.00 g, Print Success Rate -, serta empty state pada Produk Teratas dan Tren Nilai Pesanan. Expected Result membutuhkan order valid, cancelled/returned, customer payment posted, income non-customer, dan print job completed/failed untuk rekonsiliasi lima KPI, exclusion, generated time, dan consistency antarmodul. Fixture order/payment/print job tidak tersedia, sehingga seluruh rekonsiliasi dan status exclusion tidak dapat diverifikasi. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-122-131/UNX-S09-003/01-overview-kpi-empty.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1-3 membuka Overview dan memeriksa Tren Nilai Pesanan serta Produk Teratas. Kedua bagian menampilkan empty state. Expected Result membutuhkan minimal enam item/order, custom item, order cancelled/returned, sorting value descending, fallback label, dan perubahan ranking setelah reload. Tidak ada data fixture sehingga trend harian, Top 5, grouping, fallback, exclusion, dan sorting tidak dapat diverifikasi. Requirement tidak terpenuhi karena data kasus tidak tersedia. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-122-131/UNX-S09-004/01-overview-trend-top-empty.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1-4 membuka Analytics &gt; Penjualan. Halaman menampilkan Rincian Penjualan empty state; KPI terlihat order count Rp0, order value 0.00, dan AOV 0.000000. Expected Result mensyaratkan order eksternal valid, internal/cancelled/returned exclusion, dua channel, label Tanpa Kanal, AOV matematis, channel totals yang konsisten, serta format count bukan currency dan value/AOV sebagai currency. Fixture order/channel tidak tersedia dan format KPI yang terlihat tidak sesuai unit. Requirement agregasi, exclusion, rekonsiliasi, dan format tidak terpenuhi. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-122-131/UNX-S09-005/01-sales-empty-format.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1-5 membuka Analytics &gt; Pesanan. Summary created, completed, cancelled, returned, dan critical seluruhnya 0; rincian menampilkan empty state. Nilai created terlihat Rp0 meskipun expected count harus berupa jumlah. Expected Result membutuhkan beberapa status order dan priority_code critical untuk rekonsiliasi distribusi, completed/cancelled/returned, mapping critical, date range, serta scope Craft. Fixture order/status/priority tidak tersedia dan unit created salah, sehingga requirement tidak terpenuhi. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-122-131/UNX-S09-006/01-orders-overview-empty.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1-4 membuka Analytics &gt; Produk. Halaman menampilkan Rincian Produk empty state. Expected Result membutuhkan product_id yang berulang, custom item dengan nama berbeda, fallback label, exclusion cancelled/returned, sorting value, rekonsiliasi line_total, perubahan nama master, dan scope Craft. Fixture order item/product tidak tersedia sehingga agregasi, grouping, fallback, exclusion, sorting, dan rekonsiliasi tidak dapat dilakukan. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-122-131/UNX-S09-007/01-products-empty.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1-4 membuka Analytics &gt; Kanal Penjualan. Halaman menampilkan Rincian Kanal Penjualan empty state. Expected Result membutuhkan order valid dengan dua channel, order tanpa channel, internal/cancelled/returned, konsistensi totals terhadap Sales, LEFT JOIN historical channel, filter tanggal, dan scope Craft. Fixture order/channel tidak tersedia, sehingga label Tanpa Kanal, agregasi, delta definisi, filter, dan scope tidak dapat diverifikasi. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-122-131/UNX-S09-008/01-channels-empty.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1-4 membuka Analytics &gt; Pelanggan &amp; Mitra. Halaman menampilkan Rincian Pelanggan &amp; Mitra empty state. Expected Result membutuhkan pelanggan dengan frekuensi order berbeda, exclusion status, sorting value, perubahan display_name, filter tanggal, satu row per party, dan scope Craft. Fixture customer/order tidak tersedia sehingga agregasi, sorting, status comparison, filter, dan scope tidak dapat diverifikasi. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-122-131/UNX-S09-009/01-customers-empty.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1-6 membuka Analytics &gt; Produksi. Summary menampilkan jobs created 0, jobs completed 0, jobs failed 0, print minutes 0, material consumed 0.000, recorded cost 0.00, success rate -, dan print hours Rp0; rincian menampilkan empty state. Expected Result membutuhkan print job completed/failed/queued/in_progress, printer assigned/unassigned, actual minutes/material/cost, attribution finished_at/created_at, status totals, printer breakdown, trend, dan unit yang benar. Fixture production/printer/material/job tidak tersedia; selain itu jobs created dan print hours terlihat menggunakan format Rupiah yang tidak sesuai. Requirement rekonsiliasi, success rate, attribution, breakdown, dan format tidak terpenuhi. Akun #1 - Insinyur 3D. Bukti: test-evidence/session-122-131/UNX-S09-010/01-production-empty-format.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah membuka Laporan &amp; Analitik &gt; Printer dengan ACCOUNT #1 â€” Insinyur 3D di workspace Craft, halaman menampilkan Rincian Printer dan pesan "Belum ada data untuk periode ini." Expected Result meminta rekonsiliasi dua printer dan satu job tanpa printer, konsistensi jam/jumlah job, periode dan scope, pengurutan, nilai berupa jam bukan uang, serta null/0 sebagai 0. Actual: tidak ada printer atau job yang terlihat sehingga seluruh pemeriksaan tersebut tidak dapat dilakukan; prasyarat data kasus tidak tersedia di frontend. Requirement tidak terpenuhi karena data dan verifikasi analitik yang diwajibkan tidak tersedia. Bukti: test-evidence/session-132-141/UNX-S09-011/01-printer-empty.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah membuka Laporan &amp; Analitik &gt; Material dengan ACCOUNT #1 â€” Insinyur 3D di workspace Craft, halaman menampilkan Rincian Material dan pesan "Belum ada data untuk periode ini." Expected Result meminta rekonsiliasi production_usage/waste dan tipe movement lain, batas occurred_at, pengurutan, baris waste-only, unit/label material dan scope. Actual: tidak ada movement material yang terlihat sehingga rekonsiliasi, pengecualian tipe, batas tanggal, sorting, unit, dan scope tidak dapat diverifikasi; prasyarat data kasus tidak tersedia di frontend. Requirement tidak terpenuhi. Bukti: test-evidence/session-132-141/UNX-S09-012/01-material-empty.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah membuka Laporan &amp; Analitik &gt; Pengadaan dengan ACCOUNT #1 â€” Insinyur 3D di workspace Craft, halaman hanya menampilkan Rincian Pengadaan dan pesan "Belum ada data untuk periode ini." Expected Result meminta beberapa PO dari supplier/status/tanggal berbeda, rekonsiliasi jumlah/nilai per supplier, batas tanggal, makna status termasuk draft/cancelled, duplikasi/empty, dan scope. Actual: tidak ada PO atau supplier yang terlihat sehingga seluruh rekonsiliasi dan pemeriksaan status/tanggal/scope tidak dapat dilakukan; prasyarat data kasus tidak tersedia di frontend. Requirement tidak terpenuhi. Bukti: test-evidence/session-132-141/UNX-S09-013/01-procurement-empty.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah membuka Laporan &amp; Analitik &gt; Profitabilitas dengan ACCOUNT #1 â€” Insinyur 3D di workspace Craft, KPI terlihat bernilai Rp 0 untuk order/revenue/cost/production cost/gross profit, gross margin ditampilkan "â€”", dan Rincian Profitabilitas menampilkan "Belum ada data untuk periode ini." Expected Result meminta verifikasi income/expense posted, reversal finance, actual_cost job, gross profit/margin, pengecualian unposted/void/foreign, dan format margin. Actual: tidak ada data finance atau production yang terlihat sehingga rekonsiliasi reversal, actual cost, exclusion, dan scope tidak dapat dilakukan; hanya tampilan zero/garis yang dapat diamati. Requirement tidak terpenuhi karena fixture data dan bukti perhitungan yang diwajibkan tidak tersedia. Bukti: test-evidence/session-132-141/UNX-S09-014/01-profitability-empty.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah membuka Pusat Laporan dengan ACCOUNT #1 â€” Insinyur 3D dan membandingkan melalui ACCOUNT #5 â€” Staf Spesialis, kedua tampilan menampilkan Laporan Tersedia 0 dan "Tidak ada laporan yang sesuai atau dapat diakses", serta riwayat ekspor kosong. Expected Result meminta 11 laporan Craft Analytics, source/default period, preview konsisten, ekspor CSV/XLSX/PDF, riwayat, comparison read-only tanpa export, validasi report/format/range, dan isolasi Studio. Actual: registry laporan kosong sehingga preview, ekspor, riwayat, invalid input, batas range, dan permission separation tidak dapat diuji. Requirement tidak terpenuhi karena laporan yang diwajibkan tidak tersedia pada frontend. Bukti: test-evidence/session-132-141/UNX-S09-015/01-reports-empty-main-account.png; test-evidence/session-132-141/UNX-S09-015/02-reports-empty-comparison.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah Marketplace &amp; Kanal Penjualan dengan ACCOUNT #1 â€” Insinyur 3D di workspace Craft, kanal Marketplace valid berhasil dibuat, diedit, dinonaktifkan, dan diaktifkan kembali; validasi nama kosong, URL ftp, dan kode duplikat menolak input. Namun kode lowercase/spasi "qa bad" diterima dan dinormalisasi menjadi QA_BAD, padahal Expected Result mengharuskan kode lowercase/spasi ditolak. Selain itu tabel menunjukkan 0 pesanan, API belum dikonfigurasi, dan settlement/pemetaan tidak memiliki fixture sehingga KPI/detail, status order, API, settlement, dan mapping tidak dapat direkonsiliasi. Saat diuji dengan ACCOUNT #5 â€” Staf Spesialis, kontrol Tambah Kanal, Edit, dan Nonaktifkan tetap terlihat pada halaman read-only, sehingga pemisahan read/write juga tidak terpenuhi. Bukti: test-evidence/session-132-141/UNX-S10-001/01-marketplace-readonly-write-controls-visible.png; test-evidence/session-132-141/UNX-S10-001/02-marketplace-main-table.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah Pemetaan Produk dengan ACCOUNT #1 â€” Insinyur 3D di workspace Craft, pemetaan SKU valid berhasil dibuat dan dihapus; URL ftp ditolak dengan pesan "Data marketplace tidak valid.", SKU kosong tertahan oleh validasi required, duplikasi SKU pada kanal yang sama ditolak, dan SKU yang sama pada kanal berbeda dapat dibuat. Expected Result juga meminta verifikasi variant, referensi foreign invalid, status sync, import resolver, audit, dan scope. Actual: alur sinkronisasi/import resolver, referensi foreign invalid, audit/scope, serta pemetaan variant tidak dapat seluruhnya diverifikasi dari UI/data yang tersedia. Requirement tidak terpenuhi secara lengkap. Bukti: test-evidence/session-132-141/UNX-S10-002/01-product-mapping-result.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah Aturan Biaya Marketplace dengan ACCOUNT #1 â€” Insinyur 3D, aturan persentase 6%, tetap Rp 2.000, dan campuran 3% + Rp 1.000 berhasil dibuat; input tarif 101% dan tanggal berakhir sebelum mulai ditolak dengan pesan "Data marketplace tidak valid.", dan satu aturan berhasil dinonaktifkan. Expected Result juga meminta verifikasi inactive/overlap/boundary, formula estimate pada order marketplace, penggunaan formula yang sama pada Order form, tanpa double-count, dan blokir mutasi read-only. Actual: tidak ada order marketplace atau form order dengan data biaya yang terlihat, sehingga estimasi, formula end-to-end, snapshot historis, double-count, dan kontrol read-only tidak dapat diverifikasi. Requirement tidak terpenuhi secara lengkap. Bukti: test-evidence/session-132-141/UNX-S10-003/01-fee-rules-final.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah Impor Pesanan dengan ACCOUNT #1 â€” Insinyur 3D, template CSV dapat diunduh, file .txt ditolak dengan pesan "Jenis file tidak didukung untuk unggahan ini.", dan CSV kanonik valid menghasilkan pemetaan kolom otomatis, ringkasan 1 order/1 baris/1 valid, resolusi produk terpetakan, parsing tanggal dan nominal, serta pengelompokan dua baris pada satu order. Namun ketika template yang diunduh dipreview, frontend menampilkan "Header kolom tidak ditemukan." Expected Result juga mencakup XLSX, alias header, batas ukuran/jumlah baris, mapping JSON, duplicate/resolution lengkap, token expiry/cancel, dan foreign scope. Actual: template bawaan gagal dipreview dan sub-langkah cakupan tersebut tidak dapat seluruhnya diverifikasi dari UI yang tersedia. Requirement tidak terpenuhi. Bukti: test-evidence/session-132-141/UNX-S10-004/01-import-template-preview-error.png; test-evidence/session-132-141/UNX-S10-004/02-import-valid-preview.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah Konfirmasi Impor dengan ACCOUNT #1 â€” Insinyur 3D setelah preview CSV valid yang berstatus "Siap Diimpor", frontend menampilkan "Impor selesai. 0 pesanan berhasil dibuat, 0 duplikat, 1 gagal." Expected Result meminta customer/product resolution, penyimpanan mapping, pembuatan canonical order, rekonsiliasi nilai, deduplikasi/token reuse, atomic transaction, dan audit. Actual: tidak ada pesanan yang berhasil dibuat dan satu baris gagal meskipun preview menyatakan siap diimpor, sehingga commit dan requirement terkait tidak terpenuhi. Bukti: test-evidence/session-132-141/UNX-S10-005/01-import-commit-result.png.</t>
+  </si>
+  <si>
+    <t>Langkah uji dijalankan pada Marketplace &gt; Integrasi Marketplace dengan ACCOUNT #1 â€” Insinyur 3D (ENGINEER_3D). UI berhasil membuat integrasi Manual Import dan API unsupported; hasil yang terlihat adalah â€œBelum Terhubungâ€, â€œAPI Belum Dikonfigurasiâ€, â€œDirencanakanâ€, serta â€œConnector API belum dikonfigurasiâ€, dan aksi nonaktifkan dapat dilakukan. Namun UI tidak menyediakan config_json/field secret-key, tombol Test Connection, validasi kanal/order foreign, atau verifikasi is_integrated dan pembatasan sync akun read-only. Expected Result tentang penolakan secret, koneksi unsupported yang jujur, dan seluruh validasi integrasi tidak dapat dipenuhi secara lengkap karena aksi UI yang diperlukan tidak tersedia. Status Bug/Failed. Bukti: test-evidence/session-142-151/UNX-S10-006/01-marketplace-integrations.png; test-evidence/session-142-151/UNX-S10-006/02-integration-disabled.png.</t>
+  </si>
+  <si>
+    <t>Langkah uji dijalankan pada Riwayat Sinkronisasi dan Ringkasan Otomasi dengan ACCOUNT #1 â€” Insinyur 3D (ENGINEER_3D). Halaman Riwayat Sinkronisasi menampilkan â€œBelum Ada Riwayat Sinkronisasiâ€ dan â€œTidak ada sync API karena connector belum dikonfigurasiâ€, tetapi tidak menyediakan tombol sync, pemilihan integrasi, detail hasil, atau kontrol permission/read-only. Ringkasan Otomasi juga menampilkan 0 aturan, 0 eksekusi, dan belum ada eksekusi. Akibatnya sync unsupported, foreign ID, idempotensi, history scope, dan dependency automation tidak dapat dijalankan serta tidak dapat dibuktikan lengkap dari frontend; fitur/aksi UI yang diperlukan tidak tersedia. Status Bug/Failed. Bukti: test-evidence/session-142-151/UNX-S10-007/01-sync-history-empty.png; test-evidence/session-142-151/UNX-S10-007/02-automation-empty.png.</t>
+  </si>
+  <si>
+    <t>Langkah uji dijalankan pada Settlement Marketplace dengan ACCOUNT #1 â€” Insinyur 3D (ENGINEER_3D). Halaman awal menampilkan â€œBelum Ada Settlementâ€. Pada form Tambah Settlement dipilih kanal Craft dan dimasukkan gross 100, platform fees 10, serta net 95; saat disimpan, UI menampilkan â€œData marketplace tidak valid.â€ dan tidak membuat settlement. Penolakan terlihat, tetapi pesan tidak menyatakan validasi formula secara spesifik. Tidak tersedia data order/treasury/finance yang diperlukan dan tidak ada hasil UI untuk auto-match, manual match, receive sekali, posting finance, reconcile, atau perubahan KPI. Expected Result end-to-end settlement tidak terpenuhi karena prerequisite dan aksi UI terkait tidak tersedia. Status Bug/Failed. Bukti: test-evidence/session-142-151/UNX-S10-008/01-settlement-empty.png; test-evidence/session-142-151/UNX-S10-008/02-settlement-formula-rejected.png.</t>
+  </si>
+  <si>
+    <t>Langkah uji dijalankan pada Overview, Catalog, Events, Templates, Runs, dan Rules dengan ACCOUNT #1 â€” Insinyur 3D (ENGINEER_3D). Catalog menampilkan trigger/action Craft dan Events menampilkan event Craft, sedangkan pada saat pengujian Rules dan Runs belum memiliki data. Overview menunjukkan KPI nol dan health tanpa run. Tidak tersedia UI untuk menyiapkan serta merekonsiliasi rule/run/pending event, menguji warning event lebih dari 5 menit, membandingkan akun permission parsial, atau membuktikan pemisahan read/write/run dan seluruh scope foreign. Expected Result permission, health, scope, dan rekonsiliasi tidak dapat dipenuhi lengkap; sebagian workflow belum tersedia atau prerequisite UI tidak tersedia. Status Bug/Failed. Bukti: test-evidence/session-142-151/UNX-S10-009/01-catalog.png; test-evidence/session-142-151/UNX-S10-009/02-events.png; test-evidence/session-142-151/UNX-S10-009/03-templates.png; test-evidence/session-142-151/UNX-S10-009/04-runs-empty.png; test-evidence/session-142-151/UNX-S10-009/05-rules-empty.png.</t>
+  </si>
+  <si>
+    <t>Langkah uji dijalankan pada Template Otomasi dengan ACCOUNT #1 â€” Insinyur 3D (ENGINEER_3D). UI menampilkan 10 template dan penggunaan template notifikasi dua kali menghasilkan draft independen AUT-000002 dan AUT-000003. Template Sinkronisasi Marketplace Berkala menghasilkan draft dengan ID integrasi kosong; saat diaktifkan, UI menolak dan menampilkan â€œSinkronisasi marketplace membutuhkan integration_idâ€ dengan status tetap Draf. Penggunaan template Laporan Craft Mingguan menampilkan â€œIntegrasi export Craft belum tersedia untuk otomasiâ€. Namun UI tidak menyediakan pengujian code template tidak ada/404, konfigurasi lengkap placeholder lalu verifikasi next_run_at, permission action lintas akun, atau pembuktian source immutable secara lengkap. Expected Result tidak terpenuhi seluruhnya karena fitur/aksi UI tersebut tidak tersedia. Status Bug/Failed. Bukti: test-evidence/session-142-151/UNX-S10-010/01-template-draft.png; test-evidence/session-142-151/UNX-S10-010/02-second-independent-draft.png; test-evidence/session-142-151/UNX-S10-010/03-marketplace-placeholder-draft.png; test-evidence/session-142-151/UNX-S10-010/04-marketplace-activation-rejected.png; test-evidence/session-142-151/UNX-S10-010/05-weekly-report-rejected.png.</t>
+  </si>
+  <si>
+    <t>Langkah uji dijalankan pada Rule Builder dengan ACCOUNT #1 â€” Insinyur 3D (ENGINEER_3D). Draft valid AUT-000005 berhasil dibuat dengan event CRAFT order.status_changed, kondisi order.new_status eq ready, dan aksi notification.create. Saat priority diubah menjadi -1 lalu disimpan, halaman tetap berada di form dan tidak menampilkan pesan validasi yang terlihat. Builder yang tersedia hanya satu kondisi datar dan satu aksi; tidak tersedia editor nested all/any, pengujian jumlah actions, continue_on_error per action, trigger/event invalid buatan, atau pengujian lengkap schedule/sensor, retry, cooldown, dan permission action. Expected Result untuk menolak seluruh konfigurasi invalid dan menerapkan semua batas tidak dapat dipenuhi lengkap. Status Bug/Failed. Bukti: test-evidence/session-142-151/UNX-S10-011/01-rule-builder-invalid-priority.png; test-evidence/session-142-151/UNX-S10-011/02-valid-draft.png.</t>
+  </si>
+  <si>
+    <t>Langkah uji dijalankan pada lifecycle rule dengan ACCOUNT #1 â€” Insinyur 3D (ENGINEER_3D). AUT-000005 berhasil diaktifkan, dijeda dengan status â€œDijedaâ€, diaktifkan kembali, lalu dinonaktifkan dengan status â€œDinonaktifkanâ€. Menu tindakan juga menggandakan rule menjadi AUT-000006 dan hasil salinan dapat diedit independen. Namun tidak tersedia system rule untuk menguji read-only, tidak ada UI untuk mencabut permission/akses owner lalu memverifikasi recheck, foreign unit/organization, audit detail, atau next_run_at pada rule event yang digunakan. Expected Result lifecycle lengkap, permission recheck, system protection, audit, dan scope tidak terpenuhi seluruhnya. Status Bug/Failed. Bukti: test-evidence/session-142-151/UNX-S10-012/01-active.png; test-evidence/session-142-151/UNX-S10-012/02-lifecycle-disabled-duplicate.png; test-evidence/session-142-151/UNX-S10-012/03-duplicate-edited.png.</t>
+  </si>
+  <si>
+    <t>Langkah uji dijalankan dengan dua tab frontend Craft pada AUT-000006 menggunakan ACCOUNT #1 â€” Insinyur 3D (ENGINEER_3D). Sesi A menyimpan perubahan dan versi meningkat; saat sesi B menyimpan data lama, UI menampilkan â€œAturan telah diperbarui oleh pengguna lain. Muat ulang sebelum menyimpan.â€ Setelah sesi B dimuat ulang, perubahan dengan versi terbaru berhasil disimpan dan versi meningkat lagi. Namun UI tidak menyediakan verifikasi rule_snapshot_json/rule_version untuk run queued, perhitungan next_run_at schedule/timezone, cleanup pause/disable, invalid schedule update, atau audit/run forensik secara lengkap. Expected Result optimistic concurrency terbukti sebagian tetapi tidak terpenuhi end-to-end. Status Bug/Failed. Bukti: test-evidence/session-142-151/UNX-S10-013/01-stale-update-conflict.png; test-evidence/session-142-151/UNX-S10-013/02-latest-version.png.</t>
+  </si>
+  <si>
+    <t>Langkah uji dijalankan pada AUT-000006 dengan ACCOUNT #1 â€” Insinyur 3D (ENGINEER_3D). Tombol Uji Aturan menampilkan hasil dry_run=true, conditions_matched=false, evaluasi lengkap, would_run=false, dan peringatan bahwa rule belum aktif tanpa side effect. Rule lalu diaktifkan; Jalankan Sekarang menampilkan konfirmasi bahwa aksi akan masuk antrean worker, dan setelah dikonfirmasi run terlihat di Riwayat Eksekusi sebagai antrean lalu Dilewati. Detail run menampilkan run key, correlation ID, attempt/chain, serta reason CONDITIONS_NOT_MET. Namun UI tidak menyediakan input matched/unmatched yang dapat dikendalikan, event_id/event foreign, pengujian 409 rule nonaktif, permission action kurang, atau verifikasi side effect sukses. Expected Result dry-run dan manual-run tidak terpenuhi lengkap. Status Bug/Failed. Bukti: test-evidence/session-142-151/UNX-S10-014/01-dry-run.png; test-evidence/session-142-151/UNX-S10-014/02-manual-run-queued.png; test-evidence/session-142-151/UNX-S10-014/03-run-detail-skipped.png.</t>
+  </si>
+  <si>
+    <t>Langkah uji dijalankan pada Overview dan Riwayat Eksekusi Craft dengan ACCOUNT #1 â€” Insinyur 3D (ENGINEER_3D). Overview merekonsiliasi 1 aturan aktif dan 1 eksekusi hari ini berstatus Dilewati; Run history menampilkan run yang sama sebagai Dilewati dan kondisi false tercatat tanpa side effect. Namun builder hanya menyediakan satu aksi, rule yang diuji memiliki cooldown 0 dan retry 0, dan UI tidak menyediakan uji owner permission revocation, scope revoke, cooldown duplicate, retrySafe/backoff, continue_on_error antar aksi, chain limit, side effect domain satu-kali, atau outcome marketplace connector unsupported sebagai run worker. Expected Result worker end-to-end, retry/cooldown/security, side effect, dan evidence lintas modul tidak terpenuhi lengkap. Status Bug/Failed. Bukti: test-evidence/session-142-151/UNX-S10-015/01-overview-reconciled.png; test-evidence/session-142-151/UNX-S10-015/02-worker-run-history.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1–8, halaman Proyek dapat dimuat dan kontrol search/filter/sort tersedia; namun daftar menampilkan Belum Ada Proyek, katalog layanan kosong (filter Layanan disabled), sehingga pencarian berbasis data, intersection filter, pagination page size 24/meta, dan urutan sort tidak dapat diverifikasi. Pada langkah reset, filter kembali ke semua, tetapi kata kunci pencarian tetap tersisa sehingga kondisi awal daftar tidak sepenuhnya pulih. Langkah 9 tidak dapat dilakukan karena tidak ada card proyek. Langkah 10–11 belum dapat diverifikasi melalui UI karena diperlukan akun pembanding dan data proyek lintas unit. Expected Result tidak seluruhnya terpenuhi. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-152-161/UNX-S11-001/01-project-list.png sampai 05-reset-empty-result.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1–6 dijalankan pada daftar Proyek dan halaman Proyek Aktif. KPI yang terlihat seluruhnya 0 dan halaman Proyek Aktif menampilkan Belum Ada Proyek Aktif. Karena tidak ada proyek/milestone/deliverable, langkah boundary deadline hari ini/+7, completed_at bulan berjalan, derived progress milestone→deliverable→status, progress 100% untuk completed/paid, null tanpa rencana, serta konsistensi badge list/active/detail tidak dapat direkonsiliasi. Expected Result tidak seluruhnya dapat dibuktikan. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-152-161/UNX-S11-002/01-overview-kpi-empty.png dan 02-active-projects-empty.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1–3 dan validasi submit dijalankan melalui Proyek Baru. Form memuat field identitas, scope kustom, tim, tahapan, deliverable, dan nilai proyek; submit tanpa client menampilkan 'Klien wajib dipilih.'. Namun prasyarat client Studio valid tidak tersedia karena UI menyatakan 0 klien tersedia, katalog layanan/paket kosong dan combobox layanan disabled. Karena client valid tidak ada, create valid, kode PRJ, transaksi atomic, rollback child, subtotal/contract seed, duplicate PM membership, history, audit, dan domain event tidak dapat diuji melalui frontend. Nilai negatif yang diisi pada field angka tidak dipertahankan sebagai nilai negatif pada UI dan tampak ter-normalisasi menjadi 1, sedangkan currency 3 karakter tidak memiliki field pada form. Expected Result tidak terpenuhi sepenuhnya karena prasyarat dan bagian workflow utama tidak tersedia. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-152-161/UNX-S11-003/01-project-form-empty.png, 02-project-validation-no-client.png, dan 03-nested-fields-no-client.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1–2 dijalankan dari selector Client → Klien Baru. UI menampilkan kandidat duplicate berdasarkan nomor telepon dan menyediakan tombol Gunakan Party Ini; hal ini membuktikan kandidat relevan dapat ditampilkan. Langkah 3 dicoba dengan data client valid, tetapi klik Simpan Klien memicu dialog beforeunload dan modal tetap terbuka sehingga client baru tidak berhasil dibuat/ditampilkan sebagai client baru. Langkah 4 diisi dengan nama valid dan email 'bukan-email'; tombol simpan tetap aktif dan tidak ada pesan validasi email yang terlihat, lalu alur tidak selesai. Langkah 5 memilih Gunakan Party Ini dan selector sempat memilih QA Customer S09 — CUS-000026, tetapi flag reused tidak terlihat. Setelah pengulangan duplicate, UI kembali hanya menunjukkan 1 klien tersedia dan detail selector ter-render kosong sehingga identitas terpilih tidak dapat diverifikasi. Langkah 8–9 tentang kombinasi permission dan party organisasi lain tidak dapat diverifikasi dengan account pembanding melalui UI pada sesi ini. Langkah 10 tidak dapat diselesaikan karena alur quick-create baru gagal dan selector setelah reuse kehilangan tampilan client. Expected Result tidak terpenuhi: quick-create valid tidak selesai, email invalid tidak ditolak secara terlihat, flag reused tidak ditampilkan, dan selector tidak stabil setelah reuse. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-152-161/UNX-S11-004/01-quick-client-modal.png sampai 06-duplicate-repeat-candidate.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1–11 tidak dapat dilakukan pada Detail Proyek karena daftar Proyek melalui UI menampilkan Belum Ada Proyek dan tidak ada project ID/card yang dapat dibuka. Prasyarat project non-cancelled serta katalog service/package aktif, inactive, dan foreign unit tidak tersedia; form Proyek Baru juga menyatakan katalog layanan Studio masih kosong. Akibatnya CRUD scope, validasi line, server line_total/subtotal, snapshot harga, custom line, cancelled guard, foreign line ID, dan audit tidak dapat dipenuhi atau diverifikasi melalui frontend. Dialog Perubahan Belum Disimpan yang muncul saat meninggalkan form sebelumnya ditutup dengan pilihan Keluar Tanpa Menyimpan; tidak ada data proyek tersimpan. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-152-161/UNX-S11-005/01-no-project-for-service-scope.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1–11 tidak dapat direkonsiliasi karena UI daftar Proyek menampilkan Belum Ada Proyek; tidak ada project dengan service line, quotation, invoice, atau lock source yang bisa dibuka. Menu Keuangan terlihat tersedia, tetapi tanpa project komersial dan dokumen Billing/Finance, contract_value versus subtotal, sync eksplisit, commercial lock quotation/invoice, field operasional saat locked, UI alasan lock, dan unlock workflow tidak dapat diuji melalui frontend. Expected Result tidak terpenuhi karena seluruh prasyarat data komersial tidak tersedia. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-152-161/UNX-S11-006/01-no-project-billing-lock.png dan 02-finance-menu-no-project.png.</t>
+  </si>
+  <si>
+    <t>Pada Proyek Baru, nama proyek diisi lalu navigasi ke Semua Proyek memunculkan dialog Perubahan Belum Disimpan dengan pilihan Lanjut Mengedit dan Keluar Tanpa Menyimpan. Lanjut Mengedit mempertahankan form, sedangkan Keluar Tanpa Menyimpan membawa kembali ke daftar yang menampilkan Belum Ada Proyek. Guard perubahan yang belum disimpan terlihat berfungsi, tetapi tidak ada proyek tersimpan untuk langkah edit master, validasi client/PM, field finansial read-only, atau guard proyek Selesai/Dibatalkan. Expected Result tidak seluruhnya terpenuhi karena workflow Detail Proyek dan lock finansial tidak dapat dilakukan. Akun yang digunakan: ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-152-161/UNX-S11-007/01-unsaved-changes-guard.png, 02-unsaved-continue.png, dan 03-unsaved-leave-empty.png.</t>
+  </si>
+  <si>
+    <t>Halaman Proyek Aktif dibuka melalui frontend dan menampilkan Belum Ada Proyek Aktif; tidak ada card atau project ID yang dapat dibuka. Karena tidak ada proyek, transisi Prospek ke Disetujui/Sedang Dikerjakan/Tinjauan/Selesai/Dibatalkan, validasi alasan pembatalan, guard sebelum pembatalan, timestamp, history, audit, dan domain event tidak dapat dilakukan atau diverifikasi. Expected Result tidak terpenuhi karena data proyek lifecycle yang diperlukan tidak tersedia. Akun yang digunakan: ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-152-161/UNX-S11-008/01-no-project-lifecycle.png.</t>
+  </si>
+  <si>
+    <t>Daftar Proyek tidak memiliki proyek yang dapat dibuka ke tab Komersial atau aksi pembayaran. Ringkasan Keuangan yang dibuka melalui frontend menampilkan seluruh nilai Rp 0 dan pesan Belum ada transaksi tercatat. Tanpa proyek Selesai, invoice canonical, payment record, expense, external fee, dan asset, langkah guard Selesai ke Dibayar, pembayaran parsial/berlebih, konsistensi invoice-payment, serta ringkasan komersial tidak dapat diuji. Expected Result tidak terpenuhi karena prasyarat workflow pembayaran tidak tersedia. Akun yang digunakan: ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-152-161/UNX-S11-009/01-no-project-payment-guard.png.</t>
+  </si>
+  <si>
+    <t>Tidak ada card atau project ID pada daftar Proyek sehingga Detail Proyek dan tab Tim tidak dapat dibuka. Form Proyek Baru hanya memperlihatkan kontrol awal Project Manager dan Tambah Anggota; kontrol detail untuk assignment, allocation, upsert, rejoin, leave, serta guard akses tidak dapat dijalankan tanpa proyek tersimpan. Expected Result tidak terpenuhi karena prasyarat proyek untuk pengujian internal team tidak tersedia. Akun yang digunakan: ACCOUNT #1 â€” Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-152-161/UNX-S11-010/01-no-project-team.png.</t>
+  </si>
+  <si>
+    <t>Langkah 1–12 dijalankan sampai batas UI yang tersedia melalui menu Tahapan Proyek. Halaman dapat dibuka dan menyediakan filter Proyek, Klien, Project Manager, Status, serta rentang jatuh tempo, tetapi menampilkan Belum Ada Tahapan; tidak ada project/milestone/deliverable yang dapat dipilih. Akibatnya tambah/edit/reorder atomik, validasi duplicate/missing/foreign/subset, delete guard, ownership, cancelled-project guard, audit, dan urutan setelah reload tidak dapat diuji melalui frontend. Expected Result tidak terpenuhi karena prasyarat project dengan milestone tidak tersedia. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-162-171/UNX-S11-011/01-milestone-page-empty.png.</t>
+  </si>
+  <si>
+    <t>Halaman Tahapan Proyek dan filter status/rentang jatuh tempo diuji melalui frontend, termasuk refresh dengan status Sedang Berjalan dan rentang 2026-01-01 sampai 2026-12-31. Hasil tetap Belum Ada Tahapan. Tidak ada milestone untuk menguji matrix lifecycle, unchanged/invalid transition, reopen reason, completed_at, derived late, bucket board, filter grouping, progress, audit, atau event completion. Expected Result tidak terpenuhi karena fixture milestone yang diperlukan tidak tersedia. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-162-171/UNX-S11-012/01-milestone-board-filter-empty.png.</t>
+  </si>
+  <si>
+    <t>Daftar Proyek melalui frontend menampilkan Belum Ada Proyek sehingga Detail Proyek dan deliverable existing tidak dapat dibuka. Form Proyek Baru hanya menampilkan kontrol awal Deliverable/Tambah Deliverable; itu bukan Detail Proyek dengan milestone dan deliverable fixture yang dipersyaratkan. Karena itu CRUD deliverable, ownership milestone, validasi URL aman, lifecycle, empty-submit guard, delivered_at, audit/event, cancelled guard, dan progress tidak dapat diuji. Expected Result tidak terpenuhi karena prasyarat project dan milestone tidak tersedia. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-162-171/UNX-S11-013/01-project-list-empty-no-deliverable.png dan 02-project-form-no-detail-deliverable.png.</t>
+  </si>
+  <si>
+    <t>Pusat Dokumen dapat dibuka dan menyediakan Unggah dokumen, tetapi jumlah dokumen aktif/total adalah 0 dan tidak ada deliverable/project yang dapat dipilih. Langkah upload/replace/download deliverable, storage/document registry consistency, foreign project scope, missing-file handling, orphan cleanup, delete guard, cancelled guard, serta audit upload/delete tidak dapat dilakukan dari frontend tanpa deliverable pending dan project aktif yang menjadi prasyarat. Menggunakan Pusat Dokumen umum sebagai pengganti Detail Deliverable tidak memenuhi langkah uji. Expected Result tidak terpenuhi karena fixture deliverable/file tidak tersedia. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-162-171/UNX-S11-014/01-document-center-no-deliverable-file.png.</t>
+  </si>
+  <si>
+    <t>Tidak ada project card atau Detail Proyek yang dapat dibuka untuk menjalankan external assignment, lifecycle end, fee summary, activity, dan rekonsiliasi end-to-end. Proyek Baru hanya memperlihatkan Project Manager &amp; Tim internal; pencarian UI tidak menemukan kontrol external collaborator/vendor/freelancer/partner/talent. Karena parties, assignment, dan project fixture tidak tersedia, validasi party/role/period/fee, cancelled guard, no-auto-expense, external_fee_summary, audit/activity, dan cross-module reconciliation tidak dapat diuji. Expected Result tidak terpenuhi karena fitur/detail dan prasyarat yang dibutuhkan tidak tersedia di frontend. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-162-171/UNX-S11-015/01-project-form-no-external-collaborator.png.</t>
+  </si>
+  <si>
+    <t>Menu Keuangan yang terlihat melalui frontend hanya menyediakan Ringkasan Keuangan, Transaksi, Kas &amp; Bank, Pendapatan, Pengeluaran, Piutang Klien, Kewajiban Vendor/Freelancer, Profitabilitas Proyek, Arus Kas, Anggaran, dan Jurnal &amp; Periode. Tidak tersedia menu Penawaran &amp; Penagihan maupun route Billing yang dapat dinavigasi secara visible. Karena itu 13 route Billing, permission read/write, direct URL protection, pagination limit, foreign ID, scope STUDIO, dan tombol write tidak dapat diuji. Expected Result tidak terpenuhi karena modul/route Billing tidak tersedia pada UI yang dapat diakses. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-162-171/UNX-S12-001/01-finance-menu-no-billing.png.</t>
+  </si>
+  <si>
+    <t>Halaman yang tersedia adalah Ringkasan Keuangan umum, bukan Billing Overview. UI menampilkan seluruh KPI keuangan Rp 0, Invoice terlambat 0, Jatuh tempo 7 hari 0, dan Belum ada transaksi tercatat. Tidak ada dataset quotation/invoice/outstanding untuk memverifikasi KPI Billing, effective overdue/expiry, batas hari ini/+7, filter/grouping/pagination, card top 5, read-only derivation, atau scope STUDIO. Expected Result tidak terpenuhi karena route Billing dan fixture Billing tidak tersedia. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-162-171/UNX-S12-002/01-finance-overview-not-billing.png.</t>
+  </si>
+  <si>
+    <t>Pengaturan Studio &amp; Keuangan terlihat dan field default Masa berlaku penawaran, Jatuh tempo invoice, Interval termin pembayaran, serta Jendela segera jatuh tempo tersedia. Nilai Masa berlaku penawaran diubah dari 14 menjadi 15 melalui UI dan Simpan Studio &amp; Keuangan menampilkan status Studio &amp; Keuangan tersimpan.; setelah bukti diambil, nilai dikembalikan ke 14 melalui UI untuk mencegah state leakage. Namun route/selector Billing references tidak tersedia, project scope tidak dapat dibuka karena tidak ada project, dan validasi cancelled/foreign/inactive project/service serta penggunaan client-project context tidak dapat dilakukan. Expected Result tidak terpenuhi secara penuh karena prasyarat project/client/service dan modul Billing tidak tersedia. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-162-171/UNX-S12-003/01-settings-no-billing-references.png dan 02-studio-finance-default-saved-no-project-scope.png.</t>
+  </si>
+  <si>
+    <t>Menu Keuangan yang tersedia tidak memiliki Penawaran &amp; Penagihan atau Template Penawaran. Route yang terlihat hanya modul keuangan umum sehingga search/filter/pagination/detail/create/edit template, QTM code, item validation, active lifecycle, service scope, snapshot harga, idempotency, atomicity, dan audit template tidak dapat dijalankan melalui frontend. Expected Result tidak terpenuhi karena UI/route Billing Template tidak tersedia. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-162-171/UNX-S12-004/01-billing-template-route-missing.png.</t>
+  </si>
+  <si>
+    <t>UI Penawaran &amp; Penagihan/Billing tidak tersedia pada menu yang terlihat, sehingga form quotation, QTN code, default validity, item/discount/tax calculation, client/project/service context validation, dan atomicity tidak dapat dibuka atau disubmit. Form Proyek Baru yang dapat dibuka hanya menunjukkan Katalog Layanan Studio masih kosong, Project Manager &amp; Tim internal, dan belum ada project/quotation context; itu bukan pengganti form quotation Billing. Expected Result tidak terpenuhi karena route Billing serta prasyarat client, project, dan service aktif tidak tersedia. Akun yang digunakan: ACCOUNT #1 — Insinyur 3D, workspace Uni-Inside Studio. Bukti: test-evidence/session-162-171/UNX-S12-005/01-project-form-no-quotation-context.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah prasyarat, saya membuka workspace Uni-Inside Studio dengan ACCOUNT #1 â€” Insinyur 3D dan memeriksa menu Keuangan melalui frontend. Expected Result mensyaratkan quotation draft/sent/accepted/rejected/cancelled serta fitur edit quotation, partial PATCH, penggantian item, commercial lock, filter/sort, detail activity, dan audit. Actual yang terlihat: daftar proyek menampilkan Belum Ada Proyek dan submenu Keuangan hanya berisi Ringkasan Keuangan, Transaksi, Kas &amp; Bank, Pendapatan, Pengeluaran, Piutang Klien, Kewajiban Vendor/Freelancer, Profitabilitas Proyek, Arus Kas, Anggaran, serta Jurnal &amp; Periode; tidak tersedia menu atau UI quotation/billing sehingga quotation uji dan seluruh langkah tidak dapat dijalankan. Requirement tidak terpenuhi karena fitur dan data prasyarat tidak tersedia pada frontend akun ini; kondisi dikategorikan sebagai fitur unavailable/missing. Bukti: test-evidence/session-172-181/UNX-S12-006/01-visible-finance-menu-no-billing-route.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah prasyarat dan langkah 1, saya membuka Ringkasan Keuangan melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D pada workspace Uni-Inside Studio. Expected Result mensyaratkan quotation draft valid dan expired, transition draftâ†’sent, revalidasi, expiry guard, PDF resmi, handoff project, audit, serta event. Actual yang terlihat: halaman hanya menampilkan dashboard kas/piutang/pengeluaran bernilai Rp 0 dan pesan Belum ada transaksi tercatat; tidak ada quotation draft, detail quotation, tombol Send, atau alur PDF quotation. Requirement send quotation dan seluruh verifikasi lanjutan tidak dapat dipenuhi karena fitur/data Billing quotation unavailable pada frontend akun ini. Bukti: test-evidence/session-172-181/UNX-S12-007/01-finance-dashboard-no-quotation-send.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah prasyarat, saya membuka halaman Keuangan melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D pada workspace Uni-Inside Studio untuk mencari quotation sent/draft/accepted dan dua quotation pada project yang sama. Expected Result mensyaratkan state machine accept/reject/cancel, expiry guard, accepted uniqueness, reason guard, project handoff, audit, dan event. Actual yang terlihat: halaman hanya menampilkan ringkasan kas/piutang/pengeluaran bernilai Rp 0 dan Belum ada transaksi tercatat; tidak ada quotation, project uji, detail status, tombol Accept/Reject/Cancel, atau field reason. Requirement tidak terpenuhi karena fitur/data quotation yang diperlukan unavailable pada frontend akun ini sehingga seluruh langkah state machine tidak dapat dijalankan. Bukti: test-evidence/session-172-181/UNX-S12-008/01-no-quotation-state-machine-ui.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah prasyarat, saya membuka form Proyek Baru melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D. Expected Result mensyaratkan Duplikat quotation locked yang menghasilkan draft QTN baru, snapshot item independen, revisi, validitas, audit source_quotation_id, serta numbering unik. Actual yang terlihat: form hanya menampilkan pembuatan proyek dan pernyataan Katalog Layanan Studio masih kosong; tidak ada quotation, tombol Duplikat, QTN, atau konteks source quotation yang dapat dipilih. Requirement revisi quotation independen dan seluruh verifikasi lanjutan tidak dapat dipenuhi karena UI/data quotation unavailable. Bukti: test-evidence/session-172-181/UNX-S12-009/01-project-form-no-quotation-duplicate.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1, saya membuka Ringkasan Keuangan melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D untuk mencari detail quotation accepted dan tindakan Buat Invoice. Expected Result mensyaratkan hanya quotation accepted yang dapat dikonversi menjadi invoice draft dengan linkage quotation/project/client, snapshot item, tax, total, INV baru, dan audit/event. Actual yang terlihat: halaman hanya menampilkan metrik keuangan bernilai Rp 0, Invoice terlambat 0, Jatuh tempo 7 hari 0, serta Belum ada transaksi tercatat; tidak ada daftar/detail quotation, status accepted, atau tombol Buat Invoice. Requirement konversi dan seluruh guard tidak dapat diuji karena UI/data quotation Billing unavailable. Bukti: test-evidence/session-172-181/UNX-S12-010/01-no-accepted-quotation-invoice-action.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah prasyarat dan langkah 1, saya membuka daftar Proyek melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D untuk menyiapkan client/project dan mencari alur pembuatan invoice. Expected Result mensyaratkan invoice manual/project dengan source eligibility, INV unik, due-date default, perhitungan item tax/discount, validasi, rollback atomik, audit, dan event. Actual yang terlihat: halaman menampilkan Proyek Aktif 0, seluruh metrik proyek 0, dan Belum Ada Proyek; tidak tersedia invoice form, client/project billable, service aktif, atau tindakan create invoice. Requirement tidak terpenuhi karena data prasyarat dan UI invoice Billing unavailable sehingga langkah pembuatan dan validasi tidak dapat dijalankan. Bukti: test-evidence/session-172-181/UNX-S12-011/01-project-list-empty-no-invoice-create.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah prasyarat dan langkah 1, saya membuka Piutang Klien melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D untuk mencari invoice draft serta invoice issued/partial/paid/overdue/void. Expected Result mensyaratkan edit parsial invoice draft, validasi tanggal, item/schedule replacement atomik, commercial lock, filter/sort, balance recalculation, detail, dan audit. Actual yang terlihat: tabel hanya menampilkan header Invoice, Klien/Proyek, Jatuh tempo, Status, Sisa dan pesan Tidak ada piutang terbuka; tidak ada invoice draft/detail/form edit maupun schedule/payment. Requirement tidak terpenuhi karena data dan UI invoice Billing unavailable sehingga langkah edit dan verifikasi lanjutan tidak dapat dijalankan. Bukti: test-evidence/session-172-181/UNX-S12-012/01-receivables-no-invoice-drafts.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah prasyarat dan langkah 1, saya membuka halaman Transaksi melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D untuk mencari draft invoice, schedule, dan tindakan issue. Expected Result mensyaratkan schedule 0â€“24 baris dengan validasi, rekonsiliasi jumlah, issue invoice, official PDF, idempotensi, audit, event, dan atomicity. Actual yang terlihat: tabel hanya menampilkan header transaksi dan pesan Belum ada transaksi Studio; tidak ada invoice draft, schedule, tombol issue, status issued, atau dokumen official. Requirement payment schedule dan issue tidak dapat dipenuhi karena UI/data invoice Billing unavailable. Bukti: test-evidence/session-172-181/UNX-S12-013/01-transactions-no-invoice-issue-schedule.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah prasyarat dan langkah 1, saya membuka Piutang Klien melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D untuk mencari invoice project, accepted quotation, pembayaran, dan kontrol void. Expected Result mensyaratkan commercial basis, over-invoice guard, void dengan reason, pembatalan schedule, larangan void invoice berbayar, handoff Finance, payment read reconciliation, audit, dan event. Actual yang terlihat: tabel hanya menampilkan header invoice dan pesan Tidak ada piutang terbuka; tidak ada invoice, project commercial basis, payment resmi, detail, tombol issue/void, atau status canonical yang dapat direkonsiliasi. Requirement tidak terpenuhi karena data dan UI Billing invoice unavailable sehingga guard dan handoff tidak dapat diuji. Bukti: test-evidence/session-172-181/UNX-S12-014/01-no-invoice-payment-void-guard-ui.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah prasyarat dan langkah 1, saya membuka Pusat Dokumen melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D untuk mencari preview PDF quotation/invoice dan official document. Expected Result mensyaratkan preview dinamis, official snapshot setelah send/issue, metadata dokumen, checksum, branding, storage, idempotensi, audit/activity/event, serta rekonsiliasi end-to-end Projectâ€“Billingâ€“Finance. Actual yang terlihat: Pusat Dokumen menampilkan Aktif 0, Diarsipkan 0, Total 0, filter jenis Quotation/Invoice tersedia tetapi hasilnya Tidak ada dokumen sesuai filter; tidak ada quotation/invoice, preview, official PDF, metadata, atau alur pembayaran. Requirement tidak terpenuhi karena data dan UI Billing end-to-end unavailable sehingga seluruh langkah tidak dapat dijalankan. Bukti: test-evidence/session-172-181/UNX-S12-015/01-document-center-empty-no-official-billing-pdf.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1 dan langkah 4â€“6, saya membuka route Klien melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D pada workspace Uni-Inside Studio, membuka detail klien yang tersedia, membuka route Tambah Klien, membuka panel Filter, dan menguji pencarian yang tidak cocok. Expected Result mensyaratkan route list/new/detail/edit riil, permission read/write terpisah, dataset klien aktif/nonaktif dengan berbagai party kind/kota/proyek/outstanding, filter/sort/pagination/summary konsisten, serta pengujian foreign-scope dan static route. Actual yang terlihat: route list, detail, Tambah Klien, panel filter, sort, Ekspor CSV, dan pagination tersedia, tetapi hanya ada satu klien aktif; metrik proyek aktif, klien berulang, dan piutang bernilai 0, tanpa variasi fixture untuk status/party kind/kota/proyek/outstanding, foreign organization/BU, atau akun tanpa read permission. Pencarian tanpa hasil menampilkan Tidak Ada Klien Yang Cocok. Expected Result tidak terpenuhi secara penuh karena prasyarat dataset dan variasi permission/scope tidak tersedia; kondisi dikategorikan sebagai data uji unavailable. Bukti: test-evidence/session-182-191/UNX-S13-001/01-clients-list-filters-single-fixture.png dan 02-search-filter-no-match.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1 dan langkah 5â€“7, saya membuka form Tambah Klien melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D, mencoba menyimpan form kosong, lalu mengisi website dengan nilai unsafe dan mencoba menyimpan kembali. Expected Result mensyaratkan create client melalui Party canonical STUDIO, code unik, primary contact deterministik, validasi identity/contact/website, rollback child, audit, dan event. Actual yang terlihat: form create riil tersedia dengan field identitas, website, alamat, catatan, kontak, dan tombol Simpan; setelah submit kosong maupun nilai website unsafe, halaman tetap berada di form tanpa pesan validasi yang terlihat dan tidak ada client baru yang berhasil dibuat. Selain itu tidak tersedia variasi data client/contact dan skenario valid/invalid lengkap untuk memverifikasi canonical Party, collision, &gt;20 contact, primary normalization, rollback, audit, atau event. Expected Result tidak terpenuhi karena create sukses dan seluruh variasi prerequisite tidak dapat dibuktikan melalui UI; kondisi dikategorikan sebagai validasi/prasyarat tidak terpenuhi. Bukti: test-evidence/session-182-191/UNX-S13-002/01-create-client-empty-validation-form.png dan 02-unsafe-website-validation-state.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah prasyarat dan langkah 1â€“5, saya membuka detail klien yang tersedia melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D dan memeriksa ringkasan komersial serta peran yang ditampilkan. Expected Result mensyaratkan duplicate detection, reuse/adopt Party existing, perlindungan identity dan role lain, additive contacts, guard role aktif ganda, reaktivasi role nonaktif, scope organization/BU, response reused, audit create-vs-adopt, dan event. Actual yang terlihat: detail hanya menampilkan nilai komersial Rp 0, Belum Ada Penawaran, Belum Ada Invoice, dan tidak menyediakan tombol/alur Duplicate Detection, use_existing_party_id, Adopt Party, atau data Party nonaktif/foreign/usable untuk dibandingkan. Requirement adoption dan seluruh guard/traceability tidak dapat dijalankan dari UI yang tersedia; kondisi dikategorikan sebagai fitur/data prerequisite unavailable. Bukti: test-evidence/session-182-191/UNX-S13-003/01-commercial-adoption-ui-no-duplicate-action.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1â€“3, saya membuka route Edit Klien melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D dan kembali tanpa menyimpan perubahan. Expected Result mensyaratkan partial update identity, clear email/website menjadi null, URL/email guard, empty-payload validation, preservasi role/contact/project/quotation/invoice, foreign-scope guard, dan audit/event yang hanya memuat perubahan aktual. Actual yang terlihat: route Edit Klien tersedia dan UI memperingatkan bahwa identitas Party dipakai bersama modul lain, tetapi fixture hanya memiliki satu klien tanpa kontak, proyek, quotation, atau invoice; tidak tersedia skenario before/after dan foreign scope untuk memverifikasi preservation, relationship, commercial history, maupun audit/event. Saya tidak menyimpan mutation baru untuk mencegah state leakage. Expected Result tidak terpenuhi penuh karena data uji dan pembuktian mutation parsial tidak tersedia melalui frontend. Bukti: test-evidence/session-182-191/UNX-S13-004/01-edit-client-route-party-shared-warning.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah prasyarat dan langkah 1â€“5, saya membuka tab Kontak pada detail klien melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D dan membuka form Tambah Kontak. Expected Result mensyaratkan Contact CRUD lengkap, otomatisasi primary, partial update, validasi, cross-party guard, concurrency, promosi primary saat delete, dan audit. Actual yang terlihat: klien memiliki 0 kontak, halaman menampilkan Belum Ada Kontak, dan form kontak baru tersedia tetapi tombol Simpan masih disabled karena nama kontak wajib belum diisi. Tidak tersedia client kedua, kontak existing, atau data untuk menguji cross-party/concurrency/delete/promotion/audit. Saya membatalkan form tanpa menyimpan data baru. Expected Result tidak terpenuhi karena fixture kontak dan skenario CRUD lengkap tidak tersedia melalui UI. Bukti: test-evidence/session-182-191/UNX-S13-005/01-contact-form-empty-no-contacts.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1 dan langkah 3â€“9, saya membuka detail klien melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D dan membuka dialog Nonaktifkan Klien Studio, kemudian membatalkannya tanpa menyimpan perubahan. Expected Result mensyaratkan deactivate/reactivate relationship, tanggal lokal Studio, konfirmasi active project, status role/Party, penjagaan histori, idempotensi, global usability, audit, dan event. Actual yang terlihat: klien tersedia dalam status Aktif dengan 0 proyek dan 0 kontak; dialog hanya menjelaskan bahwa Party/kontak/riwayat tetap tersimpan dan menyediakan Batal/Nonaktifkan Klien, tetapi tidak ada fixture klien dengan active project, role nonaktif, Party global unusable, atau kondisi reactivation untuk menguji seluruh guard. Mutation tidak dijalankan agar state klien tidak berubah. Expected Result tidak terpenuhi karena variasi prerequisite dan reactivation tidak tersedia melalui UI. Bukti: test-evidence/session-182-191/UNX-S13-006/01-deactivate-dialog-no-project-fixture.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1â€“5 dan langkah 9, saya membuka detail klien melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D lalu memeriksa tab Proyek, Komersial, dan Aktivitas. Expected Result mensyaratkan read model Party/Projects/Billing/Finance yang konsisten, other roles, project summary/list berstatus lengkap, quotation/invoice/outstanding, read-only tanpa side effect, activity, dan foreign-scope isolation. Actual yang terlihat: tab Proyek menampilkan Belum Ada Proyek, tab Komersial menampilkan nilai Rp 0, Belum Ada Penawaran, Belum Ada Invoice, dan Outstanding Rp 0; fixture hanya satu klien tanpa variasi project/status/payment/quotation/invoice/foreign scope. Activity yang terlihat tidak menyediakan dataset gabungan client dan project status history yang diperlukan. Expected Result tidak terpenuhi karena data lintas modul dan variasi scope tidak tersedia melalui UI. Bukti: test-evidence/session-182-191/UNX-S13-007/01-client-project-commercial-activity-empty-reconciliation.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1 dan langkah 5â€“10, saya membuka list Klien melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D, membuka filter Punya proyek aktif, melihat hasil Tidak Ada Klien Yang Cocok, lalu menjalankan Ekspor CSV sebelum dan sesudah filter. Expected Result mensyaratkan activity gabungan audit client + project status history, limit 200, parity filter/export, maksimal 100 baris, filename studio-clients.csv, UTF-8/BOM, formula-injection safety, escaping, dan read-only tanpa side effect. Actual yang terlihat: filter menghasilkan daftar kosong karena tidak ada client dengan proyek aktif; ekspor frontend berhasil mengunduh studio-clients.csv, tetapi tidak ada dataset project/activity atau nilai teks berbahaya untuk memverifikasi parity, formula injection, escaping, dan batas baris. Expected Result tidak terpenuhi penuh karena fixture yang diperlukan tidak tersedia. Bukti: test-evidence/session-182-191/UNX-S13-008/01-activity-export-filter-no-fixture.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1â€“4 dan langkah 10, saya membuka route Services melalui navigasi frontend dengan ACCOUNT #1 â€” Insinyur 3D. Expected Result mensyaratkan sembilan route Services/Packages riil, permission read/write terpisah, overview/catalog/detail, filter/sort/default, pagination fallback, scope STUDIO, dan browser acceptance tanpa Akses Ditolak/Dalam Pengembangan. Actual yang terlihat pada route /app/studio/services adalah halaman Akses Ditolak dengan pesan bahwa akun tidak memiliki izin yang diperlukan; sidebar juga tidak menyediakan menu Services/Packages. Karena route awal saja tidak dapat dibuka, seluruh route, filter/sort, overview, foreign-scope, dan acceptance tidak dapat dijalankan. Requirement tidak terpenuhi karena UI unavailable/permission tidak memungkinkan pengujian. Bukti: test-evidence/session-182-191/UNX-S13-009/01-services-route-access-denied.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1â€“12, saya membuka route kategori Services melalui frontend dengan ACCOUNT #1 â€” Insinyur 3D pada workspace Uni-Inside Studio. Expected Result mensyaratkan category CRUD, normalisasi code, collision suffix, validation, deactivation guard terhadap active service, reactivation, category/service status guard, dan audit STUDIO. Actual yang terlihat pada route /app/studio/services/categories adalah halaman Akses Ditolak dengan pesan bahwa akun tidak memiliki izin yang diperlukan; tidak ada halaman category, form, service aktif, atau tombol CRUD. Seluruh langkah dan guard tidak dapat dijalankan karena UI Services unavailable/permission tidak tersedia. Bukti: test-evidence/session-182-191/UNX-S13-010/01-service-category-route-access-denied.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1–11, saya membuka alur Services melalui frontend dengan ACCOUNT #1 — Insinyur 3D pada workspace Uni-Inside Studio. Expected Result mensyaratkan create/update service, SVC code unik, pricing model, validasi harga/kategori, partial patch, foreign-scope guard, serta audit/event. Actual yang terlihat pada route /app/studio/services adalah halaman Akses Ditolak dengan pesan bahwa akun tidak memiliki izin yang diperlukan; sidebar juga tidak menyediakan menu Services. Karena UI awal tidak dapat dibuka, seluruh form, kategori, validasi, partial patch, scope, dan audit/event tidak dapat dijalankan. Requirement tidak terpenuhi karena fitur unavailable untuk akun/permission ini. Bukti: test-evidence/session-192-201/UNX-S13-011/01-services-route-access-denied.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1–10, saya membuka route Services melalui frontend dengan ACCOUNT #1 — Insinyur 3D untuk menguji activate/deactivate service, eligibility catalog, historical usage, dan state guard. Expected Result mensyaratkan service aktif/nonaktif, category guard, preservasi snapshot historis, references eligibility, idempotency, foreign-scope guard, audit, dan event. Actual yang terlihat: route /app/studio/services menampilkan Akses Ditolak dengan pesan akun tidak memiliki izin yang diperlukan; tidak ada service, category, history, tombol lifecycle, atau data fixture yang dapat diproses. Seluruh langkah tidak dapat dijalankan karena UI Services unavailable pada permission akun ini. Bukti: test-evidence/session-192-201/UNX-S13-012/01-services-lifecycle-route-unavailable.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1–10, saya membuka route detail Service melalui frontend dengan ACCOUNT #1 — Insinyur 3D. Expected Result mensyaratkan detail service, Paket, Proyek, Penggunaan Komersial, Activity, most_used sorting, perubahan harga tanpa mengubah snapshot historis, dan rekonsiliasi lintas modul. Actual yang terlihat pada route detail /app/studio/services/1 adalah Akses Ditolak dengan pesan akun tidak memiliki izin yang diperlukan; tidak ada detail service, tab, usage, history, atau activity yang dapat dibaca. Requirement tidak terpenuhi karena UI dan data Service unavailable untuk akun ini. Bukti: test-evidence/session-192-201/UNX-S13-013/01-service-detail-route-access-denied.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1–12, saya membuka route Packages melalui frontend dengan ACCOUNT #1 — Insinyur 3D pada workspace Uni-Inside Studio. Expected Result mensyaratkan package aktif dengan item service unik, PKG code, validasi item/quantity/price, partial update, replacement atomik, rollback, dan audit/event. Actual yang terlihat pada route /app/studio/services/packages adalah halaman Akses Ditolak dengan pesan akun tidak memiliki izin yang diperlukan; tidak ada daftar/form package, service, atau kontrol create/update. Seluruh langkah tidak dapat dijalankan karena UI Packages unavailable untuk akun ini. Bukti: test-evidence/session-192-201/UNX-S13-014/01-packages-route-access-denied.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1–12, saya membuka route detail Packages melalui frontend dengan ACCOUNT #1 — Insinyur 3D pada workspace Uni-Inside Studio untuk menguji aktivasi/deaktivasi package, revalidasi komposisi, historical snapshot, eligibility Project/Billing, dan rekonsiliasi end-to-end. Expected Result mensyaratkan package valid/inaktif/kosong, service aktif/nonaktif, guard activation/deactivation/idempotency, preservasi project/commercial history, serta audit/event. Actual yang terlihat pada /app/studio/services/packages/1 adalah halaman Akses Ditolak dengan pesan akun tidak memiliki izin; tidak ada detail package, item, service, project, Billing, tombol lifecycle, atau data fixture. Seluruh langkah tidak dapat dijalankan karena UI Packages unavailable untuk akun ini. Bukti: test-evidence/session-192-201/UNX-S13-015/01-package-detail-route-access-denied.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1–9, saya membuka route Equipment melalui frontend dengan ACCOUNT #1 — Insinyur 3D pada workspace Uni-Inside Studio. Expected Result mensyaratkan akses dan navigasi ke overview, daftar assets, create, detail, edit, assignments, dan maintenance, termasuk proteksi route, permission, scope STUDIO, serta penerimaan browser. Actual yang terlihat pada /app/studio/equipment adalah halaman Akses Ditolak dengan pesan akun tidak memiliki izin; sidebar tidak menyediakan menu Equipment dan route-route turunannya tidak dapat digunakan. Requirement navigasi, permission, static-route protection, scope, dan browser acceptance tidak terpenuhi karena UI Equipment unavailable untuk akun ini. Bukti: test-evidence/session-192-201/UNX-S14-001/01-equipment-route-access-denied.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1–8, saya membuka halaman overview Equipment melalui frontend dengan ACCOUNT #1 — Insinyur 3D untuk memeriksa KPI equipment, alert assignment/maintenance, total asset value, recent activity, dan rekonsiliasi kanonik. Expected Result mensyaratkan seluruh ringkasan menghitung data scoped secara konsisten dan menampilkan kondisi kosong/terisi yang benar. Actual yang terlihat pada /app/studio/equipment/overview adalah halaman Akses Ditolak dengan pesan akun tidak memiliki izin; KPI, alert, nilai aset, aktivitas terbaru, dan rekonsiliasi tidak tampil. Requirement overview tidak terpenuhi karena UI Equipment unavailable untuk akun ini. Bukti: test-evidence/session-192-201/UNX-S14-002/01-equipment-overview-access-denied.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1–10, saya membuka daftar Assets melalui frontend dengan ACCOUNT #1 — Insinyur 3D untuk menguji filter status/kategori, pencarian, effective usage, assignment saat ini dan berikutnya, maintenance, sorting, pagination, serta scope data. Expected Result mensyaratkan daftar dan filter menampilkan aset scoped dengan assignment dan maintenance yang benar serta pagination yang konsisten. Actual yang terlihat pada /app/studio/equipment/assets adalah halaman Akses Ditolak dengan pesan akun tidak memiliki izin; tabel, filter, pencarian, assignment, maintenance, sorting, dan pagination tidak tersedia. Requirement daftar Assets tidak terpenuhi karena UI unavailable untuk akun ini. Bukti: test-evidence/session-192-201/UNX-S14-003/01-assets-list-access-denied.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1–12, saya membuka form create Asset melalui frontend dengan ACCOUNT #1 — Insinyur 3D. Expected Result mensyaratkan pembuatan asset dengan AST code unik, serial number unik, custodian, status awal, book value, validasi field, dan atomicity ketika terjadi kesalahan. Actual yang terlihat pada /app/studio/equipment/assets/new adalah halaman Akses Ditolak dengan pesan akun tidak memiliki izin; form, field, validasi, tombol simpan, dan hasil atomicity tidak tersedia. Requirement create Asset tidak terpenuhi karena UI unavailable untuk akun ini. Bukti: test-evidence/session-192-201/UNX-S14-004/01-asset-create-access-denied.png.</t>
+  </si>
+  <si>
+    <t>Pada langkah 1–10, saya membuka form edit Asset melalui frontend dengan ACCOUNT #1 — Insinyur 3D untuk menguji partial update, revalidasi serial/custodian, field finansial, audit custodian, dan isolasi status. Expected Result mensyaratkan field yang tidak diubah tetap terjaga, konflik serial/custodian ditolak, perubahan finansial tervalidasi, audit tercatat, dan status tidak berubah tanpa instruksi. Actual yang terlihat pada /app/studio/equipment/assets/1/edit adalah halaman Akses Ditolak dengan pesan akun tidak memiliki izin; detail/form asset, field edit, validasi, audit, dan kontrol status tidak tersedia. Requirement partial update tidak terpenuhi karena UI unavailable untuk akun ini. Bukti: test-evidence/session-192-201/UNX-S14-005/01-asset-edit-access-denied.png.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka modul Equipment Studio dan memverifikasi transition matrix serta guard status, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, halaman /app/studio/equipment menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan state machine status, reason guard, unresolved-assignment guard, pemulihan lost/retired, histori, audit, dan event dapat diverifikasi. Actual Result: tidak ada halaman, daftar, form, atau kontrol Equipment yang dapat diakses sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Equipment yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-202-211/UNX-S14-006/01-equipment-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka modul Equipment untuk memeriksa References, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, halaman /app/studio/equipment menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan reference projects, users, external parties, categories, locations, dan depreciation methods yang valid, terscope, DISTINCT, serta terurut. Actual Result: tidak ada halaman, daftar, form, atau kontrol Equipment yang dapat diakses sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Equipment yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-202-211/UNX-S14-007/01-equipment-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka Equipment untuk membuat assignment asset ke project, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, halaman /app/studio/equipment menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan assignment untuk project operational dan asset eligible, perubahan status immediate/future yang benar, Project Commercial link, validasi waktu/scope, audit, dan event. Actual Result: tidak ada halaman, daftar, form, atau kontrol Equipment yang dapat diakses sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Equipment yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-202-211/UNX-S14-008/01-equipment-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka Equipment untuk membuat booking dan menguji konflik assignment, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, halaman /app/studio/equipment menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan pencegahan double booking, overlap/open-ended logic, availability, category filter, boundary non-overlap, dan concurrency protection. Actual Result: tidak ada halaman, daftar, form, atau kontrol Equipment yang dapat diakses sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Equipment yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-202-211/UNX-S14-009/01-equipment-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka Equipment untuk melakukan return assignment aktif, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, halaman /app/studio/equipment menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan return hanya untuk assignment yang sudah dimulai, validasi waktu, pelepasan asset yang aman, preservasi history, serta audit/event satu kali. Actual Result: tidak ada halaman, daftar, form, atau kontrol Equipment yang dapat diakses sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Equipment yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-202-211/UNX-S14-010/01-equipment-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka Equipment untuk membatalkan future booking, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, halaman /app/studio/equipment menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan hanya future booking yang dapat dibatalkan, availability pulih, next_assignment diperbarui, assignment lain tidak terhapus, dan audit cancellation tersedia. Actual Result: tidak ada halaman, daftar, form, atau kontrol Equipment yang dapat diakses sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Equipment yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-202-211/UNX-S14-011/01-equipment-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka Equipment untuk memulai maintenance pada asset available, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, halaman /app/studio/equipment menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan guard current assignment/status blocking, preservasi future booking dengan warning, blok assignment baru, serta audit/event lifecycle. Actual Result: tidak ada halaman, daftar, form, atau kontrol Equipment yang dapat diakses sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Equipment yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-202-211/UNX-S14-012/01-equipment-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka Equipment untuk menyelesaikan maintenance, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, halaman /app/studio/equipment menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan maintenance record dan perubahan status atomik, provider/time/cost/next-due tervalidasi, outcome status valid, serta audit/event lengkap. Actual Result: tidak ada halaman, daftar, form, atau kontrol Equipment yang dapat diakses sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Equipment yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-202-211/UNX-S14-013/01-equipment-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka Equipment untuk menambahkan historical maintenance record, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, halaman /app/studio/equipment menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan CRUD history tanpa side effect status, derived due states, filter, partial update, cross-asset guard, dan pengujian future-time consistency gap. Actual Result: tidak ada halaman, daftar, form, atau kontrol Equipment yang dapat diakses sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Equipment yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-202-211/UNX-S14-014/01-equipment-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka Asset Detail untuk rekonsiliasi lifecycle Equipment end-to-end, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, halaman /app/studio/equipment menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan Asset Detail, Penggunaan Proyek, Perawatan, Activity, Project Commercial, history, dan audit/event merekonsiliasi asset/project canonical. Actual Result: tidak ada halaman, daftar, form, atau kontrol Equipment yang dapat diakses sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Equipment yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-202-211/UNX-S14-015/01-equipment-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka route Vendor pertama dari delapan route browser acceptance, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, route /app/studio/vendors menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan delapan route Studio Vendors aktif, static route aman, permission read/write terpisah, scope organisasi/STUDIO benar, dan browser acceptance tanpa placeholder/runtime error. Actual Result: route, directory, detail, form, filter, dan kontrol Vendor yang diperlukan tidak tersedia sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Vendors yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-212-221/UNX-S15-001/01-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka directory Vendor untuk menguji search, role, relationship, city, assignment, sort, dan pagination, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, route /app/studio/vendors menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan search, filter, pagination, DISTINCT multi-role, dan sort asc/desc merekonsiliasi Party canonical dalam scope organisasi/STUDIO. Actual Result: route, directory, detail, form, filter, dan kontrol Vendor yang diperlukan tidak tersedia sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Vendors yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-212-221/UNX-S15-002/01-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka ringkasan Vendor untuk merekonsiliasi KPI party, role, fee, dan expense, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, route /app/studio/vendors menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan summary berasal dari data canonical, active Party mengikuti effective-role semantics, serta fee dan expense tidak double-count. Actual Result: route, directory, detail, form, filter, dan kontrol Vendor yang diperlukan tidak tersedia sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Vendors yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-212-221/UNX-S15-003/01-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka directory Vendor untuk menguji CSV export dan filter parity, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, route /app/studio/vendors menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan CSV aman UTF-8/BOM dari formula injection, mengikuti filter/list canonical, batas maksimum 100 row terlihat, tanpa leakage atau side effect. Actual Result: route, directory, detail, form, filter, dan kontrol Vendor yang diperlukan tidak tersedia sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Vendors yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-212-221/UNX-S15-004/01-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka form untuk membuat canonical external Party, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, route /app/studio/vendors menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan Party canonical dibuat atomik dengan EXT code, managed role/contact tervalidasi tanpa duplicate, dan audit hanya setelah transaksi sukses. Actual Result: route, directory, detail, form, filter, dan kontrol Vendor yang diperlukan tidak tersedia sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Vendors yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-212-221/UNX-S15-005/01-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka fungsi Cek Duplikat dan menguji duplicate confirmation, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, route /app/studio/vendors menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan duplicate check read-only dan scoped organisasi, confirmation eksplisit untuk duplikat, serta candidate match reason dan role context tersedia. Actual Result: route, directory, detail, form, filter, dan kontrol Vendor yang diperlukan tidak tersedia sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Vendors yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-212-221/UNX-S15-006/01-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka form Tambah Pihak untuk menguji adoption Party existing, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, route /app/studio/vendors menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan adoption mempertahankan Party ID/code/identity/role lama, menambah role/contact secara aman, dan UI mampu menyelesaikan adoption. Actual Result: route, directory, detail, form, filter, dan kontrol Vendor yang diperlukan tidak tersedia sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Vendors yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-212-221/UNX-S15-007/01-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka detail Party untuk menguji partial identity update, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, route /app/studio/vendors menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan update parsial canonical dengan validasi null/URL/email, tanpa mengubah role/status/code/history, serta duplicate re-check gap terdeteksi. Actual Result: route, directory, detail, form, filter, dan kontrol Vendor yang diperlukan tidak tersedia sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Vendors yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-212-221/UNX-S15-008/01-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka detail Party untuk mengaktifkan atau re-activate managed role, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, route /app/studio/vendors menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan re-activation memakai role row yang sama, guard already-active/global-inactive berlaku, role lain tetap aman, dan read model terbaru. Actual Result: route, directory, detail, form, filter, dan kontrol Vendor yang diperlukan tidak tersedia sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Vendors yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-212-221/UNX-S15-009/01-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pada langkah ketika membuka detail Party untuk menonaktifkan managed role, setelah login sebagai ACCOUNT #10 ? Insinyur 3D dan mengaktifkan workspace Uni-Inside Studio, route /app/studio/vendors menampilkan ?Akses Ditolak?; sidebar hanya menyediakan Proyek, Klien, dan Keuangan. Expected Result mengharuskan deactivation hanya memengaruhi satu managed role, active-assignment confirmation berlaku, history dipertahankan, dan last-role menjadi role_inactive. Actual Result: route, directory, detail, form, filter, dan kontrol Vendor yang diperlukan tidak tersedia sehingga langkah lanjutan tidak dapat dilakukan dari frontend. Requirement tidak terpenuhi karena fitur Vendors yang diuji unavailable bagi account/role yang ditentukan; hasil ini Bug/Failed. Bukti: test-evidence/session-212-221/UNX-S15-010/01-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan Vendor dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Halaman/detil Vendor serta tindakan tambah, edit, penghapusan, kontak utama, dan validasi kontak tidak tersedia. Expected Result CRUD kontak Vendor tidak dapat dipenuhi; fitur tidak tersedia untuk peran yang ditentukan. Bukti: test-evidence/session-222-231/UNX-S15-011/01-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan Vendor dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Halaman/detil Vendor serta UI penugasan proyek, pembuatan assignment, validasi allocation, dan guard duplikasi tidak tersedia. Expected Result Vendor Project Options &amp; Assignment Create tidak dapat dipenuhi; fitur tidak tersedia untuk peran yang ditentukan. Bukti: test-evidence/session-222-231/UNX-S15-012/01-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan Vendor dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Halaman/detil Vendor serta UI pembaruan, pengakhiran assignment, guard tanggal/allocation, dan dampak ke opsi Vendor tidak tersedia. Expected Result Vendor Assignment Update/End tidak dapat dipenuhi; fitur tidak tersedia untuk peran yang ditentukan. Bukti: test-evidence/session-222-231/UNX-S15-013/01-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan Vendor dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Halaman/detil Vendor serta ringkasan komersial, status pending/aktif, total committed, dan ketergantungan payout tidak tersedia. Expected Result Vendor Commercial Summary tidak dapat dipenuhi; fitur tidak tersedia untuk peran yang ditentukan. Bukti: test-evidence/session-222-231/UNX-S15-014/01-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan Vendor dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Halaman detil Vendor dan seluruh subbagian Read Model (profil, kontak, assignment, komersial, serta aksi standar) tidak dapat dibuka. Expected Result Vendor Detail Read Model tidak dapat dipenuhi; fitur tidak tersedia untuk peran yang ditentukan. Bukti: test-evidence/session-222-231/UNX-S15-015/01-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, 11 layar utama Finance dapat dibuka melalui sidebar tanpa placeholder. Namun pada langkah wildcard, navigasi UI ke /app/studio/finance/route-yang-tidak-ada tetap berada di URL tersebut dan area utama kosong, bukan kembali ke Finance index. Expected Result redirect wildcard/rute anak aman tidak terpenuhi; perilaku rute salah. Bukti: test-evidence/session-222-231/UNX-S16-001/01-wildcard-route-blank.png</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, halaman Ringkasan Keuangan tampil tetapi seluruh KPI dan daftar perhatian bernilai Rp 0/0 dengan pesan belum ada transaksi. Fixture yang diwajibkan langkah uji (treasury aktif, transaksi posted bulanan, invoice/piutang, kewajiban dan jadwal) tidak tersedia di UI sehingga rekonsiliasi lintas modul dan Expected Result KPI tidak dapat divalidasi lengkap. Prasyarat kasus tidak tersedia. Bukti: test-evidence/session-222-231/UNX-S16-002/01-overview-empty-fixture.png</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, layar Transaksi menampilkan riwayat posted dan empty state. Namun UI tidak menyediakan kontrol pencarian, filter tipe/sumber/status, rentang tanggal, maupun pagination yang diwajibkan Langkah Uji; fixture transaksi untuk verifikasi urutan dan source juga tidak tersedia. Expected Result filter dan verifikasi transaksi tidak dapat dipenuhi lengkap; fitur UI tidak tersedia. Bukti: test-evidence/session-222-231/UNX-S16-003/01-transactions-ui.png</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI berhasil membuat treasury uji dengan kode TRS-000015 dan status active. Namun formulir tidak menampilkan input mata uang, pilihan tipe marketplace balance, atau kontrol status per treasury untuk menjalankan siklus active/inactive/closed serta validasi mismatch yang diwajibkan. Expected Result lifecycle dan validasi treasury tidak dapat dipenuhi lengkap; fitur UI tidak tersedia. Bukti: test-evidence/session-222-231/UNX-S16-004/01-treasury-created-ui-gap.png</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, transfer antar dua treasury uji berhasil secara UI (saldo sumber Rp 100 menjadi Rp 75 dan tujuan Rp 0 menjadi Rp 25); percobaan sumber=tujuan ditolak dengan pesan bahwa akun harus berbeda. Namun UI tidak menyediakan cara memverifikasi akun asing, concurrency transfer berlawanan, jurnal seimbang, audit/event, dan pencegahan inflasi arus kas sebagaimana diwajibkan Expected Result. Expected Result tidak dapat dipenuhi lengkap; permukaan UI verifikasi yang diperlukan tidak tersedia. Bukti: test-evidence/session-222-231/UNX-S16-005/01-transfer-and-same-account-guard.png</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, form Catat Pendapatan Manual tampil tetapi pemilih kategori income memiliki 0 opsi. Kategori Studio aktif yang diwajibkan tidak tersedia sehingga posting valid tidak dapat dilakukan; transaction, journal, audit, Party/reference, dan Overview tidak dapat diverifikasi. Expected Result tidak terpenuhi karena prasyarat kategori/UI tidak tersedia. Bukti: test-evidence/session-232-241/UNX-S16-006/01-income-empty-category.png</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, Piutang Klien menampilkan 'Tidak ada piutang terbuka.' Tidak tersedia invoice issued, payment schedule, project, maupun tindakan pembayaran; pembayaran parsial, guard overpayment, treasury posting, dan sinkronisasi invoice/schedule/project/Billing tidak dapat dijalankan literal. Expected Result tidak terpenuhi karena fixture kanonis tidak tersedia di UI. Bukti: test-evidence/session-232-241/UNX-S16-007/01-receivables-empty.png</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, daftar Pengeluaran kosong dan form Pengeluaran Baru memiliki pemilih kategori dengan 0 opsi. Expense draft/approved/paid tidak dapat dibuat sah; filter, direct-payment confirmation, posting kas, dan actual_cost tidak dapat diverifikasi. Expected Result tidak terpenuhi karena kategori/fixture wajib tidak tersedia di UI. Bukti: test-evidence/session-232-241/UNX-S16-008/01-expense-form-empty-category.png</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, daftar expense kosong dan form pembuatan tidak memiliki opsi kategori. Tidak tersedia expense draft/approved yang terhubung project untuk approve, pay, bypass, double-pay guard, treasury/journal, dan sync actual_cost. Expected Result tidak terpenuhi karena fixture expense wajib tidak tersedia dari UI. Bukti: test-evidence/session-232-241/UNX-S16-009/01-no-expense-approval-payment-fixture.png</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, tidak ada row expense dan form baru tidak dapat dibuat karena pemilih kategori kosong. Aksi receipt upload/replace/download/delete tidak tersedia, sehingga storage/Document Registry dan missing-receipt guard tidak dapat diuji. Expected Result tidak terpenuhi karena fixture dan tindakan UI wajib tidak tersedia. Bukti: test-evidence/session-232-241/UNX-S16-010/01-no-expense-receipt-fixture.png</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, daftar Pengeluaran kosong dan tidak ada paid expense dengan financial transaction untuk dibalik. Paid-only guard, reversal tunggal, pengembalian treasury/journal, void history, source type, audit, dan rollback actual_cost tidak dapat dijalankan dari UI. Expected Result tidak terpenuhi karena prasyarat paid expense tidak tersedia. Bukti: test-evidence/session-232-241/UNX-S16-011/01-no-paid-expense-reversal-fixture.png</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, tabel Kewajiban Vendor/Freelancer tanpa assignment/payable. Tidak ada external assignment, agreed fee, Party, proyek, category, atau aksi payout untuk menguji partial/full, overpayment, generated expense, dan rekonsiliasi lintas modul. Expected Result tidak terpenuhi karena fixture dan tindakan UI wajib tidak tersedia. Bukti: test-evidence/session-232-241/UNX-S16-012/01-payables-empty.png</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, navigasi Equipment menampilkan 'Akses Ditolak'. Maintenance record dan aksi payment tidak dapat dibuka; idempotency, generated expense, treasury/journal, optional project cost, dan rekonsiliasi Equipment tidak dapat dijalankan. Expected Result tidak terpenuhi karena fitur UI tidak tersedia untuk peran yang ditentukan. Bukti: test-evidence/session-232-241/UNX-S16-013/01-equipment-access-denied.png</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, Profitabilitas tidak memiliki baris proyek dan Arus Kas seluruhnya Rp 0. Fixture project, invoice, paid/void expense, external payout, serta transaksi bertanggal tidak tersedia untuk margin, date filter, dan rekonsiliasi. Transfer internal tidak tampak sebagai arus bisnis, tetapi Expected Result lengkap tidak dapat dibuktikan. Bukti: test-evidence/session-232-241/UNX-S16-014/01-profitability-empty.png dan test-evidence/session-232-241/UNX-S16-014/02-cash-flow-zero.png</t>
+  </si>
+  <si>
+    <t>Dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, form Anggaran tidak memiliki pemilih kategori maupun kontrol 1?100 item dan daftar anggaran kosong. Jurnal &amp; Periode baca-saja tidak memiliki jurnal posted atau periode keuangan. Tidak ada paid expense/fixture smoke Finance untuk actuals, approval, balance, shared periods, dan rekonsiliasi end-to-end. Expected Result tidak terpenuhi. Bukti: test-evidence/session-232-241/UNX-S16-015/01-budget-form-ui-gap.png dan test-evidence/session-232-241/UNX-S16-015/02-accounting-no-journals-periods.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan /app/studio/analytics dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Kesembilan child route Analytics juga menampilkan pesan yang sama; route liar tidak dapat diarahkan ke index. Expected Result sepuluh report aktif, permission read/export, deep-link, wildcard redirect, dan browser acceptance tidak terpenuhi karena akses UI Analytics tidak tersedia untuk peran yang memiliki permission yang dipersyaratkan. Bukti: test-evidence/session-242-251/UNX-S17-001/01-studio-analytics-access-denied.png dan test-evidence/session-242-251/UNX-S17-001/02-analytics-wildcard-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan Analytics dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Karena halaman tidak dapat dibuka, default 30 hari Jakarta, alias filter, compare period, range/currency guard, pagination, preset, dan query-string tidak dapat diuji melalui frontend. Expected Result tidak terpenuhi karena report dan kontrol filter tidak tersedia untuk peran yang ditentukan. Bukti: test-evidence/session-242-251/UNX-S17-002/01-243-analytics-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan Analytics dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Overview KPI tidak dapat dibuka sehingga cohort/snapshot, comparison, definisi cash/invoice/cost, dan read-only integrity tidak dapat direkonsiliasi melalui UI. Expected Result tidak terpenuhi karena akses report Analytics tidak tersedia. Bukti: test-evidence/session-242-251/UNX-S17-003/01-244-analytics-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan Analytics dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Trends, granularity, ranking, status distribution, attention queue, serta perilaku filter tidak dapat dijalankan. Expected Result tidak terpenuhi karena report Analytics dan transparansi filter yang diwajibkan tidak tersedia untuk peran yang ditentukan. Bukti: test-evidence/session-242-251/UNX-S17-004/01-245-analytics-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan route Analytics Projects dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Data cohort, funnel status-history, cycle time, on-time delivery, milestone/deliverable, type breakdown, pagination, dan detail project tidak dapat diakses. Expected Result tidak terpenuhi karena report Projects tidak tersedia di frontend. Bukti: test-evidence/session-242-251/UNX-S17-005/01-246-analytics-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan route Analytics Clients dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Agregasi client_party_id, repeat rate, active projects, ranking, concentration, historical identity, filter, dan pagination tidak dapat diuji. Expected Result tidak terpenuhi karena report Clients tidak tersedia di frontend. Bukti: test-evidence/session-242-251/UNX-S17-006/01-247-analytics-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan route Analytics Services dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Scope snapshot service, catalog/custom grouping, quotation/invoice values, accepted value, historical pricing, dan cross-filter consistency tidak dapat diuji. Expected Result tidak terpenuhi karena report Services tidak tersedia di frontend. Bukti: test-evidence/session-242-251/UNX-S17-007/01-248-analytics-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan route Analytics Commercial dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Commercial funnel, conversion, expiry, invoice cohort, customer cash, schedule snapshot, dan period-semantics gap tidak dapat diverifikasi. Expected Result tidak terpenuhi karena report Commercial tidak tersedia di frontend. Bukti: test-evidence/session-242-251/UNX-S17-008/01-249-analytics-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan route Analytics Revenue dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Revenue/cash-flow, posted transaction type, category/source breakdown, treasury snapshot, adjustment, transfer neutrality, dan daily average tidak dapat diuji. Expected Result tidak terpenuhi karena report Revenue tidak tersedia di frontend. Bukti: test-evidence/session-242-251/UNX-S17-009/01-250-analytics-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan route Analytics Profitability dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Commercial basis, invoice collection, paid project cost, external commitment, negative margin, ranking, cohort semantics, pagination, dan currency guard tidak dapat direkonsiliasi. Expected Result tidak terpenuhi karena report Profitability tidak tersedia di frontend. Bukti: test-evidence/session-242-251/UNX-S17-010/01-251-analytics-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan Analytics Receivables dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Snapshot aging, due-in-7-days, breakdown klien/proyek, collection-speed, boundary tanggal Jakarta, filter, dan pagination tidak dapat dijalankan. Expected Result tidak terpenuhi karena report tidak tersedia untuk peran yang memiliki permission yang dipersyaratkan. Bukti: test-evidence/session-252-261/UNX-S17-011/01-analytics-receivables-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan Analytics Vendors dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Commitment, payout, remaining, role distribution, collaborator ranking, pagination, fee trend, dan filter capability tidak dapat diverifikasi. Expected Result tidak terpenuhi karena report Vendors tidak tersedia di frontend. Bukti: test-evidence/session-252-261/UNX-S17-012/01-analytics-vendors-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan Analytics Equipment dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Snapshot asset, utilization overlap-safe, distinct project, maintenance cost, upcoming-due, value snapshot, dan filter applicability tidak dapat diuji. Expected Result tidak terpenuhi karena report Equipment tidak tersedia di frontend. Bukti: test-evidence/session-252-261/UNX-S17-013/01-analytics-equipment-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah pembukaan Analytics dan pengujian export dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Tombol/export CSV-XLSX-PDF, formula safety, permission boundary, truncation, storage/registry/audit, dan source consistency tidak dapat diuji. Expected Result tidak terpenuhi karena report Analytics dan kemampuan export tidak tersedia pada UI. Bukti: test-evidence/session-252-261/UNX-S17-014/01-analytics-export-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah membuka Report Center melalui UI dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, halaman menampilkan Laporan Tersedia 0, Studio 0, Keuangan 0, Ekspor Terbaru 0, serta 'Tidak ada laporan yang sesuai atau dapat diakses'. Expected Result tepat sepuluh registry report Studio, preview, export, history, permission, cap, formula safety, dan rekonsiliasi tidak dapat dipenuhi karena katalog report tidak tersedia. Bukti: test-evidence/session-252-261/UNX-S17-015/01-report-center-empty.png</t>
+  </si>
+  <si>
+    <t>Pada langkah membuka /app/studio/automations dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Tujuh route, permission read/write/run, capability gating, scope STUDIO, dan browser acceptance tidak dapat dijalankan. Expected Result tidak terpenuhi karena pusat Automations Studio tidak tersedia untuk peran yang ditentukan. Bukti: test-evidence/session-252-261/UNX-S18-001/01-studio-automations-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah membuka Global Automations Center melalui UI dengan ACCOUNT #10 ? Insinyur 3D, halaman tidak merender center dan menampilkan 'Unexpected Application Error!' dengan pesan 'Invalid time value'. Expected Result workspace capability, operation guard, pagination, sanitization, dan isolasi lintas workspace tidak terpenuhi; aplikasi mengalami error runtime yang terlihat. Bukti: test-evidence/session-252-261/UNX-S18-002/01-global-automations-invalid-time-error.png</t>
+  </si>
+  <si>
+    <t>Pada langkah membuka katalog Automations Studio dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Registry 32 trigger, 6 action, metadata, recommended actions, modules, dan guard kebocoran Craft tidak dapat diverifikasi. Expected Result tidak terpenuhi karena katalog tidak tersedia di frontend. Bukti: test-evidence/session-252-261/UNX-S18-003/01-automation-catalog-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah membuka halaman template Automations Studio dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Enam built-in template, cron WIB, cooldown, use-to-draft, immutability, permission action, dan safe activation tidak dapat diuji. Expected Result tidak terpenuhi karena fitur template tidak tersedia di frontend. Bukti: test-evidence/session-252-261/UNX-S18-004/01-automation-templates-access-denied.png</t>
+  </si>
+  <si>
+    <t>Pada langkah membuka Rule Builder Automations Studio dengan ACCOUNT #10 ? Insinyur 3D dan workspace Studio aktif, UI menampilkan 'Akses Ditolak'. Kompatibilitas trigger/action, supportedEvents, filtering, config validation, payload rejection, draft, activation, dan permission domain tidak dapat diuji. Expected Result tidak terpenuhi karena Rule Builder tidak tersedia di frontend. Bukti: test-evidence/session-252-261/UNX-S18-005/01-automation-rule-builder-access-denied.png</t>
   </si>
 </sst>
 </file>
@@ -10486,7 +11166,9 @@
       <c r="M9" s="6"/>
       <c r="N9" s="7"/>
       <c r="O9" s="8"/>
-      <c r="P9" s="7"/>
+      <c r="P9" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="Q9" s="6"/>
     </row>
     <row r="10" spans="1:17" ht="22.5" customHeight="1">
@@ -10546,7 +11228,9 @@
       <c r="M11" s="6"/>
       <c r="N11" s="7"/>
       <c r="O11" s="8"/>
-      <c r="P11" s="7"/>
+      <c r="P11" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="Q11" s="6"/>
     </row>
     <row r="12" spans="1:17" ht="22.5" customHeight="1">
@@ -10635,7 +11319,9 @@
       <c r="M14" s="6"/>
       <c r="N14" s="7"/>
       <c r="O14" s="8"/>
-      <c r="P14" s="7"/>
+      <c r="P14" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="Q14" s="6"/>
     </row>
     <row r="15" spans="1:17" ht="22.5" customHeight="1">
@@ -10666,7 +11352,9 @@
       <c r="M15" s="6"/>
       <c r="N15" s="7"/>
       <c r="O15" s="8"/>
-      <c r="P15" s="7"/>
+      <c r="P15" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="Q15" s="6"/>
     </row>
     <row r="16" spans="1:17" ht="345" customHeight="1">
@@ -10755,7 +11443,9 @@
       <c r="M18" s="6"/>
       <c r="N18" s="7"/>
       <c r="O18" s="8"/>
-      <c r="P18" s="7"/>
+      <c r="P18" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="Q18" s="6"/>
     </row>
     <row r="19" spans="1:17" ht="22.5" customHeight="1">
@@ -10786,7 +11476,9 @@
       <c r="M19" s="6"/>
       <c r="N19" s="7"/>
       <c r="O19" s="8"/>
-      <c r="P19" s="7"/>
+      <c r="P19" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="Q19" s="6"/>
     </row>
     <row r="20" spans="1:17" ht="15.75" customHeight="1">
@@ -10846,7 +11538,9 @@
       <c r="M21" s="6"/>
       <c r="N21" s="7"/>
       <c r="O21" s="8"/>
-      <c r="P21" s="7"/>
+      <c r="P21" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="Q21" s="6"/>
     </row>
     <row r="22" spans="1:17" ht="15.75" customHeight="1">
@@ -10877,7 +11571,9 @@
       <c r="M22" s="6"/>
       <c r="N22" s="7"/>
       <c r="O22" s="8"/>
-      <c r="P22" s="7"/>
+      <c r="P22" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="Q22" s="6"/>
     </row>
     <row r="23" spans="1:17" ht="15.75" customHeight="1">
@@ -10937,7 +11633,9 @@
       <c r="M24" s="6"/>
       <c r="N24" s="7"/>
       <c r="O24" s="8"/>
-      <c r="P24" s="7"/>
+      <c r="P24" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="Q24" s="6"/>
     </row>
     <row r="25" spans="1:17" ht="15.75" customHeight="1">
@@ -10997,7 +11695,9 @@
       <c r="M26" s="6"/>
       <c r="N26" s="7"/>
       <c r="O26" s="8"/>
-      <c r="P26" s="7"/>
+      <c r="P26" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="Q26" s="6"/>
     </row>
     <row r="27" spans="1:17" ht="39" customHeight="1">
@@ -11115,7 +11815,9 @@
       <c r="M30" s="6"/>
       <c r="N30" s="7"/>
       <c r="O30" s="8"/>
-      <c r="P30" s="7"/>
+      <c r="P30" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="Q30" s="6"/>
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
@@ -11180,7 +11882,7 @@
       <c r="P32" s="9"/>
       <c r="Q32" s="9"/>
     </row>
-    <row r="33" spans="1:15" ht="405" customHeight="1">
+    <row r="33" spans="1:16" ht="405" customHeight="1">
       <c r="A33" s="4" t="s">
         <v>179</v>
       </c>
@@ -11205,8 +11907,11 @@
       </c>
       <c r="I33" s="4"/>
       <c r="O33" s="10"/>
-    </row>
-    <row r="34" spans="1:15" ht="409.2" customHeight="1">
+      <c r="P33" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="409.2" customHeight="1">
       <c r="A34" s="4" t="s">
         <v>185</v>
       </c>
@@ -11231,8 +11936,11 @@
       </c>
       <c r="I34" s="4"/>
       <c r="O34" s="10"/>
-    </row>
-    <row r="35" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P34" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="15.75" customHeight="1">
       <c r="A35" s="4" t="s">
         <v>189</v>
       </c>
@@ -11256,7 +11964,7 @@
       <c r="I35" s="4"/>
       <c r="O35" s="10"/>
     </row>
-    <row r="36" spans="1:15" ht="15.75" customHeight="1">
+    <row r="36" spans="1:16" ht="15.75" customHeight="1">
       <c r="A36" s="4" t="s">
         <v>193</v>
       </c>
@@ -11280,7 +11988,7 @@
       <c r="I36" s="4"/>
       <c r="O36" s="10"/>
     </row>
-    <row r="37" spans="1:15" ht="15.75" customHeight="1">
+    <row r="37" spans="1:16" ht="15.75" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>197</v>
       </c>
@@ -11304,7 +12012,7 @@
       <c r="I37" s="4"/>
       <c r="O37" s="10"/>
     </row>
-    <row r="38" spans="1:15" ht="15.75" customHeight="1">
+    <row r="38" spans="1:16" ht="15.75" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>201</v>
       </c>
@@ -11328,7 +12036,7 @@
       <c r="I38" s="4"/>
       <c r="O38" s="10"/>
     </row>
-    <row r="39" spans="1:15" ht="15.75" customHeight="1">
+    <row r="39" spans="1:16" ht="15.75" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>206</v>
       </c>
@@ -11353,8 +12061,11 @@
       </c>
       <c r="I39" s="4"/>
       <c r="O39" s="10"/>
-    </row>
-    <row r="40" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P39" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="15.75" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>211</v>
       </c>
@@ -11379,8 +12090,11 @@
       </c>
       <c r="I40" s="4"/>
       <c r="O40" s="10"/>
-    </row>
-    <row r="41" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P40" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="15.75" customHeight="1">
       <c r="A41" s="4" t="s">
         <v>216</v>
       </c>
@@ -11405,8 +12119,11 @@
       </c>
       <c r="I41" s="4"/>
       <c r="O41" s="10"/>
-    </row>
-    <row r="42" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P41" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="15.75" customHeight="1">
       <c r="A42" s="4" t="s">
         <v>221</v>
       </c>
@@ -11422,13 +12139,20 @@
       <c r="E42" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="F42" s="5"/>
+      <c r="F42" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
+      <c r="H42" s="4" t="s">
+        <v>1484</v>
+      </c>
       <c r="I42" s="4"/>
       <c r="O42" s="10"/>
-    </row>
-    <row r="43" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P42" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="15.75" customHeight="1">
       <c r="A43" s="4" t="s">
         <v>226</v>
       </c>
@@ -11444,13 +12168,20 @@
       <c r="E43" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="F43" s="5"/>
+      <c r="F43" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
+      <c r="H43" s="4" t="s">
+        <v>1485</v>
+      </c>
       <c r="I43" s="4"/>
       <c r="O43" s="10"/>
-    </row>
-    <row r="44" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P43" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="15.75" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>231</v>
       </c>
@@ -11466,13 +12197,20 @@
       <c r="E44" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="F44" s="5"/>
+      <c r="F44" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
+      <c r="H44" s="4" t="s">
+        <v>1486</v>
+      </c>
       <c r="I44" s="4"/>
       <c r="O44" s="10"/>
-    </row>
-    <row r="45" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P44" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="15.75" customHeight="1">
       <c r="A45" s="4" t="s">
         <v>236</v>
       </c>
@@ -11488,13 +12226,20 @@
       <c r="E45" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="5"/>
+      <c r="F45" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
+      <c r="H45" s="4" t="s">
+        <v>1487</v>
+      </c>
       <c r="I45" s="4"/>
       <c r="O45" s="10"/>
-    </row>
-    <row r="46" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P45" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="15.75" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>241</v>
       </c>
@@ -11510,13 +12255,20 @@
       <c r="E46" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="F46" s="5"/>
+      <c r="F46" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
+      <c r="H46" s="4" t="s">
+        <v>1488</v>
+      </c>
       <c r="I46" s="4"/>
       <c r="O46" s="10"/>
-    </row>
-    <row r="47" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P46" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="15.75" customHeight="1">
       <c r="A47" s="4" t="s">
         <v>246</v>
       </c>
@@ -11532,13 +12284,20 @@
       <c r="E47" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="F47" s="5"/>
+      <c r="F47" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
+      <c r="H47" s="4" t="s">
+        <v>1489</v>
+      </c>
       <c r="I47" s="4"/>
       <c r="O47" s="10"/>
-    </row>
-    <row r="48" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P47" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="15.75" customHeight="1">
       <c r="A48" s="4" t="s">
         <v>251</v>
       </c>
@@ -11554,13 +12313,20 @@
       <c r="E48" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="F48" s="5"/>
+      <c r="F48" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
+      <c r="H48" s="4" t="s">
+        <v>1490</v>
+      </c>
       <c r="I48" s="4"/>
       <c r="O48" s="10"/>
-    </row>
-    <row r="49" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P48" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="15.75" customHeight="1">
       <c r="A49" s="4" t="s">
         <v>256</v>
       </c>
@@ -11576,13 +12342,20 @@
       <c r="E49" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="F49" s="5"/>
+      <c r="F49" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
+      <c r="H49" s="4" t="s">
+        <v>1491</v>
+      </c>
       <c r="I49" s="4"/>
       <c r="O49" s="10"/>
-    </row>
-    <row r="50" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P49" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" ht="15.75" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>261</v>
       </c>
@@ -11598,13 +12371,20 @@
       <c r="E50" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="F50" s="5"/>
+      <c r="F50" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
+      <c r="H50" s="4" t="s">
+        <v>1492</v>
+      </c>
       <c r="I50" s="4"/>
       <c r="O50" s="10"/>
-    </row>
-    <row r="51" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P50" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" ht="15.75" customHeight="1">
       <c r="A51" s="4" t="s">
         <v>266</v>
       </c>
@@ -11620,13 +12400,20 @@
       <c r="E51" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="F51" s="5"/>
+      <c r="F51" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
+      <c r="H51" s="4" t="s">
+        <v>1493</v>
+      </c>
       <c r="I51" s="4"/>
       <c r="O51" s="10"/>
-    </row>
-    <row r="52" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P51" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="15.75" customHeight="1">
       <c r="A52" s="4" t="s">
         <v>270</v>
       </c>
@@ -11642,13 +12429,20 @@
       <c r="E52" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="F52" s="5"/>
+      <c r="F52" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
+      <c r="H52" s="4" t="s">
+        <v>1434</v>
+      </c>
       <c r="I52" s="4"/>
       <c r="O52" s="10"/>
-    </row>
-    <row r="53" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P52" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="15.75" customHeight="1">
       <c r="A53" s="4" t="s">
         <v>274</v>
       </c>
@@ -11664,13 +12458,20 @@
       <c r="E53" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="F53" s="5"/>
+      <c r="F53" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
+      <c r="H53" s="4" t="s">
+        <v>1435</v>
+      </c>
       <c r="I53" s="4"/>
       <c r="O53" s="10"/>
-    </row>
-    <row r="54" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P53" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15.75" customHeight="1">
       <c r="A54" s="4" t="s">
         <v>278</v>
       </c>
@@ -11686,13 +12487,20 @@
       <c r="E54" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="F54" s="5"/>
+      <c r="F54" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
+      <c r="H54" s="4" t="s">
+        <v>1436</v>
+      </c>
       <c r="I54" s="4"/>
       <c r="O54" s="10"/>
-    </row>
-    <row r="55" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P54" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="15.75" customHeight="1">
       <c r="A55" s="4" t="s">
         <v>283</v>
       </c>
@@ -11708,13 +12516,20 @@
       <c r="E55" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="F55" s="5"/>
+      <c r="F55" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
+      <c r="H55" s="4" t="s">
+        <v>1437</v>
+      </c>
       <c r="I55" s="4"/>
       <c r="O55" s="10"/>
-    </row>
-    <row r="56" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P55" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" ht="15.75" customHeight="1">
       <c r="A56" s="4" t="s">
         <v>287</v>
       </c>
@@ -11730,13 +12545,20 @@
       <c r="E56" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="F56" s="5"/>
+      <c r="F56" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
+      <c r="H56" s="4" t="s">
+        <v>1438</v>
+      </c>
       <c r="I56" s="4"/>
       <c r="O56" s="10"/>
-    </row>
-    <row r="57" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P56" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="15.75" customHeight="1">
       <c r="A57" s="4" t="s">
         <v>291</v>
       </c>
@@ -11752,13 +12574,20 @@
       <c r="E57" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="F57" s="5"/>
+      <c r="F57" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
+      <c r="H57" s="4" t="s">
+        <v>1439</v>
+      </c>
       <c r="I57" s="4"/>
       <c r="O57" s="10"/>
-    </row>
-    <row r="58" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P57" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="15.75" customHeight="1">
       <c r="A58" s="4" t="s">
         <v>295</v>
       </c>
@@ -11774,13 +12603,20 @@
       <c r="E58" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="F58" s="5"/>
+      <c r="F58" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
+      <c r="H58" s="4" t="s">
+        <v>1440</v>
+      </c>
       <c r="I58" s="4"/>
       <c r="O58" s="10"/>
-    </row>
-    <row r="59" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P58" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="15.75" customHeight="1">
       <c r="A59" s="4" t="s">
         <v>299</v>
       </c>
@@ -11796,13 +12632,20 @@
       <c r="E59" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="F59" s="5"/>
+      <c r="F59" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
+      <c r="H59" s="4" t="s">
+        <v>1441</v>
+      </c>
       <c r="I59" s="4"/>
       <c r="O59" s="10"/>
-    </row>
-    <row r="60" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P59" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="15.75" customHeight="1">
       <c r="A60" s="4" t="s">
         <v>303</v>
       </c>
@@ -11818,13 +12661,20 @@
       <c r="E60" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="F60" s="5"/>
+      <c r="F60" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
+      <c r="H60" s="4" t="s">
+        <v>1442</v>
+      </c>
       <c r="I60" s="4"/>
       <c r="O60" s="10"/>
-    </row>
-    <row r="61" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P60" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="15.75" customHeight="1">
       <c r="A61" s="4" t="s">
         <v>307</v>
       </c>
@@ -11840,13 +12690,20 @@
       <c r="E61" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="F61" s="5"/>
+      <c r="F61" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
+      <c r="H61" s="4" t="s">
+        <v>1443</v>
+      </c>
       <c r="I61" s="4"/>
       <c r="O61" s="10"/>
-    </row>
-    <row r="62" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P61" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="15.75" customHeight="1">
       <c r="A62" s="4" t="s">
         <v>312</v>
       </c>
@@ -11862,13 +12719,20 @@
       <c r="E62" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="F62" s="5"/>
+      <c r="F62" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
+      <c r="H62" s="4" t="s">
+        <v>1444</v>
+      </c>
       <c r="I62" s="4"/>
       <c r="O62" s="10"/>
-    </row>
-    <row r="63" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P62" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="15.75" customHeight="1">
       <c r="A63" s="4" t="s">
         <v>317</v>
       </c>
@@ -11884,13 +12748,20 @@
       <c r="E63" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="F63" s="5"/>
+      <c r="F63" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
+      <c r="H63" s="4" t="s">
+        <v>1445</v>
+      </c>
       <c r="I63" s="4"/>
       <c r="O63" s="10"/>
-    </row>
-    <row r="64" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P63" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="15.75" customHeight="1">
       <c r="A64" s="4" t="s">
         <v>321</v>
       </c>
@@ -11906,11 +12777,18 @@
       <c r="E64" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="F64" s="5"/>
+      <c r="F64" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
+      <c r="H64" s="4" t="s">
+        <v>1446</v>
+      </c>
       <c r="I64" s="4"/>
       <c r="O64" s="10"/>
+      <c r="P64" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="65" spans="1:15" ht="15.75" customHeight="1">
       <c r="A65" s="4" t="s">
@@ -11928,11 +12806,18 @@
       <c r="E65" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="F65" s="5"/>
+      <c r="F65" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
+      <c r="H65" s="4" t="s">
+        <v>1447</v>
+      </c>
       <c r="I65" s="4"/>
       <c r="O65" s="10"/>
+      <c r="P65" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="66" spans="1:15" ht="15.75" customHeight="1">
       <c r="A66" s="4" t="s">
@@ -11950,11 +12835,18 @@
       <c r="E66" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="F66" s="5"/>
+      <c r="F66" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
+      <c r="H66" s="4" t="s">
+        <v>1448</v>
+      </c>
       <c r="I66" s="4"/>
       <c r="O66" s="10"/>
+      <c r="P66" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="67" spans="1:15" ht="15.75" customHeight="1">
       <c r="A67" s="4" t="s">
@@ -11972,11 +12864,18 @@
       <c r="E67" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="F67" s="5"/>
+      <c r="F67" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
+      <c r="H67" s="4" t="s">
+        <v>1449</v>
+      </c>
       <c r="I67" s="4"/>
       <c r="O67" s="10"/>
+      <c r="P67" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="68" spans="1:15" ht="15.75" customHeight="1">
       <c r="A68" s="4" t="s">
@@ -11994,11 +12893,18 @@
       <c r="E68" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="F68" s="5"/>
+      <c r="F68" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
+      <c r="H68" s="4" t="s">
+        <v>1450</v>
+      </c>
       <c r="I68" s="4"/>
       <c r="O68" s="10"/>
+      <c r="P68" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="69" spans="1:15" ht="15.75" customHeight="1">
       <c r="A69" s="4" t="s">
@@ -12016,11 +12922,18 @@
       <c r="E69" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="F69" s="5"/>
+      <c r="F69" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
+      <c r="H69" s="4" t="s">
+        <v>1451</v>
+      </c>
       <c r="I69" s="4"/>
       <c r="O69" s="10"/>
+      <c r="P69" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="70" spans="1:15" ht="15.75" customHeight="1">
       <c r="A70" s="4" t="s">
@@ -12038,11 +12951,18 @@
       <c r="E70" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="F70" s="5"/>
+      <c r="F70" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
+      <c r="H70" s="4" t="s">
+        <v>1452</v>
+      </c>
       <c r="I70" s="4"/>
       <c r="O70" s="10"/>
+      <c r="P70" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="71" spans="1:15" ht="15.75" customHeight="1">
       <c r="A71" s="4" t="s">
@@ -12060,11 +12980,18 @@
       <c r="E71" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="F71" s="5"/>
+      <c r="F71" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
+      <c r="H71" s="4" t="s">
+        <v>1453</v>
+      </c>
       <c r="I71" s="4"/>
       <c r="O71" s="10"/>
+      <c r="P71" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="72" spans="1:15" ht="15.75" customHeight="1">
       <c r="A72" s="4" t="s">
@@ -12082,11 +13009,18 @@
       <c r="E72" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="F72" s="5"/>
+      <c r="F72" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
+      <c r="H72" s="4" t="s">
+        <v>1454</v>
+      </c>
       <c r="I72" s="4"/>
       <c r="O72" s="10"/>
+      <c r="P72" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="73" spans="1:15" ht="15.75" customHeight="1">
       <c r="A73" s="4" t="s">
@@ -12104,11 +13038,18 @@
       <c r="E73" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="F73" s="5"/>
+      <c r="F73" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
+      <c r="H73" s="4" t="s">
+        <v>1455</v>
+      </c>
       <c r="I73" s="4"/>
       <c r="O73" s="10"/>
+      <c r="P73" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="74" spans="1:15" ht="15.75" customHeight="1">
       <c r="A74" s="4" t="s">
@@ -12126,11 +13067,18 @@
       <c r="E74" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="F74" s="5"/>
+      <c r="F74" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
+      <c r="H74" s="4" t="s">
+        <v>1456</v>
+      </c>
       <c r="I74" s="4"/>
       <c r="O74" s="10"/>
+      <c r="P74" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="75" spans="1:15" ht="15.75" customHeight="1">
       <c r="A75" s="4" t="s">
@@ -12148,11 +13096,18 @@
       <c r="E75" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="F75" s="5"/>
+      <c r="F75" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
+      <c r="H75" s="4" t="s">
+        <v>1457</v>
+      </c>
       <c r="I75" s="4"/>
       <c r="O75" s="10"/>
+      <c r="P75" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="76" spans="1:15" ht="15.75" customHeight="1">
       <c r="A76" s="4" t="s">
@@ -12170,11 +13125,18 @@
       <c r="E76" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="F76" s="5"/>
+      <c r="F76" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
+      <c r="H76" s="4" t="s">
+        <v>1458</v>
+      </c>
       <c r="I76" s="4"/>
       <c r="O76" s="10"/>
+      <c r="P76" s="5" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="77" spans="1:15" ht="15.75" customHeight="1">
       <c r="A77" s="4" t="s">
@@ -12192,11 +13154,18 @@
       <c r="E77" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="F77" s="5"/>
+      <c r="F77" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
+      <c r="H77" s="4" t="s">
+        <v>1459</v>
+      </c>
       <c r="I77" s="4"/>
       <c r="O77" s="10"/>
+      <c r="P77" s="5" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="78" spans="1:15" ht="15.75" customHeight="1">
       <c r="A78" s="4" t="s">
@@ -12214,11 +13183,18 @@
       <c r="E78" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="F78" s="5"/>
+      <c r="F78" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
+      <c r="H78" s="4" t="s">
+        <v>1460</v>
+      </c>
       <c r="I78" s="4"/>
       <c r="O78" s="10"/>
+      <c r="P78" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="79" spans="1:15" ht="15.75" customHeight="1">
       <c r="A79" s="4" t="s">
@@ -12236,11 +13212,18 @@
       <c r="E79" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="F79" s="5"/>
+      <c r="F79" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
+      <c r="H79" s="4" t="s">
+        <v>1461</v>
+      </c>
       <c r="I79" s="4"/>
       <c r="O79" s="10"/>
+      <c r="P79" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="80" spans="1:15" ht="15.75" customHeight="1">
       <c r="A80" s="4" t="s">
@@ -12258,11 +13241,18 @@
       <c r="E80" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="F80" s="5"/>
+      <c r="F80" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G80" s="4"/>
-      <c r="H80" s="4"/>
+      <c r="H80" s="4" t="s">
+        <v>1462</v>
+      </c>
       <c r="I80" s="4"/>
       <c r="O80" s="10"/>
+      <c r="P80" s="5" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="81" spans="1:15" ht="15.75" customHeight="1">
       <c r="A81" s="4" t="s">
@@ -12280,11 +13270,18 @@
       <c r="E81" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="F81" s="5"/>
+      <c r="F81" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G81" s="4"/>
-      <c r="H81" s="4"/>
+      <c r="H81" s="4" t="s">
+        <v>1463</v>
+      </c>
       <c r="I81" s="4"/>
       <c r="O81" s="10"/>
+      <c r="P81" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="82" spans="1:15" ht="15.75" customHeight="1">
       <c r="A82" s="4" t="s">
@@ -12302,11 +13299,18 @@
       <c r="E82" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="F82" s="5"/>
+      <c r="F82" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
+      <c r="H82" s="4" t="s">
+        <v>1464</v>
+      </c>
       <c r="I82" s="4"/>
       <c r="O82" s="10"/>
+      <c r="P82" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="83" spans="1:15" ht="15.75" customHeight="1">
       <c r="A83" s="4" t="s">
@@ -12324,11 +13328,18 @@
       <c r="E83" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="F83" s="5"/>
+      <c r="F83" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G83" s="4"/>
-      <c r="H83" s="4"/>
+      <c r="H83" s="4" t="s">
+        <v>1465</v>
+      </c>
       <c r="I83" s="4"/>
       <c r="O83" s="10"/>
+      <c r="P83" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="84" spans="1:15" ht="15.75" customHeight="1">
       <c r="A84" s="4" t="s">
@@ -12346,11 +13357,18 @@
       <c r="E84" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="F84" s="5"/>
+      <c r="F84" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G84" s="4"/>
-      <c r="H84" s="4"/>
+      <c r="H84" s="4" t="s">
+        <v>1466</v>
+      </c>
       <c r="I84" s="4"/>
       <c r="O84" s="10"/>
+      <c r="P84" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="85" spans="1:15" ht="15.75" customHeight="1">
       <c r="A85" s="4" t="s">
@@ -12368,11 +13386,18 @@
       <c r="E85" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="F85" s="5"/>
+      <c r="F85" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
+      <c r="H85" s="4" t="s">
+        <v>1467</v>
+      </c>
       <c r="I85" s="4"/>
       <c r="O85" s="10"/>
+      <c r="P85" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="86" spans="1:15" ht="15.75" customHeight="1">
       <c r="A86" s="4" t="s">
@@ -12390,11 +13415,18 @@
       <c r="E86" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="F86" s="5"/>
+      <c r="F86" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
+      <c r="H86" s="4" t="s">
+        <v>1468</v>
+      </c>
       <c r="I86" s="4"/>
       <c r="O86" s="10"/>
+      <c r="P86" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="87" spans="1:15" ht="15.75" customHeight="1">
       <c r="A87" s="4" t="s">
@@ -12412,11 +13444,18 @@
       <c r="E87" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="F87" s="5"/>
+      <c r="F87" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
+      <c r="H87" s="4" t="s">
+        <v>1469</v>
+      </c>
       <c r="I87" s="4"/>
       <c r="O87" s="10"/>
+      <c r="P87" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="88" spans="1:15" ht="15.75" customHeight="1">
       <c r="A88" s="4" t="s">
@@ -12434,11 +13473,18 @@
       <c r="E88" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="F88" s="5"/>
+      <c r="F88" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
+      <c r="H88" s="4" t="s">
+        <v>1470</v>
+      </c>
       <c r="I88" s="4"/>
       <c r="O88" s="10"/>
+      <c r="P88" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="89" spans="1:15" ht="15.75" customHeight="1">
       <c r="A89" s="4" t="s">
@@ -12456,11 +13502,18 @@
       <c r="E89" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="F89" s="5"/>
+      <c r="F89" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
+      <c r="H89" s="4" t="s">
+        <v>1471</v>
+      </c>
       <c r="I89" s="4"/>
       <c r="O89" s="10"/>
+      <c r="P89" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="90" spans="1:15" ht="15.75" customHeight="1">
       <c r="A90" s="4" t="s">
@@ -12478,11 +13531,18 @@
       <c r="E90" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="F90" s="5"/>
+      <c r="F90" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
+      <c r="H90" s="4" t="s">
+        <v>1472</v>
+      </c>
       <c r="I90" s="4"/>
       <c r="O90" s="10"/>
+      <c r="P90" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="91" spans="1:15" ht="15.75" customHeight="1">
       <c r="A91" s="4" t="s">
@@ -12500,11 +13560,18 @@
       <c r="E91" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="F91" s="5"/>
+      <c r="F91" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
+      <c r="H91" s="4" t="s">
+        <v>1473</v>
+      </c>
       <c r="I91" s="4"/>
       <c r="O91" s="10"/>
+      <c r="P91" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="92" spans="1:15" ht="22.5" customHeight="1">
       <c r="A92" s="4" t="s">
@@ -12522,11 +13589,18 @@
       <c r="E92" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="F92" s="5"/>
+      <c r="F92" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
+      <c r="H92" s="4" t="s">
+        <v>1474</v>
+      </c>
       <c r="I92" s="4"/>
       <c r="O92" s="10"/>
+      <c r="P92" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="93" spans="1:15" ht="22.5" customHeight="1">
       <c r="A93" s="4" t="s">
@@ -12544,11 +13618,18 @@
       <c r="E93" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="F93" s="5"/>
+      <c r="F93" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
+      <c r="H93" s="4" t="s">
+        <v>1475</v>
+      </c>
       <c r="I93" s="4"/>
       <c r="O93" s="10"/>
+      <c r="P93" s="5" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="94" spans="1:15" ht="22.5" customHeight="1">
       <c r="A94" s="4" t="s">
@@ -12566,11 +13647,18 @@
       <c r="E94" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="F94" s="5"/>
+      <c r="F94" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
+      <c r="H94" s="4" t="s">
+        <v>1476</v>
+      </c>
       <c r="I94" s="4"/>
       <c r="O94" s="10"/>
+      <c r="P94" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="95" spans="1:15" ht="22.5" customHeight="1">
       <c r="A95" s="4" t="s">
@@ -12588,11 +13676,18 @@
       <c r="E95" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="F95" s="5"/>
+      <c r="F95" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
+      <c r="H95" s="4" t="s">
+        <v>1477</v>
+      </c>
       <c r="I95" s="4"/>
       <c r="O95" s="10"/>
+      <c r="P95" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="96" spans="1:15" ht="22.5" customHeight="1">
       <c r="A96" s="4" t="s">
@@ -12610,11 +13705,18 @@
       <c r="E96" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="F96" s="5"/>
+      <c r="F96" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
+      <c r="H96" s="4" t="s">
+        <v>1478</v>
+      </c>
       <c r="I96" s="4"/>
       <c r="O96" s="10"/>
+      <c r="P96" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="97" spans="1:15" ht="22.5" customHeight="1">
       <c r="A97" s="4" t="s">
@@ -12632,11 +13734,18 @@
       <c r="E97" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="F97" s="5"/>
+      <c r="F97" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G97" s="4"/>
-      <c r="H97" s="4"/>
+      <c r="H97" s="4" t="s">
+        <v>1479</v>
+      </c>
       <c r="I97" s="4"/>
       <c r="O97" s="10"/>
+      <c r="P97" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="98" spans="1:15" ht="22.5" customHeight="1">
       <c r="A98" s="4" t="s">
@@ -12654,11 +13763,18 @@
       <c r="E98" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="F98" s="5"/>
+      <c r="F98" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
+      <c r="H98" s="4" t="s">
+        <v>1480</v>
+      </c>
       <c r="I98" s="4"/>
       <c r="O98" s="10"/>
+      <c r="P98" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="99" spans="1:15" ht="22.5" customHeight="1">
       <c r="A99" s="4" t="s">
@@ -12676,11 +13792,18 @@
       <c r="E99" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="F99" s="5"/>
+      <c r="F99" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
+      <c r="H99" s="4" t="s">
+        <v>1481</v>
+      </c>
       <c r="I99" s="4"/>
       <c r="O99" s="10"/>
+      <c r="P99" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="100" spans="1:15" ht="22.5" customHeight="1">
       <c r="A100" s="4" t="s">
@@ -12698,11 +13821,18 @@
       <c r="E100" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="F100" s="5"/>
+      <c r="F100" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
+      <c r="H100" s="4" t="s">
+        <v>1482</v>
+      </c>
       <c r="I100" s="4"/>
       <c r="O100" s="10"/>
+      <c r="P100" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="101" spans="1:15" ht="22.5" customHeight="1">
       <c r="A101" s="4" t="s">
@@ -12720,11 +13850,18 @@
       <c r="E101" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="F101" s="5"/>
+      <c r="F101" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G101" s="4"/>
-      <c r="H101" s="4"/>
+      <c r="H101" s="4" t="s">
+        <v>1483</v>
+      </c>
       <c r="I101" s="4"/>
       <c r="O101" s="10"/>
+      <c r="P101" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="102" spans="1:15" ht="22.5" customHeight="1">
       <c r="A102" s="4" t="s">
@@ -12742,11 +13879,18 @@
       <c r="E102" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="F102" s="5"/>
+      <c r="F102" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G102" s="4"/>
-      <c r="H102" s="4"/>
+      <c r="H102" s="4" t="s">
+        <v>1494</v>
+      </c>
       <c r="I102" s="4"/>
       <c r="O102" s="10"/>
+      <c r="P102" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="103" spans="1:15" ht="22.5" customHeight="1">
       <c r="A103" s="4" t="s">
@@ -12764,11 +13908,18 @@
       <c r="E103" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="F103" s="5"/>
+      <c r="F103" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G103" s="4"/>
-      <c r="H103" s="4"/>
+      <c r="H103" s="4" t="s">
+        <v>1495</v>
+      </c>
       <c r="I103" s="4"/>
       <c r="O103" s="10"/>
+      <c r="P103" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="104" spans="1:15" ht="22.5" customHeight="1">
       <c r="A104" s="4" t="s">
@@ -12786,11 +13937,18 @@
       <c r="E104" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="F104" s="5"/>
+      <c r="F104" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G104" s="4"/>
-      <c r="H104" s="4"/>
+      <c r="H104" s="4" t="s">
+        <v>1496</v>
+      </c>
       <c r="I104" s="4"/>
       <c r="O104" s="10"/>
+      <c r="P104" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="105" spans="1:15" ht="22.5" customHeight="1">
       <c r="A105" s="4" t="s">
@@ -12808,11 +13966,18 @@
       <c r="E105" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="F105" s="5"/>
+      <c r="F105" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G105" s="4"/>
-      <c r="H105" s="4"/>
+      <c r="H105" s="4" t="s">
+        <v>1497</v>
+      </c>
       <c r="I105" s="4"/>
       <c r="O105" s="10"/>
+      <c r="P105" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="106" spans="1:15" ht="22.5" customHeight="1">
       <c r="A106" s="4" t="s">
@@ -12830,11 +13995,18 @@
       <c r="E106" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="F106" s="5"/>
+      <c r="F106" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G106" s="4"/>
-      <c r="H106" s="4"/>
+      <c r="H106" s="4" t="s">
+        <v>1498</v>
+      </c>
       <c r="I106" s="4"/>
       <c r="O106" s="10"/>
+      <c r="P106" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="107" spans="1:15" ht="22.5" customHeight="1">
       <c r="A107" s="4" t="s">
@@ -12852,11 +14024,18 @@
       <c r="E107" s="4" t="s">
         <v>505</v>
       </c>
-      <c r="F107" s="5"/>
+      <c r="F107" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
+      <c r="H107" s="4" t="s">
+        <v>1499</v>
+      </c>
       <c r="I107" s="4"/>
       <c r="O107" s="10"/>
+      <c r="P107" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="108" spans="1:15" ht="22.5" customHeight="1">
       <c r="A108" s="4" t="s">
@@ -12874,11 +14053,18 @@
       <c r="E108" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="F108" s="5"/>
+      <c r="F108" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G108" s="4"/>
-      <c r="H108" s="4"/>
+      <c r="H108" s="4" t="s">
+        <v>1500</v>
+      </c>
       <c r="I108" s="4"/>
       <c r="O108" s="10"/>
+      <c r="P108" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="109" spans="1:15" ht="22.5" customHeight="1">
       <c r="A109" s="4" t="s">
@@ -12896,11 +14082,18 @@
       <c r="E109" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="F109" s="5"/>
+      <c r="F109" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G109" s="4"/>
-      <c r="H109" s="4"/>
+      <c r="H109" s="4" t="s">
+        <v>1501</v>
+      </c>
       <c r="I109" s="4"/>
       <c r="O109" s="10"/>
+      <c r="P109" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="110" spans="1:15" ht="22.5" customHeight="1">
       <c r="A110" s="4" t="s">
@@ -12918,11 +14111,18 @@
       <c r="E110" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="F110" s="5"/>
+      <c r="F110" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G110" s="4"/>
-      <c r="H110" s="4"/>
+      <c r="H110" s="4" t="s">
+        <v>1502</v>
+      </c>
       <c r="I110" s="4"/>
       <c r="O110" s="10"/>
+      <c r="P110" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="111" spans="1:15" ht="22.5" customHeight="1">
       <c r="A111" s="4" t="s">
@@ -12940,11 +14140,18 @@
       <c r="E111" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="F111" s="5"/>
+      <c r="F111" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G111" s="4"/>
-      <c r="H111" s="4"/>
+      <c r="H111" s="4" t="s">
+        <v>1503</v>
+      </c>
       <c r="I111" s="4"/>
       <c r="O111" s="10"/>
+      <c r="P111" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="112" spans="1:15" ht="22.5" customHeight="1">
       <c r="A112" s="4" t="s">
@@ -12962,11 +14169,18 @@
       <c r="E112" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="F112" s="5"/>
+      <c r="F112" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G112" s="4"/>
-      <c r="H112" s="4"/>
+      <c r="H112" s="4" t="s">
+        <v>1504</v>
+      </c>
       <c r="I112" s="4"/>
       <c r="O112" s="10"/>
+      <c r="P112" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="113" spans="1:15" ht="22.5" customHeight="1">
       <c r="A113" s="4" t="s">
@@ -12984,11 +14198,18 @@
       <c r="E113" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="F113" s="5"/>
+      <c r="F113" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G113" s="4"/>
-      <c r="H113" s="4"/>
+      <c r="H113" s="4" t="s">
+        <v>1505</v>
+      </c>
       <c r="I113" s="4"/>
       <c r="O113" s="10"/>
+      <c r="P113" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="114" spans="1:15" ht="22.5" customHeight="1">
       <c r="A114" s="4" t="s">
@@ -13006,11 +14227,18 @@
       <c r="E114" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="F114" s="5"/>
+      <c r="F114" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G114" s="4"/>
-      <c r="H114" s="4"/>
+      <c r="H114" s="4" t="s">
+        <v>1506</v>
+      </c>
       <c r="I114" s="4"/>
       <c r="O114" s="10"/>
+      <c r="P114" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="115" spans="1:15" ht="22.5" customHeight="1">
       <c r="A115" s="4" t="s">
@@ -13028,11 +14256,18 @@
       <c r="E115" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="F115" s="5"/>
+      <c r="F115" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G115" s="4"/>
-      <c r="H115" s="4"/>
+      <c r="H115" s="4" t="s">
+        <v>1507</v>
+      </c>
       <c r="I115" s="4"/>
       <c r="O115" s="10"/>
+      <c r="P115" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="116" spans="1:15" ht="22.5" customHeight="1">
       <c r="A116" s="4" t="s">
@@ -13050,11 +14285,18 @@
       <c r="E116" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="F116" s="5"/>
+      <c r="F116" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G116" s="4"/>
-      <c r="H116" s="4"/>
+      <c r="H116" s="4" t="s">
+        <v>1508</v>
+      </c>
       <c r="I116" s="4"/>
       <c r="O116" s="10"/>
+      <c r="P116" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="117" spans="1:15" ht="22.5" customHeight="1">
       <c r="A117" s="4" t="s">
@@ -13072,11 +14314,18 @@
       <c r="E117" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="F117" s="5"/>
+      <c r="F117" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G117" s="4"/>
-      <c r="H117" s="4"/>
+      <c r="H117" s="4" t="s">
+        <v>1509</v>
+      </c>
       <c r="I117" s="4"/>
       <c r="O117" s="10"/>
+      <c r="P117" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="118" spans="1:15" ht="22.5" customHeight="1">
       <c r="A118" s="4" t="s">
@@ -13094,11 +14343,18 @@
       <c r="E118" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="F118" s="5"/>
+      <c r="F118" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G118" s="4"/>
-      <c r="H118" s="4"/>
+      <c r="H118" s="4" t="s">
+        <v>1510</v>
+      </c>
       <c r="I118" s="4"/>
       <c r="O118" s="10"/>
+      <c r="P118" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="119" spans="1:15" ht="22.5" customHeight="1">
       <c r="A119" s="4" t="s">
@@ -13116,11 +14372,18 @@
       <c r="E119" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="F119" s="5"/>
+      <c r="F119" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G119" s="4"/>
-      <c r="H119" s="4"/>
+      <c r="H119" s="4" t="s">
+        <v>1511</v>
+      </c>
       <c r="I119" s="4"/>
       <c r="O119" s="10"/>
+      <c r="P119" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="120" spans="1:15" ht="22.5" customHeight="1">
       <c r="A120" s="4" t="s">
@@ -13138,11 +14401,18 @@
       <c r="E120" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="F120" s="5"/>
+      <c r="F120" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G120" s="4"/>
-      <c r="H120" s="4"/>
+      <c r="H120" s="4" t="s">
+        <v>1512</v>
+      </c>
       <c r="I120" s="4"/>
       <c r="O120" s="10"/>
+      <c r="P120" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="121" spans="1:15" ht="22.5" customHeight="1">
       <c r="A121" s="4" t="s">
@@ -13160,11 +14430,18 @@
       <c r="E121" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="F121" s="5"/>
+      <c r="F121" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G121" s="4"/>
-      <c r="H121" s="4"/>
+      <c r="H121" s="4" t="s">
+        <v>1513</v>
+      </c>
       <c r="I121" s="4"/>
       <c r="O121" s="10"/>
+      <c r="P121" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="122" spans="1:15" ht="15.75" customHeight="1">
       <c r="A122" s="4" t="s">
@@ -13182,11 +14459,18 @@
       <c r="E122" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="F122" s="5"/>
+      <c r="F122" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G122" s="4"/>
-      <c r="H122" s="4"/>
+      <c r="H122" s="4" t="s">
+        <v>1514</v>
+      </c>
       <c r="I122" s="4"/>
       <c r="O122" s="10"/>
+      <c r="P122" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="123" spans="1:15" ht="15.75" customHeight="1">
       <c r="A123" s="4" t="s">
@@ -13204,11 +14488,18 @@
       <c r="E123" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="F123" s="5"/>
+      <c r="F123" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G123" s="4"/>
-      <c r="H123" s="4"/>
+      <c r="H123" s="4" t="s">
+        <v>1515</v>
+      </c>
       <c r="I123" s="4"/>
       <c r="O123" s="10"/>
+      <c r="P123" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="124" spans="1:15" ht="15.75" customHeight="1">
       <c r="A124" s="4" t="s">
@@ -13226,11 +14517,18 @@
       <c r="E124" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="F124" s="5"/>
+      <c r="F124" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G124" s="4"/>
-      <c r="H124" s="4"/>
+      <c r="H124" s="4" t="s">
+        <v>1516</v>
+      </c>
       <c r="I124" s="4"/>
       <c r="O124" s="10"/>
+      <c r="P124" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="125" spans="1:15" ht="15.75" customHeight="1">
       <c r="A125" s="4" t="s">
@@ -13248,11 +14546,18 @@
       <c r="E125" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="F125" s="5"/>
+      <c r="F125" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G125" s="4"/>
-      <c r="H125" s="4"/>
+      <c r="H125" s="4" t="s">
+        <v>1517</v>
+      </c>
       <c r="I125" s="4"/>
       <c r="O125" s="10"/>
+      <c r="P125" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="126" spans="1:15" ht="15.75" customHeight="1">
       <c r="A126" s="4" t="s">
@@ -13270,11 +14575,18 @@
       <c r="E126" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="F126" s="5"/>
+      <c r="F126" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G126" s="4"/>
-      <c r="H126" s="4"/>
+      <c r="H126" s="4" t="s">
+        <v>1518</v>
+      </c>
       <c r="I126" s="4"/>
       <c r="O126" s="10"/>
+      <c r="P126" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="127" spans="1:15" ht="15.75" customHeight="1">
       <c r="A127" s="4" t="s">
@@ -13292,11 +14604,18 @@
       <c r="E127" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="F127" s="5"/>
+      <c r="F127" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G127" s="4"/>
-      <c r="H127" s="4"/>
+      <c r="H127" s="4" t="s">
+        <v>1519</v>
+      </c>
       <c r="I127" s="4"/>
       <c r="O127" s="10"/>
+      <c r="P127" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="128" spans="1:15" ht="15.75" customHeight="1">
       <c r="A128" s="4" t="s">
@@ -13314,13 +14633,20 @@
       <c r="E128" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="F128" s="5"/>
+      <c r="F128" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G128" s="4"/>
-      <c r="H128" s="4"/>
+      <c r="H128" s="4" t="s">
+        <v>1520</v>
+      </c>
       <c r="I128" s="4"/>
       <c r="O128" s="10"/>
-    </row>
-    <row r="129" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P128" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" ht="15.75" customHeight="1">
       <c r="A129" s="4" t="s">
         <v>602</v>
       </c>
@@ -13336,13 +14662,20 @@
       <c r="E129" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="F129" s="5"/>
+      <c r="F129" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G129" s="4"/>
-      <c r="H129" s="4"/>
+      <c r="H129" s="4" t="s">
+        <v>1521</v>
+      </c>
       <c r="I129" s="4"/>
       <c r="O129" s="10"/>
-    </row>
-    <row r="130" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P129" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="15.75" customHeight="1">
       <c r="A130" s="4" t="s">
         <v>606</v>
       </c>
@@ -13358,13 +14691,20 @@
       <c r="E130" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="F130" s="5"/>
+      <c r="F130" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G130" s="4"/>
-      <c r="H130" s="4"/>
+      <c r="H130" s="4" t="s">
+        <v>1522</v>
+      </c>
       <c r="I130" s="4"/>
       <c r="O130" s="10"/>
-    </row>
-    <row r="131" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P130" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" ht="15.75" customHeight="1">
       <c r="A131" s="4" t="s">
         <v>611</v>
       </c>
@@ -13380,13 +14720,20 @@
       <c r="E131" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="F131" s="5"/>
+      <c r="F131" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G131" s="4"/>
-      <c r="H131" s="4"/>
+      <c r="H131" s="4" t="s">
+        <v>1523</v>
+      </c>
       <c r="I131" s="4"/>
       <c r="O131" s="10"/>
-    </row>
-    <row r="132" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P131" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" ht="15.75" customHeight="1">
       <c r="A132" s="4" t="s">
         <v>616</v>
       </c>
@@ -13404,11 +14751,16 @@
       </c>
       <c r="F132" s="5"/>
       <c r="G132" s="4"/>
-      <c r="H132" s="4"/>
+      <c r="H132" s="4" t="s">
+        <v>1524</v>
+      </c>
       <c r="I132" s="4"/>
       <c r="O132" s="10"/>
-    </row>
-    <row r="133" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P132" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" ht="15.75" customHeight="1">
       <c r="A133" s="4" t="s">
         <v>621</v>
       </c>
@@ -13426,11 +14778,16 @@
       </c>
       <c r="F133" s="5"/>
       <c r="G133" s="4"/>
-      <c r="H133" s="4"/>
+      <c r="H133" s="4" t="s">
+        <v>1525</v>
+      </c>
       <c r="I133" s="4"/>
       <c r="O133" s="10"/>
-    </row>
-    <row r="134" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P133" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" ht="15.75" customHeight="1">
       <c r="A134" s="4" t="s">
         <v>626</v>
       </c>
@@ -13448,11 +14805,16 @@
       </c>
       <c r="F134" s="5"/>
       <c r="G134" s="4"/>
-      <c r="H134" s="4"/>
+      <c r="H134" s="4" t="s">
+        <v>1526</v>
+      </c>
       <c r="I134" s="4"/>
       <c r="O134" s="10"/>
-    </row>
-    <row r="135" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P134" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" ht="15.75" customHeight="1">
       <c r="A135" s="4" t="s">
         <v>631</v>
       </c>
@@ -13470,11 +14832,16 @@
       </c>
       <c r="F135" s="5"/>
       <c r="G135" s="4"/>
-      <c r="H135" s="4"/>
+      <c r="H135" s="4" t="s">
+        <v>1527</v>
+      </c>
       <c r="I135" s="4"/>
       <c r="O135" s="10"/>
-    </row>
-    <row r="136" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P135" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" ht="15.75" customHeight="1">
       <c r="A136" s="4" t="s">
         <v>636</v>
       </c>
@@ -13492,11 +14859,16 @@
       </c>
       <c r="F136" s="5"/>
       <c r="G136" s="4"/>
-      <c r="H136" s="4"/>
+      <c r="H136" s="4" t="s">
+        <v>1528</v>
+      </c>
       <c r="I136" s="4"/>
       <c r="O136" s="10"/>
-    </row>
-    <row r="137" spans="1:15" ht="22.5" customHeight="1">
+      <c r="P136" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" ht="22.5" customHeight="1">
       <c r="A137" s="4" t="s">
         <v>641</v>
       </c>
@@ -13514,11 +14886,16 @@
       </c>
       <c r="F137" s="5"/>
       <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
+      <c r="H137" s="4" t="s">
+        <v>1529</v>
+      </c>
       <c r="I137" s="4"/>
       <c r="O137" s="10"/>
-    </row>
-    <row r="138" spans="1:15" ht="22.5" customHeight="1">
+      <c r="P137" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" ht="22.5" customHeight="1">
       <c r="A138" s="4" t="s">
         <v>646</v>
       </c>
@@ -13536,11 +14913,16 @@
       </c>
       <c r="F138" s="5"/>
       <c r="G138" s="4"/>
-      <c r="H138" s="4"/>
+      <c r="H138" s="4" t="s">
+        <v>1530</v>
+      </c>
       <c r="I138" s="4"/>
       <c r="O138" s="10"/>
-    </row>
-    <row r="139" spans="1:15" ht="22.5" customHeight="1">
+      <c r="P138" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" ht="22.5" customHeight="1">
       <c r="A139" s="4" t="s">
         <v>651</v>
       </c>
@@ -13558,11 +14940,16 @@
       </c>
       <c r="F139" s="5"/>
       <c r="G139" s="4"/>
-      <c r="H139" s="4"/>
+      <c r="H139" s="4" t="s">
+        <v>1531</v>
+      </c>
       <c r="I139" s="4"/>
       <c r="O139" s="10"/>
-    </row>
-    <row r="140" spans="1:15" ht="22.5" customHeight="1">
+      <c r="P139" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" ht="22.5" customHeight="1">
       <c r="A140" s="4" t="s">
         <v>656</v>
       </c>
@@ -13580,11 +14967,16 @@
       </c>
       <c r="F140" s="5"/>
       <c r="G140" s="4"/>
-      <c r="H140" s="4"/>
+      <c r="H140" s="4" t="s">
+        <v>1532</v>
+      </c>
       <c r="I140" s="4"/>
       <c r="O140" s="10"/>
-    </row>
-    <row r="141" spans="1:15" ht="22.5" customHeight="1">
+      <c r="P140" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" ht="22.5" customHeight="1">
       <c r="A141" s="4" t="s">
         <v>661</v>
       </c>
@@ -13602,11 +14994,16 @@
       </c>
       <c r="F141" s="5"/>
       <c r="G141" s="4"/>
-      <c r="H141" s="4"/>
+      <c r="H141" s="4" t="s">
+        <v>1533</v>
+      </c>
       <c r="I141" s="4"/>
       <c r="O141" s="10"/>
-    </row>
-    <row r="142" spans="1:15" ht="22.5" customHeight="1">
+      <c r="P141" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" ht="22.5" customHeight="1">
       <c r="A142" s="4" t="s">
         <v>666</v>
       </c>
@@ -13622,13 +15019,20 @@
       <c r="E142" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="F142" s="5"/>
+      <c r="F142" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G142" s="4"/>
-      <c r="H142" s="4"/>
+      <c r="H142" s="4" t="s">
+        <v>1534</v>
+      </c>
       <c r="I142" s="4"/>
       <c r="O142" s="10"/>
-    </row>
-    <row r="143" spans="1:15" ht="22.5" customHeight="1">
+      <c r="P142" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" ht="22.5" customHeight="1">
       <c r="A143" s="4" t="s">
         <v>671</v>
       </c>
@@ -13644,13 +15048,20 @@
       <c r="E143" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="F143" s="5"/>
+      <c r="F143" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G143" s="4"/>
-      <c r="H143" s="4"/>
+      <c r="H143" s="4" t="s">
+        <v>1535</v>
+      </c>
       <c r="I143" s="4"/>
       <c r="O143" s="10"/>
-    </row>
-    <row r="144" spans="1:15" ht="22.5" customHeight="1">
+      <c r="P143" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" ht="22.5" customHeight="1">
       <c r="A144" s="4" t="s">
         <v>676</v>
       </c>
@@ -13666,11 +15077,18 @@
       <c r="E144" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="F144" s="5"/>
+      <c r="F144" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G144" s="4"/>
-      <c r="H144" s="4"/>
+      <c r="H144" s="4" t="s">
+        <v>1536</v>
+      </c>
       <c r="I144" s="4"/>
       <c r="O144" s="10"/>
+      <c r="P144" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="145" spans="1:15" ht="22.5" customHeight="1">
       <c r="A145" s="4" t="s">
@@ -13688,11 +15106,18 @@
       <c r="E145" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="F145" s="5"/>
+      <c r="F145" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G145" s="4"/>
-      <c r="H145" s="4"/>
+      <c r="H145" s="4" t="s">
+        <v>1537</v>
+      </c>
       <c r="I145" s="4"/>
       <c r="O145" s="10"/>
+      <c r="P145" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="146" spans="1:15" ht="22.5" customHeight="1">
       <c r="A146" s="4" t="s">
@@ -13710,11 +15135,18 @@
       <c r="E146" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="F146" s="5"/>
+      <c r="F146" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G146" s="4"/>
-      <c r="H146" s="4"/>
+      <c r="H146" s="4" t="s">
+        <v>1538</v>
+      </c>
       <c r="I146" s="4"/>
       <c r="O146" s="10"/>
+      <c r="P146" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="147" spans="1:15" ht="22.5" customHeight="1">
       <c r="A147" s="4" t="s">
@@ -13732,11 +15164,18 @@
       <c r="E147" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="F147" s="5"/>
+      <c r="F147" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G147" s="4"/>
-      <c r="H147" s="4"/>
+      <c r="H147" s="4" t="s">
+        <v>1539</v>
+      </c>
       <c r="I147" s="4"/>
       <c r="O147" s="10"/>
+      <c r="P147" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="148" spans="1:15" ht="22.5" customHeight="1">
       <c r="A148" s="4" t="s">
@@ -13754,11 +15193,18 @@
       <c r="E148" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="F148" s="5"/>
+      <c r="F148" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G148" s="4"/>
-      <c r="H148" s="4"/>
+      <c r="H148" s="4" t="s">
+        <v>1540</v>
+      </c>
       <c r="I148" s="4"/>
       <c r="O148" s="10"/>
+      <c r="P148" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="149" spans="1:15" ht="22.5" customHeight="1">
       <c r="A149" s="4" t="s">
@@ -13776,11 +15222,18 @@
       <c r="E149" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="F149" s="5"/>
+      <c r="F149" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G149" s="4"/>
-      <c r="H149" s="4"/>
+      <c r="H149" s="4" t="s">
+        <v>1541</v>
+      </c>
       <c r="I149" s="4"/>
       <c r="O149" s="10"/>
+      <c r="P149" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="150" spans="1:15" ht="22.5" customHeight="1">
       <c r="A150" s="4" t="s">
@@ -13798,11 +15251,18 @@
       <c r="E150" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="F150" s="5"/>
+      <c r="F150" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G150" s="4"/>
-      <c r="H150" s="4"/>
+      <c r="H150" s="4" t="s">
+        <v>1542</v>
+      </c>
       <c r="I150" s="4"/>
       <c r="O150" s="10"/>
+      <c r="P150" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="151" spans="1:15" ht="22.5" customHeight="1">
       <c r="A151" s="4" t="s">
@@ -13820,11 +15280,18 @@
       <c r="E151" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="F151" s="5"/>
+      <c r="F151" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G151" s="4"/>
-      <c r="H151" s="4"/>
+      <c r="H151" s="4" t="s">
+        <v>1543</v>
+      </c>
       <c r="I151" s="4"/>
       <c r="O151" s="10"/>
+      <c r="P151" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="152" spans="1:15" ht="22.5" customHeight="1">
       <c r="A152" s="4" t="s">
@@ -13842,11 +15309,18 @@
       <c r="E152" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="F152" s="5"/>
+      <c r="F152" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G152" s="4"/>
-      <c r="H152" s="4"/>
+      <c r="H152" s="4" t="s">
+        <v>1544</v>
+      </c>
       <c r="I152" s="4"/>
       <c r="O152" s="10"/>
+      <c r="P152" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="153" spans="1:15" ht="22.5" customHeight="1">
       <c r="A153" s="4" t="s">
@@ -13864,11 +15338,18 @@
       <c r="E153" s="4" t="s">
         <v>723</v>
       </c>
-      <c r="F153" s="5"/>
+      <c r="F153" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G153" s="4"/>
-      <c r="H153" s="4"/>
+      <c r="H153" s="4" t="s">
+        <v>1545</v>
+      </c>
       <c r="I153" s="4"/>
       <c r="O153" s="10"/>
+      <c r="P153" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="154" spans="1:15" ht="22.5" customHeight="1">
       <c r="A154" s="4" t="s">
@@ -13886,11 +15367,18 @@
       <c r="E154" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="F154" s="5"/>
+      <c r="F154" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G154" s="4"/>
-      <c r="H154" s="4"/>
+      <c r="H154" s="4" t="s">
+        <v>1546</v>
+      </c>
       <c r="I154" s="4"/>
       <c r="O154" s="10"/>
+      <c r="P154" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="155" spans="1:15" ht="22.5" customHeight="1">
       <c r="A155" s="4" t="s">
@@ -13908,11 +15396,18 @@
       <c r="E155" s="4" t="s">
         <v>733</v>
       </c>
-      <c r="F155" s="5"/>
+      <c r="F155" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G155" s="4"/>
-      <c r="H155" s="4"/>
+      <c r="H155" s="4" t="s">
+        <v>1547</v>
+      </c>
       <c r="I155" s="4"/>
       <c r="O155" s="10"/>
+      <c r="P155" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="156" spans="1:15" ht="22.5" customHeight="1">
       <c r="A156" s="4" t="s">
@@ -13930,11 +15425,18 @@
       <c r="E156" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="F156" s="5"/>
+      <c r="F156" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G156" s="4"/>
-      <c r="H156" s="4"/>
+      <c r="H156" s="4" t="s">
+        <v>1548</v>
+      </c>
       <c r="I156" s="4"/>
       <c r="O156" s="10"/>
+      <c r="P156" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="157" spans="1:15" ht="22.5" customHeight="1">
       <c r="A157" s="4" t="s">
@@ -13952,11 +15454,18 @@
       <c r="E157" s="4" t="s">
         <v>743</v>
       </c>
-      <c r="F157" s="5"/>
+      <c r="F157" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G157" s="4"/>
-      <c r="H157" s="4"/>
+      <c r="H157" s="4" t="s">
+        <v>1549</v>
+      </c>
       <c r="I157" s="4"/>
       <c r="O157" s="10"/>
+      <c r="P157" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="158" spans="1:15" ht="22.5" customHeight="1">
       <c r="A158" s="4" t="s">
@@ -13974,11 +15483,18 @@
       <c r="E158" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="F158" s="5"/>
+      <c r="F158" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G158" s="4"/>
-      <c r="H158" s="4"/>
+      <c r="H158" s="4" t="s">
+        <v>1550</v>
+      </c>
       <c r="I158" s="4"/>
       <c r="O158" s="10"/>
+      <c r="P158" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="159" spans="1:15" ht="22.5" customHeight="1">
       <c r="A159" s="4" t="s">
@@ -13996,11 +15512,18 @@
       <c r="E159" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="F159" s="5"/>
+      <c r="F159" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G159" s="4"/>
-      <c r="H159" s="4"/>
+      <c r="H159" s="4" t="s">
+        <v>1551</v>
+      </c>
       <c r="I159" s="4"/>
       <c r="O159" s="10"/>
+      <c r="P159" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="160" spans="1:15" ht="22.5" customHeight="1">
       <c r="A160" s="4" t="s">
@@ -14018,11 +15541,18 @@
       <c r="E160" s="4" t="s">
         <v>757</v>
       </c>
-      <c r="F160" s="5"/>
+      <c r="F160" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G160" s="4"/>
-      <c r="H160" s="4"/>
+      <c r="H160" s="4" t="s">
+        <v>1552</v>
+      </c>
       <c r="I160" s="4"/>
       <c r="O160" s="10"/>
+      <c r="P160" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="161" spans="1:15" ht="22.5" customHeight="1">
       <c r="A161" s="4" t="s">
@@ -14040,11 +15570,18 @@
       <c r="E161" s="4" t="s">
         <v>761</v>
       </c>
-      <c r="F161" s="5"/>
+      <c r="F161" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G161" s="4"/>
-      <c r="H161" s="4"/>
+      <c r="H161" s="4" t="s">
+        <v>1553</v>
+      </c>
       <c r="I161" s="4"/>
       <c r="O161" s="10"/>
+      <c r="P161" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="162" spans="1:15" ht="22.5" customHeight="1">
       <c r="A162" s="4" t="s">
@@ -14062,11 +15599,18 @@
       <c r="E162" s="4" t="s">
         <v>765</v>
       </c>
-      <c r="F162" s="5"/>
+      <c r="F162" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G162" s="4"/>
-      <c r="H162" s="4"/>
+      <c r="H162" s="4" t="s">
+        <v>1554</v>
+      </c>
       <c r="I162" s="4"/>
       <c r="O162" s="10"/>
+      <c r="P162" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="163" spans="1:15" ht="22.5" customHeight="1">
       <c r="A163" s="4" t="s">
@@ -14084,11 +15628,18 @@
       <c r="E163" s="4" t="s">
         <v>769</v>
       </c>
-      <c r="F163" s="5"/>
+      <c r="F163" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G163" s="4"/>
-      <c r="H163" s="4"/>
+      <c r="H163" s="4" t="s">
+        <v>1555</v>
+      </c>
       <c r="I163" s="4"/>
       <c r="O163" s="10"/>
+      <c r="P163" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="164" spans="1:15" ht="22.5" customHeight="1">
       <c r="A164" s="4" t="s">
@@ -14106,11 +15657,18 @@
       <c r="E164" s="4" t="s">
         <v>773</v>
       </c>
-      <c r="F164" s="5"/>
+      <c r="F164" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G164" s="4"/>
-      <c r="H164" s="4"/>
+      <c r="H164" s="4" t="s">
+        <v>1556</v>
+      </c>
       <c r="I164" s="4"/>
       <c r="O164" s="10"/>
+      <c r="P164" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="165" spans="1:15" ht="22.5" customHeight="1">
       <c r="A165" s="4" t="s">
@@ -14128,11 +15686,18 @@
       <c r="E165" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="F165" s="5"/>
+      <c r="F165" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G165" s="4"/>
-      <c r="H165" s="4"/>
+      <c r="H165" s="4" t="s">
+        <v>1557</v>
+      </c>
       <c r="I165" s="4"/>
       <c r="O165" s="10"/>
+      <c r="P165" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="166" spans="1:15" ht="22.5" customHeight="1">
       <c r="A166" s="4" t="s">
@@ -14150,11 +15715,18 @@
       <c r="E166" s="4" t="s">
         <v>781</v>
       </c>
-      <c r="F166" s="5"/>
+      <c r="F166" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G166" s="4"/>
-      <c r="H166" s="4"/>
+      <c r="H166" s="4" t="s">
+        <v>1558</v>
+      </c>
       <c r="I166" s="4"/>
       <c r="O166" s="10"/>
+      <c r="P166" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="167" spans="1:15" ht="22.5" customHeight="1">
       <c r="A167" s="4" t="s">
@@ -14172,11 +15744,18 @@
       <c r="E167" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="F167" s="5"/>
+      <c r="F167" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G167" s="4"/>
-      <c r="H167" s="4"/>
+      <c r="H167" s="4" t="s">
+        <v>1559</v>
+      </c>
       <c r="I167" s="4"/>
       <c r="O167" s="10"/>
+      <c r="P167" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="168" spans="1:15" ht="22.5" customHeight="1">
       <c r="A168" s="4" t="s">
@@ -14194,11 +15773,18 @@
       <c r="E168" s="4" t="s">
         <v>791</v>
       </c>
-      <c r="F168" s="5"/>
+      <c r="F168" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G168" s="4"/>
-      <c r="H168" s="4"/>
+      <c r="H168" s="4" t="s">
+        <v>1560</v>
+      </c>
       <c r="I168" s="4"/>
       <c r="O168" s="10"/>
+      <c r="P168" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="169" spans="1:15" ht="22.5" customHeight="1">
       <c r="A169" s="4" t="s">
@@ -14216,11 +15802,18 @@
       <c r="E169" s="4" t="s">
         <v>796</v>
       </c>
-      <c r="F169" s="5"/>
+      <c r="F169" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G169" s="4"/>
-      <c r="H169" s="4"/>
+      <c r="H169" s="4" t="s">
+        <v>1561</v>
+      </c>
       <c r="I169" s="4"/>
       <c r="O169" s="10"/>
+      <c r="P169" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="170" spans="1:15" ht="22.5" customHeight="1">
       <c r="A170" s="4" t="s">
@@ -14238,11 +15831,18 @@
       <c r="E170" s="4" t="s">
         <v>801</v>
       </c>
-      <c r="F170" s="5"/>
+      <c r="F170" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G170" s="4"/>
-      <c r="H170" s="4"/>
+      <c r="H170" s="4" t="s">
+        <v>1562</v>
+      </c>
       <c r="I170" s="4"/>
       <c r="O170" s="10"/>
+      <c r="P170" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="171" spans="1:15" ht="22.5" customHeight="1">
       <c r="A171" s="4" t="s">
@@ -14260,11 +15860,18 @@
       <c r="E171" s="4" t="s">
         <v>806</v>
       </c>
-      <c r="F171" s="5"/>
+      <c r="F171" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G171" s="4"/>
-      <c r="H171" s="4"/>
+      <c r="H171" s="4" t="s">
+        <v>1563</v>
+      </c>
       <c r="I171" s="4"/>
       <c r="O171" s="10"/>
+      <c r="P171" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="172" spans="1:15" ht="22.5" customHeight="1">
       <c r="A172" s="4" t="s">
@@ -14282,11 +15889,18 @@
       <c r="E172" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="F172" s="5"/>
+      <c r="F172" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G172" s="4"/>
-      <c r="H172" s="4"/>
+      <c r="H172" s="4" t="s">
+        <v>1564</v>
+      </c>
       <c r="I172" s="4"/>
       <c r="O172" s="10"/>
+      <c r="P172" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="173" spans="1:15" ht="22.5" customHeight="1">
       <c r="A173" s="4" t="s">
@@ -14304,11 +15918,18 @@
       <c r="E173" s="4" t="s">
         <v>816</v>
       </c>
-      <c r="F173" s="5"/>
+      <c r="F173" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G173" s="4"/>
-      <c r="H173" s="4"/>
+      <c r="H173" s="4" t="s">
+        <v>1565</v>
+      </c>
       <c r="I173" s="4"/>
       <c r="O173" s="10"/>
+      <c r="P173" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="174" spans="1:15" ht="22.5" customHeight="1">
       <c r="A174" s="4" t="s">
@@ -14326,11 +15947,18 @@
       <c r="E174" s="4" t="s">
         <v>821</v>
       </c>
-      <c r="F174" s="5"/>
+      <c r="F174" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G174" s="4"/>
-      <c r="H174" s="4"/>
+      <c r="H174" s="4" t="s">
+        <v>1566</v>
+      </c>
       <c r="I174" s="4"/>
       <c r="O174" s="10"/>
+      <c r="P174" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="175" spans="1:15" ht="22.5" customHeight="1">
       <c r="A175" s="4" t="s">
@@ -14348,11 +15976,18 @@
       <c r="E175" s="4" t="s">
         <v>825</v>
       </c>
-      <c r="F175" s="5"/>
+      <c r="F175" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G175" s="4"/>
-      <c r="H175" s="4"/>
+      <c r="H175" s="4" t="s">
+        <v>1567</v>
+      </c>
       <c r="I175" s="4"/>
       <c r="O175" s="10"/>
+      <c r="P175" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="176" spans="1:15" ht="22.5" customHeight="1">
       <c r="A176" s="4" t="s">
@@ -14370,11 +16005,18 @@
       <c r="E176" s="4" t="s">
         <v>830</v>
       </c>
-      <c r="F176" s="5"/>
+      <c r="F176" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G176" s="4"/>
-      <c r="H176" s="4"/>
+      <c r="H176" s="4" t="s">
+        <v>1568</v>
+      </c>
       <c r="I176" s="4"/>
       <c r="O176" s="10"/>
+      <c r="P176" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="177" spans="1:15" ht="22.5" customHeight="1">
       <c r="A177" s="4" t="s">
@@ -14392,11 +16034,18 @@
       <c r="E177" s="4" t="s">
         <v>835</v>
       </c>
-      <c r="F177" s="5"/>
+      <c r="F177" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G177" s="4"/>
-      <c r="H177" s="4"/>
+      <c r="H177" s="4" t="s">
+        <v>1569</v>
+      </c>
       <c r="I177" s="4"/>
       <c r="O177" s="10"/>
+      <c r="P177" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="178" spans="1:15" ht="22.5" customHeight="1">
       <c r="A178" s="4" t="s">
@@ -14414,11 +16063,18 @@
       <c r="E178" s="4" t="s">
         <v>839</v>
       </c>
-      <c r="F178" s="5"/>
+      <c r="F178" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G178" s="4"/>
-      <c r="H178" s="4"/>
+      <c r="H178" s="4" t="s">
+        <v>1570</v>
+      </c>
       <c r="I178" s="4"/>
       <c r="O178" s="10"/>
+      <c r="P178" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="179" spans="1:15" ht="22.5" customHeight="1">
       <c r="A179" s="4" t="s">
@@ -14436,11 +16092,18 @@
       <c r="E179" s="4" t="s">
         <v>843</v>
       </c>
-      <c r="F179" s="5"/>
+      <c r="F179" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G179" s="4"/>
-      <c r="H179" s="4"/>
+      <c r="H179" s="4" t="s">
+        <v>1571</v>
+      </c>
       <c r="I179" s="4"/>
       <c r="O179" s="10"/>
+      <c r="P179" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="180" spans="1:15" ht="22.5" customHeight="1">
       <c r="A180" s="4" t="s">
@@ -14458,11 +16121,18 @@
       <c r="E180" s="4" t="s">
         <v>848</v>
       </c>
-      <c r="F180" s="5"/>
+      <c r="F180" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G180" s="4"/>
-      <c r="H180" s="4"/>
+      <c r="H180" s="4" t="s">
+        <v>1572</v>
+      </c>
       <c r="I180" s="4"/>
       <c r="O180" s="10"/>
+      <c r="P180" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="181" spans="1:15" ht="22.5" customHeight="1">
       <c r="A181" s="4" t="s">
@@ -14480,11 +16150,18 @@
       <c r="E181" s="4" t="s">
         <v>853</v>
       </c>
-      <c r="F181" s="5"/>
+      <c r="F181" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G181" s="4"/>
-      <c r="H181" s="4"/>
+      <c r="H181" s="4" t="s">
+        <v>1573</v>
+      </c>
       <c r="I181" s="4"/>
       <c r="O181" s="10"/>
+      <c r="P181" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="182" spans="1:15" ht="15.75" customHeight="1">
       <c r="A182" s="4" t="s">
@@ -14502,11 +16179,18 @@
       <c r="E182" s="4" t="s">
         <v>858</v>
       </c>
-      <c r="F182" s="5"/>
+      <c r="F182" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G182" s="4"/>
-      <c r="H182" s="4"/>
+      <c r="H182" s="4" t="s">
+        <v>1574</v>
+      </c>
       <c r="I182" s="4"/>
       <c r="O182" s="10"/>
+      <c r="P182" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="183" spans="1:15" ht="15.75" customHeight="1">
       <c r="A183" s="4" t="s">
@@ -14524,11 +16208,18 @@
       <c r="E183" s="4" t="s">
         <v>863</v>
       </c>
-      <c r="F183" s="5"/>
+      <c r="F183" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G183" s="4"/>
-      <c r="H183" s="4"/>
+      <c r="H183" s="4" t="s">
+        <v>1575</v>
+      </c>
       <c r="I183" s="4"/>
       <c r="O183" s="10"/>
+      <c r="P183" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="184" spans="1:15" ht="15.75" customHeight="1">
       <c r="A184" s="4" t="s">
@@ -14546,11 +16237,18 @@
       <c r="E184" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="F184" s="5"/>
+      <c r="F184" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G184" s="4"/>
-      <c r="H184" s="4"/>
+      <c r="H184" s="4" t="s">
+        <v>1576</v>
+      </c>
       <c r="I184" s="4"/>
       <c r="O184" s="10"/>
+      <c r="P184" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="185" spans="1:15" ht="15.75" customHeight="1">
       <c r="A185" s="4" t="s">
@@ -14568,11 +16266,18 @@
       <c r="E185" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="F185" s="5"/>
+      <c r="F185" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G185" s="4"/>
-      <c r="H185" s="4"/>
+      <c r="H185" s="4" t="s">
+        <v>1577</v>
+      </c>
       <c r="I185" s="4"/>
       <c r="O185" s="10"/>
+      <c r="P185" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="186" spans="1:15" ht="15.75" customHeight="1">
       <c r="A186" s="4" t="s">
@@ -14590,11 +16295,18 @@
       <c r="E186" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="F186" s="5"/>
+      <c r="F186" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G186" s="4"/>
-      <c r="H186" s="4"/>
+      <c r="H186" s="4" t="s">
+        <v>1578</v>
+      </c>
       <c r="I186" s="4"/>
       <c r="O186" s="10"/>
+      <c r="P186" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="187" spans="1:15" ht="15.75" customHeight="1">
       <c r="A187" s="4" t="s">
@@ -14612,11 +16324,18 @@
       <c r="E187" s="4" t="s">
         <v>881</v>
       </c>
-      <c r="F187" s="5"/>
+      <c r="F187" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G187" s="4"/>
-      <c r="H187" s="4"/>
+      <c r="H187" s="4" t="s">
+        <v>1579</v>
+      </c>
       <c r="I187" s="4"/>
       <c r="O187" s="10"/>
+      <c r="P187" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="188" spans="1:15" ht="15.75" customHeight="1">
       <c r="A188" s="4" t="s">
@@ -14634,11 +16353,18 @@
       <c r="E188" s="4" t="s">
         <v>886</v>
       </c>
-      <c r="F188" s="5"/>
+      <c r="F188" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G188" s="4"/>
-      <c r="H188" s="4"/>
+      <c r="H188" s="4" t="s">
+        <v>1580</v>
+      </c>
       <c r="I188" s="4"/>
       <c r="O188" s="10"/>
+      <c r="P188" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="189" spans="1:15" ht="15.75" customHeight="1">
       <c r="A189" s="4" t="s">
@@ -14656,11 +16382,18 @@
       <c r="E189" s="4" t="s">
         <v>891</v>
       </c>
-      <c r="F189" s="5"/>
+      <c r="F189" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G189" s="4"/>
-      <c r="H189" s="4"/>
+      <c r="H189" s="4" t="s">
+        <v>1581</v>
+      </c>
       <c r="I189" s="4"/>
       <c r="O189" s="10"/>
+      <c r="P189" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="190" spans="1:15" ht="15.75" customHeight="1">
       <c r="A190" s="4" t="s">
@@ -14678,11 +16411,18 @@
       <c r="E190" s="4" t="s">
         <v>896</v>
       </c>
-      <c r="F190" s="5"/>
+      <c r="F190" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G190" s="4"/>
-      <c r="H190" s="4"/>
+      <c r="H190" s="4" t="s">
+        <v>1582</v>
+      </c>
       <c r="I190" s="4"/>
       <c r="O190" s="10"/>
+      <c r="P190" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="191" spans="1:15" ht="15.75" customHeight="1">
       <c r="A191" s="4" t="s">
@@ -14700,11 +16440,18 @@
       <c r="E191" s="4" t="s">
         <v>901</v>
       </c>
-      <c r="F191" s="5"/>
+      <c r="F191" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G191" s="4"/>
-      <c r="H191" s="4"/>
+      <c r="H191" s="4" t="s">
+        <v>1583</v>
+      </c>
       <c r="I191" s="4"/>
       <c r="O191" s="10"/>
+      <c r="P191" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="192" spans="1:15" ht="15.75" customHeight="1">
       <c r="A192" s="4" t="s">
@@ -14722,11 +16469,18 @@
       <c r="E192" s="4" t="s">
         <v>905</v>
       </c>
-      <c r="F192" s="5"/>
+      <c r="F192" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G192" s="4"/>
-      <c r="H192" s="4"/>
+      <c r="H192" s="4" t="s">
+        <v>1584</v>
+      </c>
       <c r="I192" s="4"/>
       <c r="O192" s="10"/>
+      <c r="P192" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="193" spans="1:15" ht="15.75" customHeight="1">
       <c r="A193" s="4" t="s">
@@ -14744,11 +16498,18 @@
       <c r="E193" s="4" t="s">
         <v>910</v>
       </c>
-      <c r="F193" s="5"/>
+      <c r="F193" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G193" s="4"/>
-      <c r="H193" s="4"/>
+      <c r="H193" s="4" t="s">
+        <v>1585</v>
+      </c>
       <c r="I193" s="4"/>
       <c r="O193" s="10"/>
+      <c r="P193" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="194" spans="1:15" ht="15.75" customHeight="1">
       <c r="A194" s="4" t="s">
@@ -14766,11 +16527,18 @@
       <c r="E194" s="4" t="s">
         <v>915</v>
       </c>
-      <c r="F194" s="5"/>
+      <c r="F194" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G194" s="4"/>
-      <c r="H194" s="4"/>
+      <c r="H194" s="4" t="s">
+        <v>1586</v>
+      </c>
       <c r="I194" s="4"/>
       <c r="O194" s="10"/>
+      <c r="P194" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="195" spans="1:15" ht="15.75" customHeight="1">
       <c r="A195" s="4" t="s">
@@ -14788,11 +16556,18 @@
       <c r="E195" s="4" t="s">
         <v>919</v>
       </c>
-      <c r="F195" s="5"/>
+      <c r="F195" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G195" s="4"/>
-      <c r="H195" s="4"/>
+      <c r="H195" s="4" t="s">
+        <v>1587</v>
+      </c>
       <c r="I195" s="4"/>
       <c r="O195" s="10"/>
+      <c r="P195" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="196" spans="1:15" ht="15.75" customHeight="1">
       <c r="A196" s="4" t="s">
@@ -14810,11 +16585,18 @@
       <c r="E196" s="4" t="s">
         <v>924</v>
       </c>
-      <c r="F196" s="5"/>
+      <c r="F196" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G196" s="4"/>
-      <c r="H196" s="4"/>
+      <c r="H196" s="4" t="s">
+        <v>1588</v>
+      </c>
       <c r="I196" s="4"/>
       <c r="O196" s="10"/>
+      <c r="P196" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="197" spans="1:15" ht="22.5" customHeight="1">
       <c r="A197" s="4" t="s">
@@ -14832,11 +16614,18 @@
       <c r="E197" s="4" t="s">
         <v>929</v>
       </c>
-      <c r="F197" s="5"/>
+      <c r="F197" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G197" s="4"/>
-      <c r="H197" s="4"/>
+      <c r="H197" s="4" t="s">
+        <v>1589</v>
+      </c>
       <c r="I197" s="4"/>
       <c r="O197" s="10"/>
+      <c r="P197" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="198" spans="1:15" ht="22.5" customHeight="1">
       <c r="A198" s="4" t="s">
@@ -14854,11 +16643,18 @@
       <c r="E198" s="4" t="s">
         <v>934</v>
       </c>
-      <c r="F198" s="5"/>
+      <c r="F198" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G198" s="4"/>
-      <c r="H198" s="4"/>
+      <c r="H198" s="4" t="s">
+        <v>1590</v>
+      </c>
       <c r="I198" s="4"/>
       <c r="O198" s="10"/>
+      <c r="P198" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="199" spans="1:15" ht="22.5" customHeight="1">
       <c r="A199" s="4" t="s">
@@ -14876,11 +16672,18 @@
       <c r="E199" s="4" t="s">
         <v>938</v>
       </c>
-      <c r="F199" s="5"/>
+      <c r="F199" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G199" s="4"/>
-      <c r="H199" s="4"/>
+      <c r="H199" s="4" t="s">
+        <v>1591</v>
+      </c>
       <c r="I199" s="4"/>
       <c r="O199" s="10"/>
+      <c r="P199" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="200" spans="1:15" ht="22.5" customHeight="1">
       <c r="A200" s="4" t="s">
@@ -14898,11 +16701,18 @@
       <c r="E200" s="4" t="s">
         <v>943</v>
       </c>
-      <c r="F200" s="5"/>
+      <c r="F200" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G200" s="4"/>
-      <c r="H200" s="4"/>
+      <c r="H200" s="4" t="s">
+        <v>1592</v>
+      </c>
       <c r="I200" s="4"/>
       <c r="O200" s="10"/>
+      <c r="P200" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="201" spans="1:15" ht="22.5" customHeight="1">
       <c r="A201" s="4" t="s">
@@ -14920,11 +16730,18 @@
       <c r="E201" s="4" t="s">
         <v>948</v>
       </c>
-      <c r="F201" s="5"/>
+      <c r="F201" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G201" s="4"/>
-      <c r="H201" s="4"/>
+      <c r="H201" s="4" t="s">
+        <v>1593</v>
+      </c>
       <c r="I201" s="4"/>
       <c r="O201" s="10"/>
+      <c r="P201" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="202" spans="1:15" ht="22.5" customHeight="1">
       <c r="A202" s="4" t="s">
@@ -14944,9 +16761,14 @@
       </c>
       <c r="F202" s="5"/>
       <c r="G202" s="4"/>
-      <c r="H202" s="4"/>
+      <c r="H202" s="4" t="s">
+        <v>1594</v>
+      </c>
       <c r="I202" s="4"/>
       <c r="O202" s="10"/>
+      <c r="P202" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="203" spans="1:15" ht="22.5" customHeight="1">
       <c r="A203" s="4" t="s">
@@ -14966,9 +16788,14 @@
       </c>
       <c r="F203" s="5"/>
       <c r="G203" s="4"/>
-      <c r="H203" s="4"/>
+      <c r="H203" s="4" t="s">
+        <v>1595</v>
+      </c>
       <c r="I203" s="4"/>
       <c r="O203" s="10"/>
+      <c r="P203" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="204" spans="1:15" ht="22.5" customHeight="1">
       <c r="A204" s="4" t="s">
@@ -14988,9 +16815,14 @@
       </c>
       <c r="F204" s="5"/>
       <c r="G204" s="4"/>
-      <c r="H204" s="4"/>
+      <c r="H204" s="4" t="s">
+        <v>1596</v>
+      </c>
       <c r="I204" s="4"/>
       <c r="O204" s="10"/>
+      <c r="P204" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="205" spans="1:15" ht="22.5" customHeight="1">
       <c r="A205" s="4" t="s">
@@ -15010,9 +16842,14 @@
       </c>
       <c r="F205" s="5"/>
       <c r="G205" s="4"/>
-      <c r="H205" s="4"/>
+      <c r="H205" s="4" t="s">
+        <v>1597</v>
+      </c>
       <c r="I205" s="4"/>
       <c r="O205" s="10"/>
+      <c r="P205" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="206" spans="1:15" ht="22.5" customHeight="1">
       <c r="A206" s="4" t="s">
@@ -15032,9 +16869,14 @@
       </c>
       <c r="F206" s="5"/>
       <c r="G206" s="4"/>
-      <c r="H206" s="4"/>
+      <c r="H206" s="4" t="s">
+        <v>1598</v>
+      </c>
       <c r="I206" s="4"/>
       <c r="O206" s="10"/>
+      <c r="P206" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="207" spans="1:15" ht="22.5" customHeight="1">
       <c r="A207" s="4" t="s">
@@ -15054,9 +16896,14 @@
       </c>
       <c r="F207" s="5"/>
       <c r="G207" s="4"/>
-      <c r="H207" s="4"/>
+      <c r="H207" s="4" t="s">
+        <v>1599</v>
+      </c>
       <c r="I207" s="4"/>
       <c r="O207" s="10"/>
+      <c r="P207" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="208" spans="1:15" ht="22.5" customHeight="1">
       <c r="A208" s="4" t="s">
@@ -15076,9 +16923,14 @@
       </c>
       <c r="F208" s="5"/>
       <c r="G208" s="4"/>
-      <c r="H208" s="4"/>
+      <c r="H208" s="4" t="s">
+        <v>1600</v>
+      </c>
       <c r="I208" s="4"/>
       <c r="O208" s="10"/>
+      <c r="P208" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="209" spans="1:15" ht="22.5" customHeight="1">
       <c r="A209" s="4" t="s">
@@ -15098,9 +16950,14 @@
       </c>
       <c r="F209" s="5"/>
       <c r="G209" s="4"/>
-      <c r="H209" s="4"/>
+      <c r="H209" s="4" t="s">
+        <v>1601</v>
+      </c>
       <c r="I209" s="4"/>
       <c r="O209" s="10"/>
+      <c r="P209" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="210" spans="1:15" ht="22.5" customHeight="1">
       <c r="A210" s="4" t="s">
@@ -15120,9 +16977,14 @@
       </c>
       <c r="F210" s="5"/>
       <c r="G210" s="4"/>
-      <c r="H210" s="4"/>
+      <c r="H210" s="4" t="s">
+        <v>1602</v>
+      </c>
       <c r="I210" s="4"/>
       <c r="O210" s="10"/>
+      <c r="P210" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="211" spans="1:15" ht="22.5" customHeight="1">
       <c r="A211" s="4" t="s">
@@ -15142,9 +17004,14 @@
       </c>
       <c r="F211" s="5"/>
       <c r="G211" s="4"/>
-      <c r="H211" s="4"/>
+      <c r="H211" s="4" t="s">
+        <v>1603</v>
+      </c>
       <c r="I211" s="4"/>
       <c r="O211" s="10"/>
+      <c r="P211" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="212" spans="1:15" ht="22.5" customHeight="1">
       <c r="A212" s="4" t="s">
@@ -15164,9 +17031,14 @@
       </c>
       <c r="F212" s="5"/>
       <c r="G212" s="4"/>
-      <c r="H212" s="4"/>
+      <c r="H212" s="4" t="s">
+        <v>1604</v>
+      </c>
       <c r="I212" s="4"/>
       <c r="O212" s="10"/>
+      <c r="P212" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="213" spans="1:15" ht="22.5" customHeight="1">
       <c r="A213" s="4" t="s">
@@ -15186,9 +17058,14 @@
       </c>
       <c r="F213" s="5"/>
       <c r="G213" s="4"/>
-      <c r="H213" s="4"/>
+      <c r="H213" s="4" t="s">
+        <v>1605</v>
+      </c>
       <c r="I213" s="4"/>
       <c r="O213" s="10"/>
+      <c r="P213" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="214" spans="1:15" ht="22.5" customHeight="1">
       <c r="A214" s="4" t="s">
@@ -15208,9 +17085,14 @@
       </c>
       <c r="F214" s="5"/>
       <c r="G214" s="4"/>
-      <c r="H214" s="4"/>
+      <c r="H214" s="4" t="s">
+        <v>1606</v>
+      </c>
       <c r="I214" s="4"/>
       <c r="O214" s="10"/>
+      <c r="P214" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="215" spans="1:15" ht="22.5" customHeight="1">
       <c r="A215" s="4" t="s">
@@ -15230,9 +17112,14 @@
       </c>
       <c r="F215" s="5"/>
       <c r="G215" s="4"/>
-      <c r="H215" s="4"/>
+      <c r="H215" s="4" t="s">
+        <v>1607</v>
+      </c>
       <c r="I215" s="4"/>
       <c r="O215" s="10"/>
+      <c r="P215" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="216" spans="1:15" ht="22.5" customHeight="1">
       <c r="A216" s="4" t="s">
@@ -15252,9 +17139,14 @@
       </c>
       <c r="F216" s="5"/>
       <c r="G216" s="4"/>
-      <c r="H216" s="4"/>
+      <c r="H216" s="4" t="s">
+        <v>1608</v>
+      </c>
       <c r="I216" s="4"/>
       <c r="O216" s="10"/>
+      <c r="P216" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="217" spans="1:15" ht="22.5" customHeight="1">
       <c r="A217" s="4" t="s">
@@ -15274,9 +17166,14 @@
       </c>
       <c r="F217" s="5"/>
       <c r="G217" s="4"/>
-      <c r="H217" s="4"/>
+      <c r="H217" s="4" t="s">
+        <v>1609</v>
+      </c>
       <c r="I217" s="4"/>
       <c r="O217" s="10"/>
+      <c r="P217" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="218" spans="1:15" ht="22.5" customHeight="1">
       <c r="A218" s="4" t="s">
@@ -15296,9 +17193,14 @@
       </c>
       <c r="F218" s="5"/>
       <c r="G218" s="4"/>
-      <c r="H218" s="4"/>
+      <c r="H218" s="4" t="s">
+        <v>1610</v>
+      </c>
       <c r="I218" s="4"/>
       <c r="O218" s="10"/>
+      <c r="P218" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="219" spans="1:15" ht="22.5" customHeight="1">
       <c r="A219" s="4" t="s">
@@ -15318,9 +17220,14 @@
       </c>
       <c r="F219" s="5"/>
       <c r="G219" s="4"/>
-      <c r="H219" s="4"/>
+      <c r="H219" s="4" t="s">
+        <v>1611</v>
+      </c>
       <c r="I219" s="4"/>
       <c r="O219" s="10"/>
+      <c r="P219" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="220" spans="1:15" ht="22.5" customHeight="1">
       <c r="A220" s="4" t="s">
@@ -15340,9 +17247,14 @@
       </c>
       <c r="F220" s="5"/>
       <c r="G220" s="4"/>
-      <c r="H220" s="4"/>
+      <c r="H220" s="4" t="s">
+        <v>1612</v>
+      </c>
       <c r="I220" s="4"/>
       <c r="O220" s="10"/>
+      <c r="P220" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="221" spans="1:15" ht="22.5" customHeight="1">
       <c r="A221" s="4" t="s">
@@ -15362,9 +17274,14 @@
       </c>
       <c r="F221" s="5"/>
       <c r="G221" s="4"/>
-      <c r="H221" s="4"/>
+      <c r="H221" s="4" t="s">
+        <v>1613</v>
+      </c>
       <c r="I221" s="4"/>
       <c r="O221" s="10"/>
+      <c r="P221" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="222" spans="1:15" ht="22.5" customHeight="1">
       <c r="A222" s="4" t="s">
@@ -15384,9 +17301,14 @@
       </c>
       <c r="F222" s="5"/>
       <c r="G222" s="4"/>
-      <c r="H222" s="4"/>
+      <c r="H222" s="4" t="s">
+        <v>1614</v>
+      </c>
       <c r="I222" s="4"/>
       <c r="O222" s="10"/>
+      <c r="P222" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="223" spans="1:15" ht="22.5" customHeight="1">
       <c r="A223" s="4" t="s">
@@ -15406,9 +17328,14 @@
       </c>
       <c r="F223" s="5"/>
       <c r="G223" s="4"/>
-      <c r="H223" s="4"/>
+      <c r="H223" s="4" t="s">
+        <v>1615</v>
+      </c>
       <c r="I223" s="4"/>
       <c r="O223" s="10"/>
+      <c r="P223" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="224" spans="1:15" ht="22.5" customHeight="1">
       <c r="A224" s="4" t="s">
@@ -15428,9 +17355,14 @@
       </c>
       <c r="F224" s="5"/>
       <c r="G224" s="4"/>
-      <c r="H224" s="4"/>
+      <c r="H224" s="4" t="s">
+        <v>1616</v>
+      </c>
       <c r="I224" s="4"/>
       <c r="O224" s="10"/>
+      <c r="P224" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="225" spans="1:15" ht="22.5" customHeight="1">
       <c r="A225" s="4" t="s">
@@ -15450,9 +17382,14 @@
       </c>
       <c r="F225" s="5"/>
       <c r="G225" s="4"/>
-      <c r="H225" s="4"/>
+      <c r="H225" s="4" t="s">
+        <v>1617</v>
+      </c>
       <c r="I225" s="4"/>
       <c r="O225" s="10"/>
+      <c r="P225" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="226" spans="1:15" ht="22.5" customHeight="1">
       <c r="A226" s="4" t="s">
@@ -15472,9 +17409,14 @@
       </c>
       <c r="F226" s="5"/>
       <c r="G226" s="4"/>
-      <c r="H226" s="4"/>
+      <c r="H226" s="4" t="s">
+        <v>1618</v>
+      </c>
       <c r="I226" s="4"/>
       <c r="O226" s="10"/>
+      <c r="P226" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="227" spans="1:15" ht="22.5" customHeight="1">
       <c r="A227" s="4" t="s">
@@ -15494,9 +17436,14 @@
       </c>
       <c r="F227" s="5"/>
       <c r="G227" s="4"/>
-      <c r="H227" s="4"/>
+      <c r="H227" s="4" t="s">
+        <v>1619</v>
+      </c>
       <c r="I227" s="4"/>
       <c r="O227" s="10"/>
+      <c r="P227" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="228" spans="1:15" ht="22.5" customHeight="1">
       <c r="A228" s="4" t="s">
@@ -15516,9 +17463,14 @@
       </c>
       <c r="F228" s="5"/>
       <c r="G228" s="4"/>
-      <c r="H228" s="4"/>
+      <c r="H228" s="4" t="s">
+        <v>1620</v>
+      </c>
       <c r="I228" s="4"/>
       <c r="O228" s="10"/>
+      <c r="P228" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="229" spans="1:15" ht="22.5" customHeight="1">
       <c r="A229" s="4" t="s">
@@ -15538,9 +17490,14 @@
       </c>
       <c r="F229" s="5"/>
       <c r="G229" s="4"/>
-      <c r="H229" s="4"/>
+      <c r="H229" s="4" t="s">
+        <v>1621</v>
+      </c>
       <c r="I229" s="4"/>
       <c r="O229" s="10"/>
+      <c r="P229" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="230" spans="1:15" ht="22.5" customHeight="1">
       <c r="A230" s="4" t="s">
@@ -15560,9 +17517,14 @@
       </c>
       <c r="F230" s="5"/>
       <c r="G230" s="4"/>
-      <c r="H230" s="4"/>
+      <c r="H230" s="4" t="s">
+        <v>1622</v>
+      </c>
       <c r="I230" s="4"/>
       <c r="O230" s="10"/>
+      <c r="P230" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="231" spans="1:15" ht="22.5" customHeight="1">
       <c r="A231" s="4" t="s">
@@ -15582,9 +17544,14 @@
       </c>
       <c r="F231" s="5"/>
       <c r="G231" s="4"/>
-      <c r="H231" s="4"/>
+      <c r="H231" s="4" t="s">
+        <v>1623</v>
+      </c>
       <c r="I231" s="4"/>
       <c r="O231" s="10"/>
+      <c r="P231" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="232" spans="1:15" ht="22.5" customHeight="1">
       <c r="A232" s="4" t="s">
@@ -15604,9 +17571,14 @@
       </c>
       <c r="F232" s="5"/>
       <c r="G232" s="4"/>
-      <c r="H232" s="4"/>
+      <c r="H232" s="4" t="s">
+        <v>1624</v>
+      </c>
       <c r="I232" s="4"/>
       <c r="O232" s="10"/>
+      <c r="P232" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="233" spans="1:15" ht="22.5" customHeight="1">
       <c r="A233" s="4" t="s">
@@ -15626,9 +17598,14 @@
       </c>
       <c r="F233" s="5"/>
       <c r="G233" s="4"/>
-      <c r="H233" s="4"/>
+      <c r="H233" s="4" t="s">
+        <v>1625</v>
+      </c>
       <c r="I233" s="4"/>
       <c r="O233" s="10"/>
+      <c r="P233" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="234" spans="1:15" ht="22.5" customHeight="1">
       <c r="A234" s="4" t="s">
@@ -15648,9 +17625,14 @@
       </c>
       <c r="F234" s="5"/>
       <c r="G234" s="4"/>
-      <c r="H234" s="4"/>
+      <c r="H234" s="4" t="s">
+        <v>1626</v>
+      </c>
       <c r="I234" s="4"/>
       <c r="O234" s="10"/>
+      <c r="P234" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="235" spans="1:15" ht="22.5" customHeight="1">
       <c r="A235" s="4" t="s">
@@ -15670,9 +17652,14 @@
       </c>
       <c r="F235" s="5"/>
       <c r="G235" s="4"/>
-      <c r="H235" s="4"/>
+      <c r="H235" s="4" t="s">
+        <v>1627</v>
+      </c>
       <c r="I235" s="4"/>
       <c r="O235" s="10"/>
+      <c r="P235" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="236" spans="1:15" ht="22.5" customHeight="1">
       <c r="A236" s="4" t="s">
@@ -15692,9 +17679,14 @@
       </c>
       <c r="F236" s="5"/>
       <c r="G236" s="4"/>
-      <c r="H236" s="4"/>
+      <c r="H236" s="4" t="s">
+        <v>1628</v>
+      </c>
       <c r="I236" s="4"/>
       <c r="O236" s="10"/>
+      <c r="P236" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="237" spans="1:15" ht="22.5" customHeight="1">
       <c r="A237" s="4" t="s">
@@ -15714,9 +17706,14 @@
       </c>
       <c r="F237" s="5"/>
       <c r="G237" s="4"/>
-      <c r="H237" s="4"/>
+      <c r="H237" s="4" t="s">
+        <v>1629</v>
+      </c>
       <c r="I237" s="4"/>
       <c r="O237" s="10"/>
+      <c r="P237" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="238" spans="1:15" ht="22.5" customHeight="1">
       <c r="A238" s="4" t="s">
@@ -15736,9 +17733,14 @@
       </c>
       <c r="F238" s="5"/>
       <c r="G238" s="4"/>
-      <c r="H238" s="4"/>
+      <c r="H238" s="4" t="s">
+        <v>1630</v>
+      </c>
       <c r="I238" s="4"/>
       <c r="O238" s="10"/>
+      <c r="P238" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="239" spans="1:15" ht="22.5" customHeight="1">
       <c r="A239" s="4" t="s">
@@ -15758,9 +17760,14 @@
       </c>
       <c r="F239" s="5"/>
       <c r="G239" s="4"/>
-      <c r="H239" s="4"/>
+      <c r="H239" s="4" t="s">
+        <v>1631</v>
+      </c>
       <c r="I239" s="4"/>
       <c r="O239" s="10"/>
+      <c r="P239" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="240" spans="1:15" ht="22.5" customHeight="1">
       <c r="A240" s="4" t="s">
@@ -15780,9 +17787,14 @@
       </c>
       <c r="F240" s="5"/>
       <c r="G240" s="4"/>
-      <c r="H240" s="4"/>
+      <c r="H240" s="4" t="s">
+        <v>1632</v>
+      </c>
       <c r="I240" s="4"/>
       <c r="O240" s="10"/>
+      <c r="P240" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="241" spans="1:15" ht="22.5" customHeight="1">
       <c r="A241" s="4" t="s">
@@ -15802,9 +17814,14 @@
       </c>
       <c r="F241" s="5"/>
       <c r="G241" s="4"/>
-      <c r="H241" s="4"/>
+      <c r="H241" s="4" t="s">
+        <v>1633</v>
+      </c>
       <c r="I241" s="4"/>
       <c r="O241" s="10"/>
+      <c r="P241" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="242" spans="1:15" ht="22.5" customHeight="1">
       <c r="A242" s="4" t="s">
@@ -15824,9 +17841,14 @@
       </c>
       <c r="F242" s="5"/>
       <c r="G242" s="4"/>
-      <c r="H242" s="4"/>
+      <c r="H242" s="4" t="s">
+        <v>1634</v>
+      </c>
       <c r="I242" s="4"/>
       <c r="O242" s="10"/>
+      <c r="P242" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="243" spans="1:15" ht="22.5" customHeight="1">
       <c r="A243" s="4" t="s">
@@ -15846,9 +17868,14 @@
       </c>
       <c r="F243" s="5"/>
       <c r="G243" s="4"/>
-      <c r="H243" s="4"/>
+      <c r="H243" s="4" t="s">
+        <v>1635</v>
+      </c>
       <c r="I243" s="4"/>
       <c r="O243" s="10"/>
+      <c r="P243" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="244" spans="1:15" ht="22.5" customHeight="1">
       <c r="A244" s="4" t="s">
@@ -15868,9 +17895,14 @@
       </c>
       <c r="F244" s="5"/>
       <c r="G244" s="4"/>
-      <c r="H244" s="4"/>
+      <c r="H244" s="4" t="s">
+        <v>1636</v>
+      </c>
       <c r="I244" s="4"/>
       <c r="O244" s="10"/>
+      <c r="P244" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="245" spans="1:15" ht="22.5" customHeight="1">
       <c r="A245" s="4" t="s">
@@ -15890,9 +17922,14 @@
       </c>
       <c r="F245" s="5"/>
       <c r="G245" s="4"/>
-      <c r="H245" s="4"/>
+      <c r="H245" s="4" t="s">
+        <v>1637</v>
+      </c>
       <c r="I245" s="4"/>
       <c r="O245" s="10"/>
+      <c r="P245" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="246" spans="1:15" ht="22.5" customHeight="1">
       <c r="A246" s="4" t="s">
@@ -15912,9 +17949,14 @@
       </c>
       <c r="F246" s="5"/>
       <c r="G246" s="4"/>
-      <c r="H246" s="4"/>
+      <c r="H246" s="4" t="s">
+        <v>1638</v>
+      </c>
       <c r="I246" s="4"/>
       <c r="O246" s="10"/>
+      <c r="P246" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="247" spans="1:15" ht="22.5" customHeight="1">
       <c r="A247" s="4" t="s">
@@ -15934,9 +17976,14 @@
       </c>
       <c r="F247" s="5"/>
       <c r="G247" s="4"/>
-      <c r="H247" s="4"/>
+      <c r="H247" s="4" t="s">
+        <v>1639</v>
+      </c>
       <c r="I247" s="4"/>
       <c r="O247" s="10"/>
+      <c r="P247" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="248" spans="1:15" ht="22.5" customHeight="1">
       <c r="A248" s="4" t="s">
@@ -15956,9 +18003,14 @@
       </c>
       <c r="F248" s="5"/>
       <c r="G248" s="4"/>
-      <c r="H248" s="4"/>
+      <c r="H248" s="4" t="s">
+        <v>1640</v>
+      </c>
       <c r="I248" s="4"/>
       <c r="O248" s="10"/>
+      <c r="P248" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="249" spans="1:15" ht="22.5" customHeight="1">
       <c r="A249" s="4" t="s">
@@ -15978,9 +18030,14 @@
       </c>
       <c r="F249" s="5"/>
       <c r="G249" s="4"/>
-      <c r="H249" s="4"/>
+      <c r="H249" s="4" t="s">
+        <v>1641</v>
+      </c>
       <c r="I249" s="4"/>
       <c r="O249" s="10"/>
+      <c r="P249" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="250" spans="1:15" ht="22.5" customHeight="1">
       <c r="A250" s="4" t="s">
@@ -16000,9 +18057,14 @@
       </c>
       <c r="F250" s="5"/>
       <c r="G250" s="4"/>
-      <c r="H250" s="4"/>
+      <c r="H250" s="4" t="s">
+        <v>1642</v>
+      </c>
       <c r="I250" s="4"/>
       <c r="O250" s="10"/>
+      <c r="P250" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="251" spans="1:15" ht="22.5" customHeight="1">
       <c r="A251" s="4" t="s">
@@ -16022,9 +18084,14 @@
       </c>
       <c r="F251" s="5"/>
       <c r="G251" s="4"/>
-      <c r="H251" s="4"/>
+      <c r="H251" s="4" t="s">
+        <v>1643</v>
+      </c>
       <c r="I251" s="4"/>
       <c r="O251" s="10"/>
+      <c r="P251" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="252" spans="1:15" ht="22.5" customHeight="1">
       <c r="A252" s="4" t="s">
@@ -16044,9 +18111,14 @@
       </c>
       <c r="F252" s="5"/>
       <c r="G252" s="4"/>
-      <c r="H252" s="4"/>
+      <c r="H252" s="4" t="s">
+        <v>1644</v>
+      </c>
       <c r="I252" s="4"/>
       <c r="O252" s="10"/>
+      <c r="P252" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="253" spans="1:15" ht="22.5" customHeight="1">
       <c r="A253" s="4" t="s">
@@ -16066,9 +18138,14 @@
       </c>
       <c r="F253" s="5"/>
       <c r="G253" s="4"/>
-      <c r="H253" s="4"/>
+      <c r="H253" s="4" t="s">
+        <v>1645</v>
+      </c>
       <c r="I253" s="4"/>
       <c r="O253" s="10"/>
+      <c r="P253" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="254" spans="1:15" ht="22.5" customHeight="1">
       <c r="A254" s="4" t="s">
@@ -16088,9 +18165,14 @@
       </c>
       <c r="F254" s="5"/>
       <c r="G254" s="4"/>
-      <c r="H254" s="4"/>
+      <c r="H254" s="4" t="s">
+        <v>1646</v>
+      </c>
       <c r="I254" s="4"/>
       <c r="O254" s="10"/>
+      <c r="P254" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="255" spans="1:15" ht="22.5" customHeight="1">
       <c r="A255" s="4" t="s">
@@ -16110,9 +18192,14 @@
       </c>
       <c r="F255" s="5"/>
       <c r="G255" s="4"/>
-      <c r="H255" s="4"/>
+      <c r="H255" s="4" t="s">
+        <v>1647</v>
+      </c>
       <c r="I255" s="4"/>
       <c r="O255" s="10"/>
+      <c r="P255" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="256" spans="1:15" ht="22.5" customHeight="1">
       <c r="A256" s="4" t="s">
@@ -16132,9 +18219,14 @@
       </c>
       <c r="F256" s="5"/>
       <c r="G256" s="4"/>
-      <c r="H256" s="4"/>
+      <c r="H256" s="4" t="s">
+        <v>1648</v>
+      </c>
       <c r="I256" s="4"/>
       <c r="O256" s="10"/>
+      <c r="P256" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="257" spans="1:15" ht="22.5" customHeight="1">
       <c r="A257" s="4" t="s">
@@ -16154,9 +18246,14 @@
       </c>
       <c r="F257" s="5"/>
       <c r="G257" s="4"/>
-      <c r="H257" s="4"/>
+      <c r="H257" s="4" t="s">
+        <v>1649</v>
+      </c>
       <c r="I257" s="4"/>
       <c r="O257" s="10"/>
+      <c r="P257" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="258" spans="1:15" ht="22.5" customHeight="1">
       <c r="A258" s="4" t="s">
@@ -16176,9 +18273,14 @@
       </c>
       <c r="F258" s="5"/>
       <c r="G258" s="4"/>
-      <c r="H258" s="4"/>
+      <c r="H258" s="4" t="s">
+        <v>1650</v>
+      </c>
       <c r="I258" s="4"/>
       <c r="O258" s="10"/>
+      <c r="P258" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="259" spans="1:15" ht="22.5" customHeight="1">
       <c r="A259" s="4" t="s">
@@ -16198,9 +18300,14 @@
       </c>
       <c r="F259" s="5"/>
       <c r="G259" s="4"/>
-      <c r="H259" s="4"/>
+      <c r="H259" s="4" t="s">
+        <v>1651</v>
+      </c>
       <c r="I259" s="4"/>
       <c r="O259" s="10"/>
+      <c r="P259" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="260" spans="1:15" ht="22.5" customHeight="1">
       <c r="A260" s="4" t="s">
@@ -16220,9 +18327,14 @@
       </c>
       <c r="F260" s="5"/>
       <c r="G260" s="4"/>
-      <c r="H260" s="4"/>
+      <c r="H260" s="4" t="s">
+        <v>1652</v>
+      </c>
       <c r="I260" s="4"/>
       <c r="O260" s="10"/>
+      <c r="P260" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="261" spans="1:15" ht="22.5" customHeight="1">
       <c r="A261" s="4" t="s">
@@ -16242,9 +18354,14 @@
       </c>
       <c r="F261" s="5"/>
       <c r="G261" s="4"/>
-      <c r="H261" s="4"/>
+      <c r="H261" s="4" t="s">
+        <v>1653</v>
+      </c>
       <c r="I261" s="4"/>
       <c r="O261" s="10"/>
+      <c r="P261" s="5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="262" spans="1:15" ht="22.5" customHeight="1">
       <c r="A262" s="4" t="s">
@@ -16262,9 +18379,17 @@
       <c r="E262" s="4" t="s">
         <v>1235</v>
       </c>
-      <c r="F262" s="5"/>
+      <c r="F262" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G262" s="4"/>
-      <c r="H262" s="4"/>
+      <c r="H262" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah 1 saat membuka Pusat Otomasi setelah memilih workspace Studio menggunakan ACCOUNT #10 ? Insinyur 3D, frontend menampilkan ?Unexpected Application Error!? dan ?Invalid time value?. Expected Result mengharuskan event Studio dipublikasikan dan diproses unified worker, terisolasi dari Craft, dapat ditelusuri, serta smoke Studio Automations lulus. Actual page error membuat daftar event, rule, worker, run, dan seluruh workflow tidak tersedia. Persyaratan domain event outbox, matching, processed state, cross-workspace isolation, dan smoke test tidak terpenuhi karena UI fitur unavailable setelah error render. Bukti: test-evidence/session-262-271/UNX-S18-006/01-262-automations-invalid-time-value.png</t>
+        </is>
+      </c>
       <c r="I262" s="4"/>
       <c r="O262" s="10"/>
     </row>
@@ -16284,9 +18409,17 @@
       <c r="E263" s="4" t="s">
         <v>1240</v>
       </c>
-      <c r="F263" s="5"/>
+      <c r="F263" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G263" s="4"/>
-      <c r="H263" s="4"/>
+      <c r="H263" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah 1 saat membuka Pusat Otomasi setelah memilih workspace Studio menggunakan ACCOUNT #10 ? Insinyur 3D, frontend menampilkan ?Unexpected Application Error!? dan ?Invalid time value?. Expected Result mengharuskan candidate deadline mengikuti threshold dan status aktif, context project manager lengkap, cooldown aman, serta boundary WIB/UTC konsisten. Actual page error membuat pengaturan, candidate, context, cadence, dan boundary waktu tidak tersedia untuk diuji. Persyaratan sensor deadline approaching tidak terpenuhi karena UI fitur unavailable setelah error render. Bukti: test-evidence/session-262-271/UNX-S18-007/01-263-automations-invalid-time-value.png</t>
+        </is>
+      </c>
       <c r="I263" s="4"/>
       <c r="O263" s="10"/>
     </row>
@@ -16306,9 +18439,17 @@
       <c r="E264" s="4" t="s">
         <v>1244</v>
       </c>
-      <c r="F264" s="5"/>
+      <c r="F264" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G264" s="4"/>
-      <c r="H264" s="4"/>
+      <c r="H264" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah 1 saat membuka Pusat Otomasi setelah memilih workspace Studio menggunakan ACCOUNT #10 ? Insinyur 3D, frontend menampilkan ?Unexpected Application Error!? dan ?Invalid time value?. Expected Result mengharuskan sensor project overdue, milestone due, dan deliverable overdue memilih entity dengan eligibility yang benar, membawa nested context, menghormati status tertutup, dan tetap read-only. Actual page error membuat candidate, nested context, registry capability, dan verifikasi no-mutation tidak tersedia. Persyaratan tiga sensor tidak terpenuhi karena UI fitur unavailable setelah error render. Bukti: test-evidence/session-262-271/UNX-S18-008/01-264-automations-invalid-time-value.png</t>
+        </is>
+      </c>
       <c r="I264" s="4"/>
       <c r="O264" s="10"/>
     </row>
@@ -16328,9 +18469,17 @@
       <c r="E265" s="4" t="s">
         <v>1249</v>
       </c>
-      <c r="F265" s="5"/>
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G265" s="4"/>
-      <c r="H265" s="4"/>
+      <c r="H265" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah 1 saat membuka Pusat Otomasi setelah memilih workspace Studio menggunakan ACCOUNT #10 ? Insinyur 3D, frontend menampilkan ?Unexpected Application Error!? dan ?Invalid time value?. Expected Result mengharuskan sensor quotation expiring/expired hanya memakai quotation sent sesuai threshold, menyediakan context dan placeholder, tidak memutasi status, serta konsisten dengan Billing dan boundary WIB. Actual page error membuat setting warning-days, candidate, context, template, dan rekonsiliasi tidak tersedia. Persyaratan sensor quotation tidak terpenuhi karena UI fitur unavailable setelah error render. Bukti: test-evidence/session-262-271/UNX-S18-009/01-265-automations-invalid-time-value.png</t>
+        </is>
+      </c>
       <c r="I265" s="4"/>
       <c r="O265" s="10"/>
     </row>
@@ -16350,9 +18499,17 @@
       <c r="E266" s="4" t="s">
         <v>1254</v>
       </c>
-      <c r="F266" s="5"/>
+      <c r="F266" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G266" s="4"/>
-      <c r="H266" s="4"/>
+      <c r="H266" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah 1 saat membuka Pusat Otomasi setelah memilih workspace Studio menggunakan ACCOUNT #10 ? Insinyur 3D, frontend menampilkan ?Unexpected Application Error!? dan ?Invalid time value?. Expected Result mengharuskan sensor invoice due/overdue dan payment schedule mengikuti status, saldo, setting, mapping context, serta rekonsiliasi Billing/Finance tanpa mutasi keuangan. Actual page error membuat eligibility, pengaturan, context mapping, dan rekonsiliasi tidak tersedia. Persyaratan sensor invoice dan payment schedule tidak terpenuhi karena UI fitur unavailable setelah error render. Bukti: test-evidence/session-262-271/UNX-S18-010/01-266-automations-invalid-time-value.png</t>
+        </is>
+      </c>
       <c r="I266" s="4"/>
       <c r="O266" s="10"/>
     </row>
@@ -16372,9 +18529,17 @@
       <c r="E267" s="4" t="s">
         <v>1259</v>
       </c>
-      <c r="F267" s="5"/>
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G267" s="4"/>
-      <c r="H267" s="4"/>
+      <c r="H267" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah 1 saat membuka Pusat Otomasi setelah memilih workspace Studio menggunakan ACCOUNT #10 ? Insinyur 3D, frontend menampilkan ?Unexpected Application Error!? dan ?Invalid time value?. Expected Result mengharuskan sensor maintenance memakai record terbaru dan warning window yang benar, return overdue hanya untuk assignment yang belum dikembalikan, edge case asset transparan, dan sensor read-only. Actual page error membuat latest maintenance, candidate, assignment eligibility, status edge case, dan rekonsiliasi Equipment tidak tersedia. Persyaratan sensor maintenance/return tidak terpenuhi karena UI fitur unavailable setelah error render. Bukti: test-evidence/session-262-271/UNX-S18-011/01-267-automations-invalid-time-value.png</t>
+        </is>
+      </c>
       <c r="I267" s="4"/>
       <c r="O267" s="10"/>
     </row>
@@ -16394,9 +18559,17 @@
       <c r="E268" s="4" t="s">
         <v>1264</v>
       </c>
-      <c r="F268" s="5"/>
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G268" s="4"/>
-      <c r="H268" s="4"/>
+      <c r="H268" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah 1 saat membuka Pusat Otomasi setelah memilih workspace Studio menggunakan ACCOUNT #10 ? Insinyur 3D, frontend menampilkan ?Unexpected Application Error!? dan ?Invalid time value?. Expected Result mengharuskan notification.create dan tasks.create menerapkan source-module authorization, recipient yang eligible, project-manager guard, template whitelist, dedupe, dan retry safety tanpa memutasi source. Actual page error membuat action, recipient, template, dedupe, dan retry workflow tidak tersedia. Persyaratan notification/task automation tidak terpenuhi karena UI fitur unavailable setelah error render. Bukti: test-evidence/session-262-271/UNX-S18-012/01-268-automations-invalid-time-value.png</t>
+        </is>
+      </c>
       <c r="I268" s="4"/>
       <c r="O268" s="10"/>
     </row>
@@ -16416,9 +18589,17 @@
       <c r="E269" s="4" t="s">
         <v>1269</v>
       </c>
-      <c r="F269" s="5"/>
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G269" s="4"/>
-      <c r="H269" s="4"/>
+      <c r="H269" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah 1 saat membuka Pusat Otomasi setelah memilih workspace Studio menggunakan ACCOUNT #10 ? Insinyur 3D, frontend menampilkan ?Unexpected Application Error!? dan ?Invalid time value?. Expected Result mengharuskan priority.set dan try_mark_paid memakai supported event serta canonical guard, memetakan payment context dengan benar, idempotent, dan mengikuti permission. Actual page error membuat action mutation, guard, payment context, skip, dan permission tidak tersedia. Persyaratan project mutation actions tidak terpenuhi karena UI fitur unavailable setelah error render. Bukti: test-evidence/session-262-271/UNX-S18-013/01-269-automations-invalid-time-value.png</t>
+        </is>
+      </c>
       <c r="I269" s="4"/>
       <c r="O269" s="10"/>
     </row>
@@ -16438,9 +18619,17 @@
       <c r="E270" s="4" t="s">
         <v>1274</v>
       </c>
-      <c r="F270" s="5"/>
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G270" s="4"/>
-      <c r="H270" s="4"/>
+      <c r="H270" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah 1 saat membuka Pusat Otomasi setelah memilih workspace Studio menggunakan ACCOUNT #10 ? Insinyur 3D, frontend menampilkan ?Unexpected Application Error!? dan ?Invalid time value?. Expected Result mengharuskan studio.project.create_from_quotation hanya berjalan untuk quotation accepted, mengambil service snapshot, menjaga alur status dan satu link, serta aman terhadap concurrency dan retry. Actual page error membuat action, validasi accepted-only, status flow, one-link, dan retry workflow tidak tersedia. Persyaratan create project from quotation tidak terpenuhi karena UI fitur unavailable setelah error render. Bukti: test-evidence/session-262-271/UNX-S18-014/01-270-automations-invalid-time-value.png</t>
+        </is>
+      </c>
       <c r="I270" s="4"/>
       <c r="O270" s="10"/>
     </row>
@@ -16460,9 +18649,17 @@
       <c r="E271" s="4" t="s">
         <v>1279</v>
       </c>
-      <c r="F271" s="5"/>
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G271" s="4"/>
-      <c r="H271" s="4"/>
+      <c r="H271" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah 1 saat membuka Pusat Otomasi setelah memilih workspace Studio menggunakan ACCOUNT #10 ? Insinyur 3D, frontend menampilkan ?Unexpected Application Error!? dan ?Invalid time value?. Expected Result mengharuskan generate report memvalidasi 10 report dan 3 format, permission export, stored report/audit, semantics period/currency/row, dan completion end-to-end. Actual page error membuat rule generate report, validasi, export, stored report, audit, dan weekly template tidak tersedia. Persyaratan analytics report automation tidak terpenuhi karena UI fitur unavailable setelah error render. Bukti: test-evidence/session-262-271/UNX-S18-015/01-271-automations-invalid-time-value.png</t>
+        </is>
+      </c>
       <c r="I271" s="4"/>
       <c r="O271" s="10"/>
     </row>
@@ -16482,9 +18679,17 @@
       <c r="E272" s="4" t="s">
         <v>1284</v>
       </c>
-      <c r="F272" s="5"/>
+      <c r="F272" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G272" s="4"/>
-      <c r="H272" s="4"/>
+      <c r="H272" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah 1 saat membuka /app/documents menggunakan ACCOUNT #10 ? Insinyur 3D, Pusat Dokumen tampil dengan summary Aktif 0, Diarsipkan 0, Total 0. Search, filter workspace Uni-Inside Studio, jenis Invoice, sumber Studio Projects, tampilan arsip, dan reload dijalankan; hasilnya ?Tidak ada dokumen sesuai filter?. Expected Result mengharuskan scope organisasi/workspace/source permission, latest-version projection, histori versi, pagination, dan 404 lintas scope dapat direkonsiliasi. Actual tidak ada dokumen fixture sehingga versi, source-owned permission, metadata lintas scope, dan detail inaccessible tidak dapat diuji; Expected Result tidak terpenuhi penuh karena prerequisite data tidak tersedia. Bukti: test-evidence/session-272-281/UNX-S19-001/01-document-center-initial.png; test-evidence/session-272-281/UNX-S19-001/02-document-filter-empty.png</t>
+        </is>
+      </c>
       <c r="I272" s="4"/>
       <c r="O272" s="10"/>
     </row>
@@ -16504,9 +18709,17 @@
       <c r="E273" s="4" t="s">
         <v>1289</v>
       </c>
-      <c r="F273" s="5"/>
+      <c r="F273" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G273" s="4"/>
-      <c r="H273" s="4"/>
+      <c r="H273" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah 1 saat membuka form Unggah Dokumen menggunakan ACCOUNT #10 ? Insinyur 3D, UI menampilkan batas PDF/gambar/ZIP/DOCX/XLSX/PPTX hingga 25 MB, field Judul/Jenis/Workspace/Deskripsi, dan tombol Unggah. Submit tanpa file tidak menampilkan pesan validasi terlihat. Expected Result mengharuskan validasi file/scope, DOC code, version 1, registry, checksum, private storage, audit, dan atomic cleanup. Actual tidak tersedia fixture file valid/invalid/oversize untuk menyelesaikan alur upload dan tidak ada hasil upload yang dapat diverifikasi; Expected Result tidak terpenuhi penuh karena prerequisite file tidak tersedia. Bukti: test-evidence/session-272-281/UNX-S19-002/01-upload-validation-no-file.png</t>
+        </is>
+      </c>
       <c r="I273" s="4"/>
       <c r="O273" s="10"/>
     </row>
@@ -16526,9 +18739,17 @@
       <c r="E274" s="4" t="s">
         <v>1294</v>
       </c>
-      <c r="F274" s="5"/>
+      <c r="F274" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G274" s="4"/>
-      <c r="H274" s="4"/>
+      <c r="H274" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah 1?5 setelah filter Pusat Dokumen dikembalikan ke semua workspace/jenis/sumber menggunakan ACCOUNT #10 ? Insinyur 3D, summary tetap 0 dan UI menampilkan ?Tidak ada dokumen sesuai filter?. Expected Result mengharuskan metadata manual dapat diedit, source-owned read-only, version baru bertambah konsisten, konflik concurrent ditolak, dan histori versi tersedia. Actual tidak ada dokumen manual/source-owned untuk dipilih sehingga seluruh workflow metadata/version tidak dapat dijalankan; Expected Result tidak terpenuhi karena prerequisite data tidak tersedia. Bukti: test-evidence/session-272-281/UNX-S19-003/01-document-version-list-empty.png</t>
+        </is>
+      </c>
       <c r="I274" s="4"/>
       <c r="O274" s="10"/>
     </row>
@@ -16548,9 +18769,17 @@
       <c r="E275" s="4" t="s">
         <v>1299</v>
       </c>
-      <c r="F275" s="5"/>
+      <c r="F275" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G275" s="4"/>
-      <c r="H275" s="4"/>
+      <c r="H275" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah archive/restore saat membuka tampilan arsip Pusat Dokumen menggunakan ACCOUNT #10 ? Insinyur 3D, UI dapat berpindah ke ?Lihat arsip? tetapi summary tetap Aktif 0, Diarsipkan 0, Total 0 dan tidak ada dokumen. Expected Result mengharuskan archive/restore logical document, proteksi source-owned, preview/download scoped, dan storage integrity. Actual tidak ada dokumen untuk diproses atau di-preview/download; Expected Result tidak terpenuhi karena prerequisite data tidak tersedia. Bukti: test-evidence/session-272-281/UNX-S19-004/01-archive-preview-empty.png</t>
+        </is>
+      </c>
       <c r="I275" s="4"/>
       <c r="O275" s="10"/>
     </row>
@@ -16570,9 +18799,17 @@
       <c r="E276" s="4" t="s">
         <v>1304</v>
       </c>
-      <c r="F276" s="5"/>
+      <c r="F276" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G276" s="4"/>
-      <c r="H276" s="4"/>
+      <c r="H276" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah 1 saat membuka /app/calendar menggunakan ACCOUNT #10 ? Insinyur 3D, Kalender dapat menampilkan mode Bulan/Minggu/Agenda, Hari Ini, navigasi periode, Refresh, dan filter Uni-Inside Studio. Expected Result mengharuskan event/task ter-scope, summary/meta, source permission, deep link, ordering, dan UTC?WIB/all-day rendering dapat diverifikasi. Actual UI menampilkan ?Tidak ada jadwal dalam rentang ini? dan tidak ada fixture event/task; summary/meta yang dipersyaratkan juga tidak terlihat pada halaman. Expected Result tidak terpenuhi penuh karena prerequisite data/workflow tidak tersedia. Bukti: test-evidence/session-272-281/UNX-S19-005/01-calendar-empty-agenda-studio.png</t>
+        </is>
+      </c>
       <c r="I276" s="4"/>
       <c r="O276" s="10"/>
     </row>
@@ -16592,9 +18829,17 @@
       <c r="E277" s="4" t="s">
         <v>1309</v>
       </c>
-      <c r="F277" s="5"/>
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G277" s="4"/>
-      <c r="H277" s="4"/>
+      <c r="H277" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah create/update event manual menggunakan ACCOUNT #10 ? Insinyur 3D, event Uni-Inside Craft berhasil dibuat melalui UI dengan kode EVT-000635, status scheduled, waktu/lokasi/workspace terlihat, dan perubahan judul/deskripsi tersimpan. Validasi due sebelum start menampilkan ?Waktu selesai harus setelah waktu mulai?, sedangkan percobaan Global menampilkan ?Izin calendar.manage diperlukan untuk acara global?. Expected Result juga mengharuskan all-day/timezone/reminder/attendee guard serta soft-delete dan audit delete. Actual detail event hanya menyediakan Edit dan tidak menyediakan tombol Delete; event uji tetap terlihat, sehingga langkah soft-delete/audit delete serta sebagian validasi tidak dapat diselesaikan. Expected Result tidak terpenuhi penuh. Bukti: test-evidence/session-272-281/UNX-S19-006/01-event-created-and-date-order-validation.png; test-evidence/session-272-281/UNX-S19-006/02-global-guard-and-allday-validation.png; test-evidence/session-272-281/UNX-S19-006/03-event-detail-no-delete-action.png</t>
+        </is>
+      </c>
       <c r="I277" s="4"/>
       <c r="O277" s="10"/>
     </row>
@@ -16614,9 +18859,17 @@
       <c r="E278" s="4" t="s">
         <v>1314</v>
       </c>
-      <c r="F278" s="5"/>
+      <c r="F278" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G278" s="4"/>
-      <c r="H278" s="4"/>
+      <c r="H278" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah membuka detail event menggunakan ACCOUNT #10 ? Insinyur 3D, detail EVT-000635 menampilkan scope Uni-Inside Craft, status scheduled, tombol Edit, dan ?Peserta: Tidak ada peserta?. Expected Result mengharuskan validasi attendee workspace/permission, replace/RSVP, notification invite/update, capability matrix, source-owned read-only, dan source_action_url. Actual tidak ada attendee atau source-owned event/action URL fixture untuk menjalankan rangkaian tersebut dari frontend; Expected Result tidak terpenuhi penuh karena prerequisite data/workflow tidak tersedia. Bukti: test-evidence/session-272-281/UNX-S19-007/01-event-detail-no-attendees-source-action.png</t>
+        </is>
+      </c>
       <c r="I278" s="4"/>
       <c r="O278" s="10"/>
     </row>
@@ -16636,9 +18889,17 @@
       <c r="E279" s="4" t="s">
         <v>1319</v>
       </c>
-      <c r="F279" s="5"/>
+      <c r="F279" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G279" s="4"/>
-      <c r="H279" s="4"/>
+      <c r="H279" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah membuka tab Tugas menggunakan ACCOUNT #10 ? Insinyur 3D, summary Tugas Saya Aktif/Jatuh Tempo Hari Ini/Terlambat/Selesai Minggu Ini semuanya 0. Tugas Saya, filter status/prioritas/jatuh tempo, dan search dapat digunakan; kombinasi filter menghasilkan ?Belum ada tugas yang sesuai?. Expected Result mengharuskan source permission, workspace scope, summary/meta, pagination, DTO, dan deep-link detail dapat direkonsiliasi. Actual tidak ada task manual/generated untuk diverifikasi; Expected Result tidak terpenuhi penuh karena prerequisite data tidak tersedia. Bukti: test-evidence/session-272-281/UNX-S19-008/01-task-filters-empty.png</t>
+        </is>
+      </c>
       <c r="I279" s="4"/>
       <c r="O279" s="10"/>
     </row>
@@ -16658,9 +18919,17 @@
       <c r="E280" s="4" t="s">
         <v>1324</v>
       </c>
-      <c r="F280" s="5"/>
+      <c r="F280" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G280" s="4"/>
-      <c r="H280" s="4"/>
+      <c r="H280" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah create task manual menggunakan ACCOUNT #10 ? Insinyur 3D, form Tambah Tugas tersedia. Submit task Uni-Inside Craft tidak menampilkan task pada list setelah dialog tertutup. Percobaan Global menampilkan ?Izin tasks.manage diperlukan untuk tugas global?, dan due sebelum start menampilkan ?Jatuh tempo harus setelah waktu mulai?. Expected Result mengharuskan TSK code, status todo, scope, assignee eligibility/notification, lifecycle, capability matrix, archive, dan history. Actual tidak ada task yang dapat diverifikasi untuk bagian tersebut; Expected Result tidak terpenuhi penuh. Bukti: test-evidence/session-272-281/UNX-S19-009/01-task-global-guard-date-validation.png</t>
+        </is>
+      </c>
       <c r="I280" s="4"/>
       <c r="O280" s="10"/>
     </row>
@@ -16680,9 +18949,17 @@
       <c r="E281" s="4" t="s">
         <v>1329</v>
       </c>
-      <c r="F281" s="5"/>
+      <c r="F281" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G281" s="4"/>
-      <c r="H281" s="4"/>
+      <c r="H281" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah membuat generated task menggunakan ACCOUNT #10 ? Insinyur 3D, tidak tersedia kontrol frontend untuk sourceKey deterministik, retry/reuse, source-owned, source traceability, atau rekonsiliasi automation. Saat Pusat Otomasi dibuka melalui UI, frontend menampilkan ?Unexpected Application Error!? dan ?Invalid time value?. Expected Result mengharuskan generated task retry-safe, unik, source-owned, dan dapat ditelusuri; actual workflow tidak tersedia dari frontend. Expected Result tidak terpenuhi karena fitur UI unavailable. Bukti: test-evidence/session-272-281/UNX-S19-010/01-generated-task-automation-unavailable.png</t>
+        </is>
+      </c>
       <c r="I281" s="4"/>
       <c r="O281" s="10"/>
     </row>
@@ -16702,9 +18979,17 @@
       <c r="E282" s="4" t="s">
         <v>1334</v>
       </c>
-      <c r="F282" s="5"/>
+      <c r="F282" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G282" s="4"/>
-      <c r="H282" s="4"/>
+      <c r="H282" s="4" t="inlineStr">
+        <is>
+          <t>Langkah 1–9 dilakukan melalui UI menggunakan ACCOUNT #10 — Insinyur 3D: Log Audit dibuka, workspace/filter, summary, detail, serta ekspor CSV/XLSX dicoba. Pada langkah 10, tanggal dari 2026-09-15 dengan tanggal sampai 2026-09-14 membuat UI menampilkan ‘Log Audit tidak dapat dimuat. Silakan coba lagi.’ tanpa validasi AUDIT_INVALID_DATE. Expected Result mengharuskan audit history scoped/terfilter, summary-meta-detail konsisten, historical actor dipertahankan, data sensitif tidak bocor, dan rentang invalid menghasilkan AUDIT_INVALID_DATE; validasi tanggal yang diwajibkan tidak terpenuhi dan hasil lengkap tidak dapat dinyatakan Pass. Evidence: test-evidence/session-282-291/UNX-S19-011/01-invalid-date-and-filter-error.png; test-evidence/session-282-291/UNX-S19-011/02-summary-read-filtered.png.</t>
+        </is>
+      </c>
       <c r="I282" s="4"/>
       <c r="O282" s="10"/>
     </row>
@@ -16724,9 +19009,17 @@
       <c r="E283" s="4" t="s">
         <v>1339</v>
       </c>
-      <c r="F283" s="5"/>
+      <c r="F283" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G283" s="4"/>
-      <c r="H283" s="4"/>
+      <c r="H283" s="4" t="inlineStr">
+        <is>
+          <t>Langkah filter Login+Global dilakukan melalui UI menggunakan ACCOUNT #10 — Insinyur 3D, kemudian tombol CSV dan Excel digunakan. UI menampilkan 100 hasil; tombol ekspor tersedia dan filter dapat diterapkan. Artefak ekspor mentah tidak dipertahankan sebagai evidence karena memuat identitas aktor. Namun prasyarat dataset &gt;10.000, akun pembanding tanpa reports.export, nilai formula-injection, dan secret redaction tidak tersedia pada frontend, sehingga hard cap 10.000 eksplisit, parity seluruh filter, keamanan formula, dan redaction tidak dapat diverifikasi lengkap. Expected Result belum seluruhnya terpenuhi; kasus dicatat Bug/Failed. Evidence aman: test-evidence/session-282-291/UNX-S19-012/01-filter-parity-controls.png.</t>
+        </is>
+      </c>
       <c r="I283" s="4"/>
       <c r="O283" s="10"/>
     </row>
@@ -16746,9 +19039,17 @@
       <c r="E284" s="4" t="s">
         <v>1344</v>
       </c>
-      <c r="F284" s="5"/>
+      <c r="F284" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G284" s="4"/>
-      <c r="H284" s="4"/>
+      <c r="H284" s="4" t="inlineStr">
+        <is>
+          <t>Langkah route Integrations, connections, connections/new, providers, history, dan history detail diuji melalui UI menggunakan ACCOUNT #10 — Insinyur 3D. Provider catalog menampilkan Mock Test Connector (Development Only) sebagai ‘Tersedia’ dengan CTA ‘Hubungkan’ dan capability Test/Sync, padahal Expected Result menyatakan MOCK_TEST_CONNECTOR tidak boleh tampil di production; daftar koneksi juga hanya berisi provider legacy yang unsupported/test. Requirement provider production/planned safety dan visibilitas operasional tidak terpenuhi, sehingga hasil lengkap bukan Pass. Evidence: test-evidence/session-282-291/UNX-S19-013/01-provider-catalog.png; test-evidence/session-282-291/UNX-S19-013/02-history-detail-not-found.png; test-evidence/session-282-291/UNX-S19-013/03-connections-visible-scope-status.png.</t>
+        </is>
+      </c>
       <c r="I284" s="4"/>
       <c r="O284" s="10"/>
     </row>
@@ -16768,9 +19069,17 @@
       <c r="E285" s="4" t="s">
         <v>1349</v>
       </c>
-      <c r="F285" s="5"/>
+      <c r="F285" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G285" s="4"/>
-      <c r="H285" s="4"/>
+      <c r="H285" s="4" t="inlineStr">
+        <is>
+          <t>Wizard create Google Drive scope Craft dijalankan melalui UI menggunakan ACCOUNT #10 — Insinyur 3D. Tanpa mengisi Folder ID wajib dan tanpa kredensial, tombol Selanjutnya tetap maju; review menampilkan ‘Konfigurasi: —’ dan ‘Kredensial: 0 field akan disimpan terenkripsi.’ Expected Result mengharuskan validasi required config/credential dan tidak membuat koneksi parsial; requirement tersebut tidak terpenuhi. Create valid, planned/unknown provider, optimistic concurrency, penghapusan credential, dan audit redaction tidak dapat diselesaikan karena fixture/kredensial eksternal valid tidak tersedia dan penyimpanan data baru tidak dilakukan. Evidence: test-evidence/session-282-291/UNX-S19-014/01-required-config-form.png; test-evidence/session-282-291/UNX-S19-014/02-review-empty-required-fields.png.</t>
+        </is>
+      </c>
       <c r="I285" s="4"/>
       <c r="O285" s="10"/>
     </row>
@@ -16790,9 +19099,17 @@
       <c r="E286" s="4" t="s">
         <v>1354</v>
       </c>
-      <c r="F286" s="5"/>
+      <c r="F286" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G286" s="4"/>
-      <c r="H286" s="4"/>
+      <c r="H286" s="4" t="inlineStr">
+        <is>
+          <t>Detail koneksi TEST_PROVIDER_S10 dan koneksi disabled diuji melalui UI menggunakan ACCOUNT #10 — Insinyur 3D. Kedua koneksi berstatus belum terhubung/dinonaktifkan dengan label Connector Tidak Tersedia dan tidak menyediakan aksi Test/Sync; halaman history terfilter juga menampilkan Belum Ada Riwayat. Expected Result mengharuskan test/sync hanya pada capability+permission yang benar, lifecycle enable/disable/disconnect konsisten, diagnostics secret-safe, serta history/reconciliation lengkap. Connector valid/fixture log tidak tersedia sehingga requirement utama tidak terpenuhi dan kasus dicatat Bug/Failed. Evidence: test-evidence/session-282-291/UNX-S19-015/01-disabled-connection-no-capability-actions.png; test-evidence/session-282-291/UNX-S19-015/02-history-filter-empty.png.</t>
+        </is>
+      </c>
       <c r="I286" s="4"/>
       <c r="O286" s="10"/>
     </row>
@@ -16812,9 +19129,17 @@
       <c r="E287" s="4" t="s">
         <v>1359</v>
       </c>
-      <c r="F287" s="5"/>
+      <c r="F287" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G287" s="4"/>
-      <c r="H287" s="4"/>
+      <c r="H287" s="4" t="inlineStr">
+        <is>
+          <t>Langkah membuka /app/finance dilakukan melalui UI dengan ACCOUNT #1 — Insinyur 3D, setelah verifikasi awal memakai ACCOUNT #10 — Insinyur 3D. UI menampilkan ‘Akses Ditolak’ sehingga 9 tab Unified Finance, meta, finance.read plus domain read layer, workspace/periode/currency filter, dan capability CTA tidak dapat diakses. Expected Result mengharuskan finance.read sebagai gate global serta akses domain/UBU berlapis; route yang ditolak pada akun uji yang disyaratkan tidak memenuhi requirement. Evidence: test-evidence/session-282-291/UNX-S20-001/01-finance-route-access-denied.png.</t>
+        </is>
+      </c>
       <c r="I287" s="4"/>
       <c r="O287" s="10"/>
     </row>
@@ -16834,9 +19159,17 @@
       <c r="E288" s="4" t="s">
         <v>1364</v>
       </c>
-      <c r="F288" s="5"/>
+      <c r="F288" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G288" s="4"/>
-      <c r="H288" s="4"/>
+      <c r="H288" s="4" t="inlineStr">
+        <is>
+          <t>Tab Ringkasan Unified Finance dicoba melalui /app/finance menggunakan ACCOUNT #1 — Insinyur 3D. UI hanya menampilkan ‘Akses Ditolak’, sehingga KPI kas, income/expense/reversal, receivable/payable, transfer activity, workspace breakdown, dan isolasi IDR/USD tidak dapat diuji. Expected Result mengharuskan KPI berasal dari ledger kanonis, reversal benar, rekonsiliasi, dan mata uang tidak tercampur; route inaccessible mencegah seluruh requirement terpenuhi. Evidence: test-evidence/session-282-291/UNX-S20-002/01-finance-overview-route-denied.png.</t>
+        </is>
+      </c>
       <c r="I288" s="4"/>
       <c r="O288" s="10"/>
     </row>
@@ -16856,9 +19189,17 @@
       <c r="E289" s="4" t="s">
         <v>1369</v>
       </c>
-      <c r="F289" s="5"/>
+      <c r="F289" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G289" s="4"/>
-      <c r="H289" s="4"/>
+      <c r="H289" s="4" t="inlineStr">
+        <is>
+          <t>Tab Transaksi dibuka melalui /app/finance/transactions menggunakan ACCOUNT #1 — Insinyur 3D. UI menampilkan ‘Dalam Pengembangan’ dan ‘Mode Pratinjau’, bukan consolidated reader; data tidak disimpan dan filter, default posted, pagination cap, detail scope, join canonical, serta traceability tidak tersedia. Expected Result transaksi kanonis ter-scope dan stabil tidak terpenuhi karena fitur masih placeholder. Evidence: test-evidence/session-282-291/UNX-S20-003/01-finance-transactions-development-placeholder.png.</t>
+        </is>
+      </c>
       <c r="I289" s="4"/>
       <c r="O289" s="10"/>
     </row>
@@ -16878,9 +19219,17 @@
       <c r="E290" s="4" t="s">
         <v>1374</v>
       </c>
-      <c r="F290" s="5"/>
+      <c r="F290" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G290" s="4"/>
-      <c r="H290" s="4"/>
+      <c r="H290" s="4" t="inlineStr">
+        <is>
+          <t>Tab Kas &amp; Bank dibuka melalui /app/finance/treasury menggunakan ACCOUNT #1 — Insinyur 3D. UI menampilkan ‘Dalam Pengembangan’ dan ‘Mode Pratinjau’; lifecycle Shared Treasury, TRS code, COA, opening posting, currency, manage guard, non-zero deactivation, dan audit tidak tersedia. Expected Result treasury consolidation/lifecycle scoped dan atomic tidak terpenuhi karena fitur masih placeholder. Evidence: test-evidence/session-282-291/UNX-S20-004/01-finance-treasury-development-placeholder.png.</t>
+        </is>
+      </c>
       <c r="I290" s="4"/>
       <c r="O290" s="10"/>
     </row>
@@ -16900,9 +19249,17 @@
       <c r="E291" s="4" t="s">
         <v>1379</v>
       </c>
-      <c r="F291" s="5"/>
+      <c r="F291" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G291" s="4"/>
-      <c r="H291" s="4"/>
+      <c r="H291" s="4" t="inlineStr">
+        <is>
+          <t>Tab Transfer Internal dibuka melalui /app/finance/transfers menggunakan ACCOUNT #1 — Insinyur 3D. UI menampilkan ‘Dalam Pengembangan’ dan ‘Mode Pratinjau’; transfer permission/scope, TRF code, same-currency guard, idempotency, posting atomic, journal-balanced, dan history scope tidak tersedia. Expected Result transfer internal kanonis dan aman tidak terpenuhi karena fitur masih placeholder. Evidence: test-evidence/session-282-291/UNX-S20-005/01-finance-transfers-development-placeholder.png.</t>
+        </is>
+      </c>
       <c r="I291" s="4"/>
       <c r="O291" s="10"/>
     </row>
@@ -16922,9 +19279,17 @@
       <c r="E292" s="4" t="s">
         <v>1384</v>
       </c>
-      <c r="F292" s="5"/>
+      <c r="F292" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G292" s="4"/>
-      <c r="H292" s="4"/>
+      <c r="H292" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah membuka Unified Finance dan fitur transaksi bersama dengan ACCOUNT #10 ? Insinyur 3D, halaman /app/finance menampilkan ?Akses Ditolak?; subhalaman Transaksi menampilkan ?Dalam Pengembangan? dan ?Mode Pratinjau? yang menyatakan data tidak disimpan. Expected Result mengharuskan pencatatan transaksi SHARED, jurnal kanonis, idempotensi, pembalikan sekali, KPI dan audit; seluruh tindakan tersebut tidak tersedia. Fitur tidak tersedia. Bukti: test-evidence/session-292-301/UNX-S20-006/01-finance-access-denied.png; test-evidence/session-292-301/UNX-S20-006/02-shared-transaction-unavailable.png.</t>
+        </is>
+      </c>
       <c r="I292" s="4"/>
       <c r="O292" s="10"/>
     </row>
@@ -16944,9 +19309,17 @@
       <c r="E293" s="4" t="s">
         <v>1389</v>
       </c>
-      <c r="F293" s="5"/>
+      <c r="F293" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G293" s="4"/>
-      <c r="H293" s="4"/>
+      <c r="H293" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah membuka tab Piutang, Hutang, dan Anggaran dengan ACCOUNT #10 ? Insinyur 3D, ketiga subhalaman menampilkan ?Dalam Pengembangan? dan ?Mode Pratinjau?, bukan data keuangan operasional. Expected Result mengharuskan outstanding, relasi invoice/supplier invoice/expense/assignment, total multi-mata uang, scope dan rekonsiliasi; tidak ada data atau tindakan UI untuk menjalankannya. Fitur tidak tersedia. Bukti: test-evidence/session-292-301/UNX-S20-007/01-receivables-preview-unavailable.png; test-evidence/session-292-301/UNX-S20-007/02-payables-preview-unavailable.png; test-evidence/session-292-301/UNX-S20-007/03-budgets-preview-unavailable.png.</t>
+        </is>
+      </c>
       <c r="I293" s="4"/>
       <c r="O293" s="10"/>
     </row>
@@ -16966,9 +19339,17 @@
       <c r="E294" s="4" t="s">
         <v>1394</v>
       </c>
-      <c r="F294" s="5"/>
+      <c r="F294" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G294" s="4"/>
-      <c r="H294" s="4"/>
+      <c r="H294" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah membuka Arus Kas dan Jurnal dengan ACCOUNT #10 ? Insinyur 3D, kedua halaman menampilkan ?Dalam Pengembangan? dan ?Mode Pratinjau?. Expected Result mengharuskan bucket WIB, semantik pembalikan, detail jurnal berimbang, guard periode tumpang tindih/terkunci serta close/reopen dan audit; kontrol dan data untuk seluruh alur tersebut tidak tersedia. Fitur tidak tersedia. Bukti: test-evidence/session-292-301/UNX-S20-008/01-cashflow-preview-unavailable.png; test-evidence/session-292-301/UNX-S20-008/02-journals-preview-unavailable.png.</t>
+        </is>
+      </c>
       <c r="I294" s="4"/>
       <c r="O294" s="10"/>
     </row>
@@ -16988,9 +19369,17 @@
       <c r="E295" s="4" t="s">
         <v>1399</v>
       </c>
-      <c r="F295" s="5"/>
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G295" s="4"/>
-      <c r="H295" s="4"/>
+      <c r="H295" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah membuka Unified Finance untuk ekspor dengan ACCOUNT #10 ? Insinyur 3D, halaman menampilkan ?Akses Ditolak?; tidak ada kontrol ekspor CSV/XLSX dari UI. Expected Result mengharuskan ekspor dataset berfilter izin, parity filter, batas 20K, keamanan formula, integritas multi-mata uang dan tanpa efek samping; seluruhnya tidak dapat dijalankan. Fitur/tindakan UI tidak tersedia untuk akun yang diwajibkan. Bukti: test-evidence/session-292-301/UNX-S20-009/01-finance-export-access-denied.png.</t>
+        </is>
+      </c>
       <c r="I295" s="4"/>
       <c r="O295" s="10"/>
     </row>
@@ -17010,9 +19399,17 @@
       <c r="E296" s="4" t="s">
         <v>1404</v>
       </c>
-      <c r="F296" s="5"/>
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G296" s="4"/>
-      <c r="H296" s="4"/>
+      <c r="H296" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah membuka dan menekan Refresh di Pusat Laporan dengan ACCOUNT #10 ? Insinyur 3D, UI menampilkan Laporan Tersedia 0, Craft 0, Studio 0, Keuangan 0, serta ?Tidak ada laporan yang sesuai atau dapat diakses.? Expected Result mengharuskan inventaris registry aktif, group count, metadata, scope unit bisnis dan guard kebocoran ekspor terbaru; katalog dan metadata yang diperlukan tidak tersedia. Fitur/data laporan tidak tersedia. Bukti: test-evidence/session-292-301/UNX-S20-010/01-reports-catalog-empty.png.</t>
+        </is>
+      </c>
       <c r="I296" s="4"/>
       <c r="O296" s="10"/>
     </row>
@@ -17032,9 +19429,17 @@
       <c r="E297" s="4" t="s">
         <v>1409</v>
       </c>
-      <c r="F297" s="5"/>
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G297" s="4"/>
-      <c r="H297" s="4"/>
+      <c r="H297" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah mencari ?Executive Summary? di Pusat Laporan dengan ACCOUNT #10 ? Insinyur 3D, UI tidak menemukan laporan dan katalog tetap kosong. Expected Result mengharuskan Global Executive Summary dan 10 laporan Unified Finance beserta mapping sumber, komposisi izin, requirement SHARED, filter workspace, dan rekonsiliasi data kanonis; tidak ada laporan untuk dibuka atau divalidasi. Fitur/data laporan tidak tersedia. Bukti: test-evidence/session-292-301/UNX-S20-011/01-required-reports-unavailable.png.</t>
+        </is>
+      </c>
       <c r="I297" s="4"/>
       <c r="O297" s="10"/>
     </row>
@@ -17054,9 +19459,17 @@
       <c r="E298" s="4" t="s">
         <v>1414</v>
       </c>
-      <c r="F298" s="5"/>
+      <c r="F298" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G298" s="4"/>
-      <c r="H298" s="4"/>
+      <c r="H298" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah memilih laporan untuk membuka Preview Period dengan ACCOUNT #10 ? Insinyur 3D, Pusat Laporan tidak memiliki kartu laporan (Laporan Tersedia 0). Expected Result mengharuskan normalisasi periode/rentang kustom, guard 3660 hari, WIB, KPI, tabel, grafik, empty-state dan konsistensi sumber-filter; alur Preview tidak dapat dimulai. Fitur tidak tersedia. Bukti: test-evidence/session-292-301/UNX-S20-012/01-report-preview-unavailable.png.</t>
+        </is>
+      </c>
       <c r="I298" s="4"/>
       <c r="O298" s="10"/>
     </row>
@@ -17076,9 +19489,17 @@
       <c r="E299" s="4" t="s">
         <v>1419</v>
       </c>
-      <c r="F299" s="5"/>
+      <c r="F299" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G299" s="4"/>
-      <c r="H299" s="4"/>
+      <c r="H299" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah memilih laporan dan ekspor dengan ACCOUNT #10 ? Insinyur 3D, katalog Pusat Laporan kosong sehingga tidak ada kontrol ekspor CSV/XLSX/PDF yang dapat dioperasikan. Expected Result mengharuskan gate izin per laporan, format didukung, batas 20K, keamanan formula, disclosure PDF, branding, storage, registry dokumen, audit dan cleanup atomik; seluruhnya tidak dapat diuji melalui UI. Fitur tidak tersedia. Bukti: test-evidence/session-292-301/UNX-S20-013/01-report-export-controls-unavailable.png.</t>
+        </is>
+      </c>
       <c r="I299" s="4"/>
       <c r="O299" s="10"/>
     </row>
@@ -17098,9 +19519,17 @@
       <c r="E300" s="4" t="s">
         <v>1424</v>
       </c>
-      <c r="F300" s="5"/>
+      <c r="F300" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G300" s="4"/>
-      <c r="H300" s="4"/>
+      <c r="H300" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah membuka Riwayat Ekspor dengan ACCOUNT #10 ? Insinyur 3D, UI menyatakan ?Belum ada ekspor yang dapat diakses? dan tidak menampilkan baris detail atau unduhan. Expected Result mengharuskan visibilitas per laporan, evaluasi ulang izin/legacy permission, filter/pagination, risiko kelengkapan 500 baris, guard berkas hilang dan parity overview; tindakan serta fixture riwayat yang diperlukan tidak tersedia. Data/fitur pengujian tidak tersedia. Bukti: test-evidence/session-292-301/UNX-S20-014/01-export-history-empty.png.</t>
+        </is>
+      </c>
       <c r="I300" s="4"/>
       <c r="O300" s="10"/>
     </row>
@@ -17120,9 +19549,17 @@
       <c r="E301" s="4" t="s">
         <v>1429</v>
       </c>
-      <c r="F301" s="5"/>
+      <c r="F301" s="5" t="inlineStr">
+        <is>
+          <t>Bug/Failed</t>
+        </is>
+      </c>
       <c r="G301" s="4"/>
-      <c r="H301" s="4"/>
+      <c r="H301" s="4" t="inlineStr">
+        <is>
+          <t>Pada langkah Header Search dengan ACCOUNT #10 ? Insinyur 3D, satu karakter menampilkan guard ?Ketik minimal 2 karakter untuk mencari?; setelah kueri dua karakter, UI menampilkan ?Tidak ada hasil?. Tombol panah bawah dan Enter tidak membuka rute karena tidak ada hasil. Expected Result mengharuskan hasil multi-modul berizin, akses workspace, wildcard literal, batas 8 hasil, debounce/abort, navigasi keyboard, dan safe routing; tanpa hasil/fixture, seluruh verifikasi tersebut tidak terpenuhi. Data hasil pencarian yang disyaratkan tidak tersedia. Bukti: test-evidence/session-292-301/UNX-S20-015/01-search-minimum-character-guard.png; test-evidence/session-292-301/UNX-S20-015/02-search-no-results.png.</t>
+        </is>
+      </c>
       <c r="I301" s="4"/>
       <c r="O301" s="10"/>
     </row>
